--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,260 +478,260 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G2" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H2" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I2" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G3" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H3" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H4" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I4" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G5" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H5" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I5" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G6" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H6" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G7" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H7" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I7" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2432</v>
+        <v>2371</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
+        <v>10372003</v>
       </c>
       <c r="G8" t="n">
-        <v>226000</v>
+        <v>24045569000</v>
       </c>
       <c r="H8" t="n">
-        <v>2260</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="9">
@@ -774,49 +774,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8570</v>
+        <v>2432</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11014402</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>14194389000</v>
+        <v>226000</v>
       </c>
       <c r="H10" t="n">
-        <v>1288.711724885291</v>
+        <v>2260</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -825,109 +825,109 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G11" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H11" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I11" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G12" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H12" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I12" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G13" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H13" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I13" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -947,10 +947,10 @@
         <v>16322100</v>
       </c>
       <c r="G14" t="n">
-        <v>268179335000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H14" t="n">
-        <v>16430.4430802409</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I14" t="n">
         <v>5.01</v>
@@ -959,58 +959,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G15" t="n">
-        <v>49662804000</v>
+        <v>268179335000</v>
       </c>
       <c r="H15" t="n">
-        <v>11879.91675437757</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I15" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1018,27 +1018,27 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G16" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H16" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I16" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1047,72 +1047,72 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G17" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H17" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I17" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G18" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H18" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1121,21 +1121,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H19" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1144,12 +1144,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1158,21 +1158,21 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H20" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1181,12 +1181,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H21" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1218,12 +1218,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1232,21 +1232,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H22" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1255,12 +1255,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1269,109 +1269,109 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H23" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G24" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H24" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I24" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G25" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H25" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I25" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1403,308 +1403,308 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G27" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H27" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I27" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5331</v>
+        <v>6104</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1481600</v>
+        <v>1297500</v>
       </c>
       <c r="G28" t="n">
-        <v>5294365000</v>
+        <v>4476090000</v>
       </c>
       <c r="H28" t="n">
-        <v>3573.410502159827</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G29" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H29" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I29" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G30" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H30" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H31" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I31" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G32" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H32" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I32" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G33" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H33" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G34" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H34" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1713,190 +1713,190 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G35" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H35" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I35" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G36" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H36" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I36" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H37" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G39" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H39" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>9302</v>
+        <v>3106</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1904,27 +1904,27 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3799000</v>
+        <v>900156</v>
       </c>
       <c r="G40" t="n">
-        <v>5671170000</v>
+        <v>4095263000</v>
       </c>
       <c r="H40" t="n">
-        <v>1492.806001579363</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I40" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1933,72 +1933,72 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G41" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H41" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I41" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G42" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H42" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H43" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2030,38 +2030,38 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4849</v>
+        <v>6332</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>5148132000</v>
+        <v>141000</v>
       </c>
       <c r="H44" t="n">
-        <v>1746.940387696806</v>
+        <v>1410</v>
       </c>
       <c r="I44" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2104,160 +2104,160 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G46" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H46" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H47" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G48" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H48" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I48" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G49" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H49" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2266,172 +2266,172 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H50" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I50" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G51" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H51" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I51" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G52" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H52" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I52" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G53" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H53" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I53" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G54" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H54" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="55">
@@ -2474,86 +2474,86 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>7732</v>
+        <v>9987</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>7995900</v>
+        <v>3888200</v>
       </c>
       <c r="G56" t="n">
-        <v>16678425000</v>
+        <v>16086019000</v>
       </c>
       <c r="H56" t="n">
-        <v>2085.872134468915</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I56" t="n">
-        <v>7.380000000000001</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G57" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H57" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H58" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2585,49 +2585,49 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H59" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I59" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2636,146 +2636,146 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G60" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H60" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I60" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G61" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H61" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H62" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I62" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G63" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H63" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I63" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2784,35 +2784,35 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G64" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H64" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I64" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2821,146 +2821,146 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G65" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H65" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I65" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G66" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H66" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I66" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G67" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H67" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I67" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G68" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H68" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I68" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2969,44 +2969,44 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>8141</v>
+        <v>5482</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>100</v>
+        <v>433300</v>
       </c>
       <c r="G69" t="n">
-        <v>93000</v>
+        <v>1367192000</v>
       </c>
       <c r="H69" t="n">
-        <v>930</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4272</v>
+        <v>8141</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3014,90 +3014,90 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>26855100</v>
+        <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>29860350000</v>
+        <v>93000</v>
       </c>
       <c r="H70" t="n">
-        <v>1111.90611839092</v>
+        <v>930</v>
       </c>
       <c r="I70" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6145</v>
+        <v>4272</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G71" t="n">
-        <v>171000</v>
+        <v>29860350000</v>
       </c>
       <c r="H71" t="n">
-        <v>1710</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4205</v>
+        <v>6145</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G72" t="n">
-        <v>24829312000</v>
+        <v>171000</v>
       </c>
       <c r="H72" t="n">
-        <v>1721.078563209627</v>
+        <v>1710</v>
       </c>
       <c r="I72" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3140,160 +3140,160 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6516</v>
+        <v>4205</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>679500</v>
+        <v>14426600</v>
       </c>
       <c r="G74" t="n">
-        <v>4792335000</v>
+        <v>24829312000</v>
       </c>
       <c r="H74" t="n">
-        <v>7052.737306843267</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I74" t="n">
-        <v>5.24</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G75" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H75" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G76" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H76" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G77" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H77" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3302,72 +3302,72 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G78" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H78" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I78" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G79" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H79" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I79" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3376,81 +3376,81 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G80" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H80" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I80" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G81" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H81" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I81" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5541</v>
+        <v>2168</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3458,53 +3458,53 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G82" t="n">
-        <v>127000</v>
+        <v>4445105000</v>
       </c>
       <c r="H82" t="n">
-        <v>1270</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G83" t="n">
-        <v>20578848000</v>
+        <v>127000</v>
       </c>
       <c r="H83" t="n">
-        <v>5066.092575838703</v>
+        <v>1270</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3547,12 +3547,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3572,10 +3572,10 @@
         <v>4062075</v>
       </c>
       <c r="G85" t="n">
-        <v>8729143000</v>
+        <v>20578848000</v>
       </c>
       <c r="H85" t="n">
-        <v>2148.936934940886</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I85" t="n">
         <v>5.2</v>
@@ -3584,160 +3584,160 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G86" t="n">
-        <v>5292086000</v>
+        <v>8729143000</v>
       </c>
       <c r="H86" t="n">
-        <v>2112.609181636727</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I86" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G87" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H87" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I87" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G88" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H88" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I88" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G89" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H89" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I89" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3746,192 +3746,192 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G90" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H90" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I90" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G91" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H91" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I91" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G92" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H92" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I92" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G93" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H93" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I93" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G94" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H94" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I94" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3591</v>
+        <v>4042</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3939,249 +3939,249 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2846091</v>
+        <v>16459200</v>
       </c>
       <c r="G95" t="n">
-        <v>6888596000</v>
+        <v>33451116000</v>
       </c>
       <c r="H95" t="n">
-        <v>2420.370957920882</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I95" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G96" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H96" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G97" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H97" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I97" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G98" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H98" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I98" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G99" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H99" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I99" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G100" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H100" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G101" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H101" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I101" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G102" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H102" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I102" t="n">
         <v>5.02</v>
@@ -4213,197 +4213,197 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G103" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H103" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G104" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H104" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I104" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G105" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H105" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I105" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G106" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H106" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G107" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H107" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I107" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4416,142 +4416,142 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G108" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H108" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I108" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G109" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H109" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I109" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G110" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H110" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G111" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H111" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I111" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4560,35 +4560,35 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G112" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H112" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I112" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4597,30 +4597,30 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G113" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H113" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I113" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4293</v>
+        <v>4631</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4642,355 +4642,355 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>20896886</v>
+        <v>6563759</v>
       </c>
       <c r="G114" t="n">
-        <v>9376038000</v>
+        <v>16844475000</v>
       </c>
       <c r="H114" t="n">
-        <v>448.6811097117532</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I114" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G115" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H115" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I115" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G116" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H116" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I116" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G117" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H117" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I117" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G118" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H118" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I118" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G119" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H119" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I119" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G120" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H120" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I120" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G121" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H121" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G122" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H122" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I122" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5947</v>
+        <v>5844</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>7446200</v>
+        <v>4998800</v>
       </c>
       <c r="G123" t="n">
-        <v>21182239000</v>
+        <v>24949147000</v>
       </c>
       <c r="H123" t="n">
-        <v>2844.704547285864</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I123" t="n">
-        <v>4.96</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -5012,456 +5012,456 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G124" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H124" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I124" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>8303</v>
+        <v>5186</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>20000000</v>
+        <v>1536900</v>
       </c>
       <c r="G125" t="n">
-        <v>56014500000</v>
+        <v>4758738000</v>
       </c>
       <c r="H125" t="n">
-        <v>2800.725</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I125" t="n">
-        <v>9.75</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G126" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I126" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5451</v>
+        <v>2812</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1752800</v>
-      </c>
-      <c r="G127" t="n">
-        <v>5669831000</v>
-      </c>
-      <c r="H127" t="n">
-        <v>3234.727863989046</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>5.029999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>9072</v>
+        <v>5451</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>8377400</v>
+        <v>1752800</v>
       </c>
       <c r="G128" t="n">
-        <v>13394541000</v>
+        <v>5669831000</v>
       </c>
       <c r="H128" t="n">
-        <v>1598.889989734285</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I128" t="n">
-        <v>12.74</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5194</v>
+        <v>9072</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1068798</v>
+        <v>8377400</v>
       </c>
       <c r="G129" t="n">
-        <v>997342000</v>
+        <v>13394541000</v>
       </c>
       <c r="H129" t="n">
-        <v>933.1435874692879</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I129" t="n">
-        <v>9.77</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>8871</v>
+        <v>5194</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1807700</v>
+        <v>1068798</v>
       </c>
       <c r="G130" t="n">
-        <v>3235548000</v>
+        <v>997342000</v>
       </c>
       <c r="H130" t="n">
-        <v>1789.870000553189</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I130" t="n">
-        <v>5.050000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5929</v>
+        <v>8871</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>11571500</v>
+        <v>1807700</v>
       </c>
       <c r="G131" t="n">
-        <v>15114770000</v>
+        <v>3235548000</v>
       </c>
       <c r="H131" t="n">
-        <v>1306.206628354146</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I131" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>8140</v>
+        <v>5929</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1322800</v>
+        <v>11571500</v>
       </c>
       <c r="G132" t="n">
-        <v>4536170000</v>
+        <v>15114770000</v>
       </c>
       <c r="H132" t="n">
-        <v>3429.218324765649</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I132" t="n">
-        <v>5.29</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1878</v>
+        <v>8140</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3452100</v>
+        <v>1322800</v>
       </c>
       <c r="G133" t="n">
-        <v>44793976000</v>
+        <v>4536170000</v>
       </c>
       <c r="H133" t="n">
-        <v>12975.86280814577</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I133" t="n">
-        <v>5.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>533500</v>
+        <v>3452100</v>
       </c>
       <c r="G134" t="n">
-        <v>2009924000</v>
+        <v>44793976000</v>
       </c>
       <c r="H134" t="n">
-        <v>3767.430178069353</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I134" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>3593</v>
+        <v>1882</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1637060</v>
+        <v>533500</v>
       </c>
       <c r="G135" t="n">
-        <v>5502657000</v>
+        <v>2009924000</v>
       </c>
       <c r="H135" t="n">
-        <v>3361.304411567078</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I135" t="n">
-        <v>6.48</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1861</v>
+        <v>3593</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3102784</v>
+        <v>1637060</v>
       </c>
       <c r="G136" t="n">
-        <v>8614573000</v>
+        <v>5502657000</v>
       </c>
       <c r="H136" t="n">
-        <v>2776.401128792723</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I136" t="n">
-        <v>7.07</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="137">
@@ -5504,128 +5504,128 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7350</v>
+        <v>1861</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
+        <v>3102784</v>
+      </c>
+      <c r="G138" t="n">
+        <v>8614573000</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2776.401128792723</v>
+      </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3549</v>
+        <v>7350</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1735200</v>
-      </c>
-      <c r="G139" t="n">
-        <v>11532479000</v>
-      </c>
-      <c r="H139" t="n">
-        <v>6646.195827570309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>6770</v>
+        <v>3549</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>11259700</v>
+        <v>1735200</v>
       </c>
       <c r="G140" t="n">
-        <v>14161429000</v>
+        <v>11532479000</v>
       </c>
       <c r="H140" t="n">
-        <v>1257.709264012363</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I140" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3391</v>
+        <v>6770</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5633,101 +5633,101 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>6354522</v>
+        <v>11259700</v>
       </c>
       <c r="G141" t="n">
-        <v>28876223000</v>
+        <v>14161429000</v>
       </c>
       <c r="H141" t="n">
-        <v>4544.200649553184</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I141" t="n">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1951</v>
+        <v>3391</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>5561200</v>
+        <v>6354522</v>
       </c>
       <c r="G142" t="n">
-        <v>12623472000</v>
+        <v>28876223000</v>
       </c>
       <c r="H142" t="n">
-        <v>2269.918722577861</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I142" t="n">
-        <v>5.06</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QNRY.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3085</v>
+        <v>1951</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1756300</v>
+        <v>5561200</v>
       </c>
       <c r="G143" t="n">
-        <v>4694343000</v>
+        <v>12623472000</v>
       </c>
       <c r="H143" t="n">
-        <v>2672.859420372374</v>
+        <v>2269.918722577861</v>
       </c>
       <c r="I143" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QJNN.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5736,131 +5736,135 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>9842</v>
+        <v>3085</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>2082200</v>
+        <v>1756300</v>
       </c>
       <c r="G144" t="n">
-        <v>3059101000</v>
+        <v>4694343000</v>
       </c>
       <c r="H144" t="n">
-        <v>1469.167707232735</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I144" t="n">
-        <v>5.029999999999999</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QI52.zip</t>
+          <t>S100QJNN.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
+          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>9672</v>
+        <v>9842</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>2410900</v>
+        <v>2082200</v>
       </c>
       <c r="G145" t="n">
-        <v>9382590000</v>
+        <v>3059101000</v>
       </c>
       <c r="H145" t="n">
-        <v>3891.73752540545</v>
+        <v>1469.167707232735</v>
       </c>
       <c r="I145" t="n">
-        <v>8.380000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QGUZ.zip</t>
+          <t>S100QI52.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3558</v>
+        <v>9672</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1214200</v>
+        <v>2410900</v>
       </c>
       <c r="G146" t="n">
-        <v>1538785000</v>
+        <v>9382590000</v>
       </c>
       <c r="H146" t="n">
-        <v>1267.324164058639</v>
+        <v>3891.73752540545</v>
       </c>
       <c r="I146" t="n">
-        <v>10.57</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QF8K.zip</t>
+          <t>S100QGUZ.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2329</v>
+        <v>3558</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+        <v>1214200</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1538785000</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1267.324164058639</v>
+      </c>
       <c r="I147" t="n">
-        <v>9.550000000000001</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="148">
@@ -5899,111 +5903,144 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QDGW.zip</t>
+          <t>S100QF8K.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4324</v>
+        <v>2329</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>13655200</v>
-      </c>
-      <c r="G149" t="n">
-        <v>56753467000</v>
-      </c>
-      <c r="H149" t="n">
-        <v>4156.179843576074</v>
-      </c>
+        <v>4463000</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
-        <v>5.050000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QBB7.zip</t>
+          <t>S100QDGW.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3608</v>
+        <v>4324</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>4569000</v>
+        <v>13655200</v>
       </c>
       <c r="G150" t="n">
-        <v>2005111000</v>
+        <v>56753467000</v>
       </c>
       <c r="H150" t="n">
-        <v>438.851170934559</v>
+        <v>4156.179843576074</v>
       </c>
       <c r="I150" t="n">
-        <v>5.07</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>S100QBB7.zip</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>3608</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>4569000</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2005111000</v>
+      </c>
+      <c r="H151" t="n">
+        <v>438.851170934559</v>
+      </c>
+      <c r="I151" t="n">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>S100Q8UN.zip</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E35393-000_2023-02-13_01_2023-02-20.csv</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="D151" t="n">
+      <c r="D152" t="n">
         <v>6804</v>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="F151" t="n">
+      <c r="F152" t="n">
         <v>3315900</v>
       </c>
-      <c r="G151" t="n">
+      <c r="G152" t="n">
         <v>4322098000</v>
       </c>
-      <c r="H151" t="n">
+      <c r="H152" t="n">
         <v>1303.446424801713</v>
       </c>
-      <c r="I151" t="n">
+      <c r="I152" t="n">
         <v>5.26</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I152"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,297 +478,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G2" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H2" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I2" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G3" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H3" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I3" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G4" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H4" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H5" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I5" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G6" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H6" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I6" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G7" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H7" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G8" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H8" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I8" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G9" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H9" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I9" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="10">
@@ -811,49 +811,49 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G11" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H11" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -862,109 +862,109 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G12" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H12" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I12" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G13" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H13" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I13" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G14" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H14" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I14" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -984,10 +984,10 @@
         <v>16322100</v>
       </c>
       <c r="G15" t="n">
-        <v>268179335000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H15" t="n">
-        <v>16430.4430802409</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I15" t="n">
         <v>5.01</v>
@@ -996,58 +996,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G16" t="n">
-        <v>49662804000</v>
+        <v>268179335000</v>
       </c>
       <c r="H16" t="n">
-        <v>11879.91675437757</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I16" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1055,27 +1055,27 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G17" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H17" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I17" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1084,72 +1084,72 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G18" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H18" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I18" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G19" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H19" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1158,21 +1158,21 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H20" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1181,12 +1181,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H21" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1218,12 +1218,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1232,21 +1232,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H22" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1255,12 +1255,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H23" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1292,12 +1292,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1306,109 +1306,109 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H24" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G25" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H25" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I25" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G26" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H26" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I26" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1440,308 +1440,308 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G28" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H28" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I28" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5331</v>
+        <v>6104</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1481600</v>
+        <v>1297500</v>
       </c>
       <c r="G29" t="n">
-        <v>5294365000</v>
+        <v>4476090000</v>
       </c>
       <c r="H29" t="n">
-        <v>3573.410502159827</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G30" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H30" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I30" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G31" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H31" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H32" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I32" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G33" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H33" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I33" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G34" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H34" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G35" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H35" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1750,190 +1750,190 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G36" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H36" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I36" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G37" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H37" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I37" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G40" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H40" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9302</v>
+        <v>3106</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1941,27 +1941,27 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3799000</v>
+        <v>900156</v>
       </c>
       <c r="G41" t="n">
-        <v>5671170000</v>
+        <v>4095263000</v>
       </c>
       <c r="H41" t="n">
-        <v>1492.806001579363</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I41" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1970,72 +1970,72 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G42" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H42" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I42" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G43" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H43" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H44" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2067,38 +2067,38 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H45" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I45" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2141,160 +2141,160 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4676</v>
+        <v>6927</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
+        <v>1142700</v>
       </c>
       <c r="G47" t="n">
-        <v>242000</v>
+        <v>1023871000</v>
       </c>
       <c r="H47" t="n">
-        <v>2420</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H48" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G49" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H49" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I49" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G50" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H50" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2303,192 +2303,192 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H51" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I51" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G52" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H52" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I52" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G53" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H53" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I53" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G54" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H54" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I54" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4626</v>
+        <v>9006</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G55" t="n">
-        <v>16652257000</v>
+        <v>34824000</v>
       </c>
       <c r="H55" t="n">
-        <v>3565.648720929983</v>
+        <v>1160.8</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>9987</v>
+        <v>4626</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2496,101 +2496,101 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3888200</v>
+        <v>4670190</v>
       </c>
       <c r="G56" t="n">
-        <v>16086019000</v>
+        <v>16652257000</v>
       </c>
       <c r="H56" t="n">
-        <v>4137.137750115735</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>7732</v>
+        <v>9987</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>7995900</v>
+        <v>3888200</v>
       </c>
       <c r="G57" t="n">
-        <v>16678425000</v>
+        <v>16086019000</v>
       </c>
       <c r="H57" t="n">
-        <v>2085.872134468915</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I57" t="n">
-        <v>7.380000000000001</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G58" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H58" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H59" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2622,49 +2622,49 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H60" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I60" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2673,146 +2673,146 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G61" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H61" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I61" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G62" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H62" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H63" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I63" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G64" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H64" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I64" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2821,35 +2821,35 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G65" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H65" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I65" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2858,146 +2858,146 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G66" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H66" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I66" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G67" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H67" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I67" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G68" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H68" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I68" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G69" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H69" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I69" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3006,44 +3006,44 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>8141</v>
+        <v>5482</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>100</v>
+        <v>433300</v>
       </c>
       <c r="G70" t="n">
-        <v>93000</v>
+        <v>1367192000</v>
       </c>
       <c r="H70" t="n">
-        <v>930</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4272</v>
+        <v>8141</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3051,96 +3051,96 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>26855100</v>
+        <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>29860350000</v>
+        <v>93000</v>
       </c>
       <c r="H71" t="n">
-        <v>1111.90611839092</v>
+        <v>930</v>
       </c>
       <c r="I71" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6145</v>
+        <v>4272</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G72" t="n">
-        <v>171000</v>
+        <v>29860350000</v>
       </c>
       <c r="H72" t="n">
-        <v>1710</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G73" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H73" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I73" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4205</v>
+        <v>3569</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3162,175 +3162,175 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>14426600</v>
+        <v>4271704</v>
       </c>
       <c r="G74" t="n">
-        <v>24829312000</v>
+        <v>5808044000</v>
       </c>
       <c r="H74" t="n">
-        <v>1721.078563209627</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I74" t="n">
-        <v>6.29</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6516</v>
+        <v>4205</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>679500</v>
+        <v>14426600</v>
       </c>
       <c r="G75" t="n">
-        <v>4792335000</v>
+        <v>24829312000</v>
       </c>
       <c r="H75" t="n">
-        <v>7052.737306843267</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I75" t="n">
-        <v>5.24</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G76" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H76" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G77" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H77" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G78" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H78" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3339,72 +3339,72 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G79" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H79" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I79" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G80" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H80" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I80" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3413,61 +3413,61 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G81" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H81" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I81" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G82" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H82" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I82" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="83">
@@ -3510,58 +3510,58 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>8803</v>
+        <v>2168</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G84" t="n">
-        <v>361000</v>
+        <v>4445105000</v>
       </c>
       <c r="H84" t="n">
-        <v>3610</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3569,27 +3569,27 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G85" t="n">
-        <v>20578848000</v>
+        <v>361000</v>
       </c>
       <c r="H85" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3609,10 +3609,10 @@
         <v>4062075</v>
       </c>
       <c r="G86" t="n">
-        <v>8729143000</v>
+        <v>20578848000</v>
       </c>
       <c r="H86" t="n">
-        <v>2148.936934940886</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I86" t="n">
         <v>5.2</v>
@@ -3621,160 +3621,160 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G87" t="n">
-        <v>5292086000</v>
+        <v>8729143000</v>
       </c>
       <c r="H87" t="n">
-        <v>2112.609181636727</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I87" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G88" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H88" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I88" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G89" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H89" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I89" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G90" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H90" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I90" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3783,172 +3783,172 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G91" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H91" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I91" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G92" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H92" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I92" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G93" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H93" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I93" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G94" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H94" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I94" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G95" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H95" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I95" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="96">
@@ -3991,234 +3991,234 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4521</v>
+        <v>4042</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>100</v>
+        <v>16459200</v>
       </c>
       <c r="G97" t="n">
-        <v>353000</v>
+        <v>33451116000</v>
       </c>
       <c r="H97" t="n">
-        <v>3530</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G98" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H98" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I98" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G99" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H99" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I99" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G100" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H100" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I100" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G101" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H101" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G102" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H102" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I102" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4227,21 +4227,21 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G103" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H103" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I103" t="n">
         <v>5.02</v>
@@ -4250,197 +4250,197 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G104" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H104" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G105" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H105" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I105" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G106" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H106" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I106" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G107" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H107" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G108" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H108" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I108" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4453,142 +4453,142 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G109" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H109" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I109" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G110" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H110" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I110" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G111" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H111" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G112" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H112" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I112" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4597,35 +4597,35 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G113" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H113" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I113" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4634,30 +4634,30 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G114" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H114" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I114" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4293</v>
+        <v>4631</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4679,355 +4679,355 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>20896886</v>
+        <v>6563759</v>
       </c>
       <c r="G115" t="n">
-        <v>9376038000</v>
+        <v>16844475000</v>
       </c>
       <c r="H115" t="n">
-        <v>448.6811097117532</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I115" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G116" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H116" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G117" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H117" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I117" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G118" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H118" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I118" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G119" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H119" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I119" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G120" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H120" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I120" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G121" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H121" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I121" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G122" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H122" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G123" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H123" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I123" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5947</v>
+        <v>5844</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>7446200</v>
+        <v>4998800</v>
       </c>
       <c r="G124" t="n">
-        <v>21182239000</v>
+        <v>24949147000</v>
       </c>
       <c r="H124" t="n">
-        <v>2844.704547285864</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I124" t="n">
-        <v>4.96</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -5049,456 +5049,456 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G125" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H125" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I125" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>8303</v>
+        <v>5186</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>20000000</v>
+        <v>1536900</v>
       </c>
       <c r="G126" t="n">
-        <v>56014500000</v>
+        <v>4758738000</v>
       </c>
       <c r="H126" t="n">
-        <v>2800.725</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I126" t="n">
-        <v>9.75</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G127" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I127" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5451</v>
+        <v>2812</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1752800</v>
-      </c>
-      <c r="G128" t="n">
-        <v>5669831000</v>
-      </c>
-      <c r="H128" t="n">
-        <v>3234.727863989046</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
-        <v>5.029999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>9072</v>
+        <v>5451</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>8377400</v>
+        <v>1752800</v>
       </c>
       <c r="G129" t="n">
-        <v>13394541000</v>
+        <v>5669831000</v>
       </c>
       <c r="H129" t="n">
-        <v>1598.889989734285</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I129" t="n">
-        <v>12.74</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5194</v>
+        <v>9072</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1068798</v>
+        <v>8377400</v>
       </c>
       <c r="G130" t="n">
-        <v>997342000</v>
+        <v>13394541000</v>
       </c>
       <c r="H130" t="n">
-        <v>933.1435874692879</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I130" t="n">
-        <v>9.77</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>8871</v>
+        <v>5194</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1807700</v>
+        <v>1068798</v>
       </c>
       <c r="G131" t="n">
-        <v>3235548000</v>
+        <v>997342000</v>
       </c>
       <c r="H131" t="n">
-        <v>1789.870000553189</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I131" t="n">
-        <v>5.050000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5929</v>
+        <v>8871</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>11571500</v>
+        <v>1807700</v>
       </c>
       <c r="G132" t="n">
-        <v>15114770000</v>
+        <v>3235548000</v>
       </c>
       <c r="H132" t="n">
-        <v>1306.206628354146</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I132" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8140</v>
+        <v>5929</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1322800</v>
+        <v>11571500</v>
       </c>
       <c r="G133" t="n">
-        <v>4536170000</v>
+        <v>15114770000</v>
       </c>
       <c r="H133" t="n">
-        <v>3429.218324765649</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I133" t="n">
-        <v>5.29</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1878</v>
+        <v>8140</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3452100</v>
+        <v>1322800</v>
       </c>
       <c r="G134" t="n">
-        <v>44793976000</v>
+        <v>4536170000</v>
       </c>
       <c r="H134" t="n">
-        <v>12975.86280814577</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I134" t="n">
-        <v>5.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>533500</v>
+        <v>3452100</v>
       </c>
       <c r="G135" t="n">
-        <v>2009924000</v>
+        <v>44793976000</v>
       </c>
       <c r="H135" t="n">
-        <v>3767.430178069353</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I135" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3593</v>
+        <v>1882</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1637060</v>
+        <v>533500</v>
       </c>
       <c r="G136" t="n">
-        <v>5502657000</v>
+        <v>2009924000</v>
       </c>
       <c r="H136" t="n">
-        <v>3361.304411567078</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I136" t="n">
-        <v>6.48</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>7157</v>
+        <v>3593</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>4536300</v>
+        <v>1637060</v>
       </c>
       <c r="G137" t="n">
-        <v>4025006000</v>
+        <v>5502657000</v>
       </c>
       <c r="H137" t="n">
-        <v>887.288318673809</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I137" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="138">
@@ -5541,128 +5541,128 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>7350</v>
+        <v>7157</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+        <v>4536300</v>
+      </c>
+      <c r="G139" t="n">
+        <v>4025006000</v>
+      </c>
+      <c r="H139" t="n">
+        <v>887.288318673809</v>
+      </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3549</v>
+        <v>7350</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1735200</v>
-      </c>
-      <c r="G140" t="n">
-        <v>11532479000</v>
-      </c>
-      <c r="H140" t="n">
-        <v>6646.195827570309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6770</v>
+        <v>3549</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>11259700</v>
+        <v>1735200</v>
       </c>
       <c r="G141" t="n">
-        <v>14161429000</v>
+        <v>11532479000</v>
       </c>
       <c r="H141" t="n">
-        <v>1257.709264012363</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I141" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3391</v>
+        <v>6770</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5670,101 +5670,101 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>6354522</v>
+        <v>11259700</v>
       </c>
       <c r="G142" t="n">
-        <v>28876223000</v>
+        <v>14161429000</v>
       </c>
       <c r="H142" t="n">
-        <v>4544.200649553184</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I142" t="n">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1951</v>
+        <v>3391</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>5561200</v>
+        <v>6354522</v>
       </c>
       <c r="G143" t="n">
-        <v>12623472000</v>
+        <v>28876223000</v>
       </c>
       <c r="H143" t="n">
-        <v>2269.918722577861</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I143" t="n">
-        <v>5.06</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QNRY.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3085</v>
+        <v>1951</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1756300</v>
+        <v>5561200</v>
       </c>
       <c r="G144" t="n">
-        <v>4694343000</v>
+        <v>12623472000</v>
       </c>
       <c r="H144" t="n">
-        <v>2672.859420372374</v>
+        <v>2269.918722577861</v>
       </c>
       <c r="I144" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QJNN.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5773,131 +5773,135 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>9842</v>
+        <v>3085</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>2082200</v>
+        <v>1756300</v>
       </c>
       <c r="G145" t="n">
-        <v>3059101000</v>
+        <v>4694343000</v>
       </c>
       <c r="H145" t="n">
-        <v>1469.167707232735</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I145" t="n">
-        <v>5.029999999999999</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QI52.zip</t>
+          <t>S100QJNN.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
+          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>9672</v>
+        <v>9842</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2410900</v>
+        <v>2082200</v>
       </c>
       <c r="G146" t="n">
-        <v>9382590000</v>
+        <v>3059101000</v>
       </c>
       <c r="H146" t="n">
-        <v>3891.73752540545</v>
+        <v>1469.167707232735</v>
       </c>
       <c r="I146" t="n">
-        <v>8.380000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QGUZ.zip</t>
+          <t>S100QI52.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3558</v>
+        <v>9672</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1214200</v>
+        <v>2410900</v>
       </c>
       <c r="G147" t="n">
-        <v>1538785000</v>
+        <v>9382590000</v>
       </c>
       <c r="H147" t="n">
-        <v>1267.324164058639</v>
+        <v>3891.73752540545</v>
       </c>
       <c r="I147" t="n">
-        <v>10.57</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QGUZ.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2329</v>
+        <v>3558</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
+        <v>1214200</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1538785000</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1267.324164058639</v>
+      </c>
       <c r="I148" t="n">
-        <v>9.550000000000001</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="149">
@@ -5936,111 +5940,144 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QDGW.zip</t>
+          <t>S100QF0T.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4324</v>
+        <v>2329</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>13655200</v>
-      </c>
-      <c r="G150" t="n">
-        <v>56753467000</v>
-      </c>
-      <c r="H150" t="n">
-        <v>4156.179843576074</v>
-      </c>
+        <v>4463000</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>5.050000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QBB7.zip</t>
+          <t>S100QDGW.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3608</v>
+        <v>4324</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>4569000</v>
+        <v>13655200</v>
       </c>
       <c r="G151" t="n">
-        <v>2005111000</v>
+        <v>56753467000</v>
       </c>
       <c r="H151" t="n">
-        <v>438.851170934559</v>
+        <v>4156.179843576074</v>
       </c>
       <c r="I151" t="n">
-        <v>5.07</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
+          <t>S100QBB7.zip</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>3608</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>4569000</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2005111000</v>
+      </c>
+      <c r="H152" t="n">
+        <v>438.851170934559</v>
+      </c>
+      <c r="I152" t="n">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
           <t>S100Q8UN.zip</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E35393-000_2023-02-13_01_2023-02-20.csv</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="D152" t="n">
+      <c r="D153" t="n">
         <v>6804</v>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="F152" t="n">
+      <c r="F153" t="n">
         <v>3315900</v>
       </c>
-      <c r="G152" t="n">
+      <c r="G153" t="n">
         <v>4322098000</v>
       </c>
-      <c r="H152" t="n">
+      <c r="H153" t="n">
         <v>1303.446424801713</v>
       </c>
-      <c r="I152" t="n">
+      <c r="I153" t="n">
         <v>5.26</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,334 +478,334 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G2" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H2" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G3" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H3" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I3" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G4" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H4" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I4" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G5" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H5" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H6" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I6" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G7" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H7" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I7" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G8" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H8" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G9" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H9" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I9" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2432</v>
+        <v>2371</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>10372003</v>
       </c>
       <c r="G10" t="n">
-        <v>226000</v>
+        <v>24045569000</v>
       </c>
       <c r="H10" t="n">
-        <v>2260</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="11">
@@ -848,49 +848,49 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8570</v>
+        <v>2432</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>11014402</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>14194389000</v>
+        <v>226000</v>
       </c>
       <c r="H12" t="n">
-        <v>1288.711724885291</v>
+        <v>2260</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -899,98 +899,98 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G13" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H13" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I13" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G14" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H14" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I14" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G15" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H15" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I15" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="16">
@@ -1033,38 +1033,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G17" t="n">
-        <v>49662804000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H17" t="n">
-        <v>11879.91675437757</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I17" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="18">
@@ -1107,86 +1107,86 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4549</v>
+        <v>6856</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2546351</v>
+        <v>4180400</v>
       </c>
       <c r="G19" t="n">
-        <v>4958319000</v>
+        <v>49662804000</v>
       </c>
       <c r="H19" t="n">
-        <v>1947.225264702313</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I19" t="n">
-        <v>7.37</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G20" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H20" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H21" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1218,12 +1218,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1232,21 +1232,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H22" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1255,12 +1255,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H23" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1292,12 +1292,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H24" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1343,109 +1343,109 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H25" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G26" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H26" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I26" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G27" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H27" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I27" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1477,308 +1477,308 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G29" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H29" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I29" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5331</v>
+        <v>6104</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1481600</v>
+        <v>1297500</v>
       </c>
       <c r="G30" t="n">
-        <v>5294365000</v>
+        <v>4476090000</v>
       </c>
       <c r="H30" t="n">
-        <v>3573.410502159827</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G31" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H31" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I31" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G32" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H32" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H33" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I33" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G34" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H34" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I34" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G35" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H35" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G36" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H36" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1787,170 +1787,170 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G37" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H37" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I37" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G38" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H38" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I38" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G41" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H41" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="42">
@@ -1993,86 +1993,86 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9684</v>
+        <v>3106</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>6704059</v>
+        <v>900156</v>
       </c>
       <c r="G43" t="n">
-        <v>42054369000</v>
+        <v>4095263000</v>
       </c>
       <c r="H43" t="n">
-        <v>6272.971195510064</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I43" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G44" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H44" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H45" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2104,58 +2104,58 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4849</v>
+        <v>6332</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>5148132000</v>
+        <v>141000</v>
       </c>
       <c r="H46" t="n">
-        <v>1746.940387696806</v>
+        <v>1410</v>
       </c>
       <c r="I46" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6927</v>
+        <v>4849</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2163,175 +2163,175 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1142700</v>
+        <v>2946942</v>
       </c>
       <c r="G47" t="n">
-        <v>1023871000</v>
+        <v>5148132000</v>
       </c>
       <c r="H47" t="n">
-        <v>896.0103264198827</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I47" t="n">
-        <v>5.01</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4676</v>
+        <v>6927</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>1142700</v>
       </c>
       <c r="G48" t="n">
-        <v>242000</v>
+        <v>1023871000</v>
       </c>
       <c r="H48" t="n">
-        <v>2420</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H49" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I49" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G50" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H50" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I50" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G51" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H51" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2340,192 +2340,192 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H52" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I52" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G53" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H53" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I53" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G54" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H54" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I54" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G55" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H55" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I55" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4626</v>
+        <v>9006</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G56" t="n">
-        <v>16652257000</v>
+        <v>34824000</v>
       </c>
       <c r="H56" t="n">
-        <v>3565.648720929983</v>
+        <v>1160.8</v>
       </c>
       <c r="I56" t="n">
-        <v>8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9987</v>
+        <v>4626</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2533,101 +2533,101 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3888200</v>
+        <v>4670190</v>
       </c>
       <c r="G57" t="n">
-        <v>16086019000</v>
+        <v>16652257000</v>
       </c>
       <c r="H57" t="n">
-        <v>4137.137750115735</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>7732</v>
+        <v>9987</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>7995900</v>
+        <v>3888200</v>
       </c>
       <c r="G58" t="n">
-        <v>16678425000</v>
+        <v>16086019000</v>
       </c>
       <c r="H58" t="n">
-        <v>2085.872134468915</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I58" t="n">
-        <v>7.380000000000001</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G59" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H59" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H60" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -2659,49 +2659,49 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H61" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I61" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2710,146 +2710,146 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G62" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H62" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I62" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G63" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H63" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H64" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I64" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G65" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H65" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I65" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2858,35 +2858,35 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G66" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H66" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I66" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2895,146 +2895,146 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G67" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H67" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I67" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G68" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H68" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I68" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G69" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H69" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I69" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G70" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H70" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I70" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3043,24 +3043,24 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8141</v>
+        <v>5482</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>100</v>
+        <v>433300</v>
       </c>
       <c r="G71" t="n">
-        <v>93000</v>
+        <v>1367192000</v>
       </c>
       <c r="H71" t="n">
-        <v>930</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="72">
@@ -3103,12 +3103,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>100</v>
       </c>
       <c r="G73" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H73" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -3140,38 +3140,38 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H74" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I74" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3214,160 +3214,160 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G76" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H76" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I76" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G77" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H77" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G78" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H78" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G79" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H79" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3376,72 +3376,72 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G80" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H80" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I80" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G81" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H81" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I81" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3450,81 +3450,81 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G82" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H82" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I82" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5541</v>
+        <v>7305</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>100</v>
+        <v>309800</v>
       </c>
       <c r="G83" t="n">
-        <v>127000</v>
+        <v>1321438000</v>
       </c>
       <c r="H83" t="n">
-        <v>1270</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3532,53 +3532,53 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G84" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H84" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I84" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>8803</v>
+        <v>2168</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G85" t="n">
-        <v>361000</v>
+        <v>4445105000</v>
       </c>
       <c r="H85" t="n">
-        <v>3610</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="86">
@@ -3658,160 +3658,160 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>9882</v>
+        <v>8803</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2505000</v>
+        <v>100</v>
       </c>
       <c r="G88" t="n">
-        <v>5292086000</v>
+        <v>361000</v>
       </c>
       <c r="H88" t="n">
-        <v>2112.609181636727</v>
+        <v>3610</v>
       </c>
       <c r="I88" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G89" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H89" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I89" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G90" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H90" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I90" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G91" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H91" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I91" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3820,192 +3820,192 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G92" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H92" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I92" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G93" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H93" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I93" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G94" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H94" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I94" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G95" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H95" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I95" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3591</v>
+        <v>7278</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2846091</v>
+        <v>115400</v>
       </c>
       <c r="G96" t="n">
-        <v>6888596000</v>
+        <v>302115000</v>
       </c>
       <c r="H96" t="n">
-        <v>2420.370957920882</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I96" t="n">
-        <v>5.13</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4042</v>
+        <v>3591</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4013,249 +4013,249 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>16459200</v>
+        <v>2846091</v>
       </c>
       <c r="G97" t="n">
-        <v>33451116000</v>
+        <v>6888596000</v>
       </c>
       <c r="H97" t="n">
-        <v>2032.365850102071</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I97" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4521</v>
+        <v>4042</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>100</v>
+        <v>16459200</v>
       </c>
       <c r="G98" t="n">
-        <v>353000</v>
+        <v>33451116000</v>
       </c>
       <c r="H98" t="n">
-        <v>3530</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G99" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H99" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I99" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G100" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H100" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I100" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G101" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H101" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I101" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G102" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H102" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G103" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H103" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I103" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4264,21 +4264,21 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G104" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H104" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I104" t="n">
         <v>5.02</v>
@@ -4287,197 +4287,197 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G105" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H105" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G106" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H106" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I106" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G107" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H107" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I107" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G108" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H108" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G109" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H109" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I109" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4490,142 +4490,142 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G110" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H110" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I110" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G111" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H111" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I111" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G112" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H112" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G113" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H113" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I113" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4634,35 +4634,35 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G114" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H114" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I114" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4671,30 +4671,30 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G115" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H115" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I115" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4293</v>
+        <v>4631</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4716,355 +4716,355 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>20896886</v>
+        <v>6563759</v>
       </c>
       <c r="G116" t="n">
-        <v>9376038000</v>
+        <v>16844475000</v>
       </c>
       <c r="H116" t="n">
-        <v>448.6811097117532</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I116" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G117" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H117" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I117" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G118" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H118" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I118" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G119" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H119" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I119" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G120" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H120" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I120" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G121" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H121" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I121" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G122" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H122" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I122" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G123" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H123" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G124" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H124" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I124" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5947</v>
+        <v>5844</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>7446200</v>
+        <v>4998800</v>
       </c>
       <c r="G125" t="n">
-        <v>21182239000</v>
+        <v>24949147000</v>
       </c>
       <c r="H125" t="n">
-        <v>2844.704547285864</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I125" t="n">
-        <v>4.96</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -5086,456 +5086,456 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G126" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H126" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I126" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>8303</v>
+        <v>5186</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>20000000</v>
+        <v>1536900</v>
       </c>
       <c r="G127" t="n">
-        <v>56014500000</v>
+        <v>4758738000</v>
       </c>
       <c r="H127" t="n">
-        <v>2800.725</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I127" t="n">
-        <v>9.75</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G128" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I128" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5451</v>
+        <v>2812</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1752800</v>
-      </c>
-      <c r="G129" t="n">
-        <v>5669831000</v>
-      </c>
-      <c r="H129" t="n">
-        <v>3234.727863989046</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>5.029999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>9072</v>
+        <v>5451</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>8377400</v>
+        <v>1752800</v>
       </c>
       <c r="G130" t="n">
-        <v>13394541000</v>
+        <v>5669831000</v>
       </c>
       <c r="H130" t="n">
-        <v>1598.889989734285</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I130" t="n">
-        <v>12.74</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5194</v>
+        <v>9072</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1068798</v>
+        <v>8377400</v>
       </c>
       <c r="G131" t="n">
-        <v>997342000</v>
+        <v>13394541000</v>
       </c>
       <c r="H131" t="n">
-        <v>933.1435874692879</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I131" t="n">
-        <v>9.77</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>8871</v>
+        <v>5194</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1807700</v>
+        <v>1068798</v>
       </c>
       <c r="G132" t="n">
-        <v>3235548000</v>
+        <v>997342000</v>
       </c>
       <c r="H132" t="n">
-        <v>1789.870000553189</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I132" t="n">
-        <v>5.050000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5929</v>
+        <v>8871</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>11571500</v>
+        <v>1807700</v>
       </c>
       <c r="G133" t="n">
-        <v>15114770000</v>
+        <v>3235548000</v>
       </c>
       <c r="H133" t="n">
-        <v>1306.206628354146</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I133" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>8140</v>
+        <v>5929</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1322800</v>
+        <v>11571500</v>
       </c>
       <c r="G134" t="n">
-        <v>4536170000</v>
+        <v>15114770000</v>
       </c>
       <c r="H134" t="n">
-        <v>3429.218324765649</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I134" t="n">
-        <v>5.29</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1878</v>
+        <v>8140</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3452100</v>
+        <v>1322800</v>
       </c>
       <c r="G135" t="n">
-        <v>44793976000</v>
+        <v>4536170000</v>
       </c>
       <c r="H135" t="n">
-        <v>12975.86280814577</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I135" t="n">
-        <v>5.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>533500</v>
+        <v>3452100</v>
       </c>
       <c r="G136" t="n">
-        <v>2009924000</v>
+        <v>44793976000</v>
       </c>
       <c r="H136" t="n">
-        <v>3767.430178069353</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I136" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3593</v>
+        <v>1882</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1637060</v>
+        <v>533500</v>
       </c>
       <c r="G137" t="n">
-        <v>5502657000</v>
+        <v>2009924000</v>
       </c>
       <c r="H137" t="n">
-        <v>3361.304411567078</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I137" t="n">
-        <v>6.48</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1861</v>
+        <v>3593</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3102784</v>
+        <v>1637060</v>
       </c>
       <c r="G138" t="n">
-        <v>8614573000</v>
+        <v>5502657000</v>
       </c>
       <c r="H138" t="n">
-        <v>2776.401128792723</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I138" t="n">
-        <v>7.07</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="139">
@@ -5578,128 +5578,128 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>7350</v>
+        <v>1861</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+        <v>3102784</v>
+      </c>
+      <c r="G140" t="n">
+        <v>8614573000</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2776.401128792723</v>
+      </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3549</v>
+        <v>7350</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1735200</v>
-      </c>
-      <c r="G141" t="n">
-        <v>11532479000</v>
-      </c>
-      <c r="H141" t="n">
-        <v>6646.195827570309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6770</v>
+        <v>3549</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>11259700</v>
+        <v>1735200</v>
       </c>
       <c r="G142" t="n">
-        <v>14161429000</v>
+        <v>11532479000</v>
       </c>
       <c r="H142" t="n">
-        <v>1257.709264012363</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I142" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3391</v>
+        <v>6770</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5707,101 +5707,101 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>6354522</v>
+        <v>11259700</v>
       </c>
       <c r="G143" t="n">
-        <v>28876223000</v>
+        <v>14161429000</v>
       </c>
       <c r="H143" t="n">
-        <v>4544.200649553184</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I143" t="n">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1951</v>
+        <v>3391</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>5561200</v>
+        <v>6354522</v>
       </c>
       <c r="G144" t="n">
-        <v>12623472000</v>
+        <v>28876223000</v>
       </c>
       <c r="H144" t="n">
-        <v>2269.918722577861</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I144" t="n">
-        <v>5.06</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QNRY.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3085</v>
+        <v>1951</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1756300</v>
+        <v>5561200</v>
       </c>
       <c r="G145" t="n">
-        <v>4694343000</v>
+        <v>12623472000</v>
       </c>
       <c r="H145" t="n">
-        <v>2672.859420372374</v>
+        <v>2269.918722577861</v>
       </c>
       <c r="I145" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QJNN.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5810,131 +5810,135 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>9842</v>
+        <v>3085</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2082200</v>
+        <v>1756300</v>
       </c>
       <c r="G146" t="n">
-        <v>3059101000</v>
+        <v>4694343000</v>
       </c>
       <c r="H146" t="n">
-        <v>1469.167707232735</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I146" t="n">
-        <v>5.029999999999999</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QI52.zip</t>
+          <t>S100QJNN.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
+          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>9672</v>
+        <v>9842</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2410900</v>
+        <v>2082200</v>
       </c>
       <c r="G147" t="n">
-        <v>9382590000</v>
+        <v>3059101000</v>
       </c>
       <c r="H147" t="n">
-        <v>3891.73752540545</v>
+        <v>1469.167707232735</v>
       </c>
       <c r="I147" t="n">
-        <v>8.380000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100QGUZ.zip</t>
+          <t>S100QI52.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3558</v>
+        <v>9672</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1214200</v>
+        <v>2410900</v>
       </c>
       <c r="G148" t="n">
-        <v>1538785000</v>
+        <v>9382590000</v>
       </c>
       <c r="H148" t="n">
-        <v>1267.324164058639</v>
+        <v>3891.73752540545</v>
       </c>
       <c r="I148" t="n">
-        <v>10.57</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QF8K.zip</t>
+          <t>S100QGUZ.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2329</v>
+        <v>3558</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
+        <v>1214200</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1538785000</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1267.324164058639</v>
+      </c>
       <c r="I149" t="n">
-        <v>9.550000000000001</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="150">
@@ -5973,111 +5977,144 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QDGW.zip</t>
+          <t>S100QF8K.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4324</v>
+        <v>2329</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>13655200</v>
-      </c>
-      <c r="G151" t="n">
-        <v>56753467000</v>
-      </c>
-      <c r="H151" t="n">
-        <v>4156.179843576074</v>
-      </c>
+        <v>4463000</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>5.050000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QBB7.zip</t>
+          <t>S100QDGW.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3608</v>
+        <v>4324</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>4569000</v>
+        <v>13655200</v>
       </c>
       <c r="G152" t="n">
-        <v>2005111000</v>
+        <v>56753467000</v>
       </c>
       <c r="H152" t="n">
-        <v>438.851170934559</v>
+        <v>4156.179843576074</v>
       </c>
       <c r="I152" t="n">
-        <v>5.07</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>S100QBB7.zip</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>3608</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>4569000</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2005111000</v>
+      </c>
+      <c r="H153" t="n">
+        <v>438.851170934559</v>
+      </c>
+      <c r="I153" t="n">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>S100Q8UN.zip</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E35393-000_2023-02-13_01_2023-02-20.csv</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="D153" t="n">
+      <c r="D154" t="n">
         <v>6804</v>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="F153" t="n">
+      <c r="F154" t="n">
         <v>3315900</v>
       </c>
-      <c r="G153" t="n">
+      <c r="G154" t="n">
         <v>4322098000</v>
       </c>
-      <c r="H153" t="n">
+      <c r="H154" t="n">
         <v>1303.446424801713</v>
       </c>
-      <c r="I153" t="n">
+      <c r="I154" t="n">
         <v>5.26</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -478,371 +478,371 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7745</v>
+        <v>6675</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1458700</v>
+        <v>314400</v>
       </c>
       <c r="G2" t="n">
-        <v>3040190000</v>
+        <v>1717778000</v>
       </c>
       <c r="H2" t="n">
-        <v>2084.177692465894</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I2" t="n">
-        <v>5.24</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G3" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H3" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G4" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H4" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I4" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G5" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H5" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I5" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G6" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H6" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H7" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I7" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G8" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H8" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I8" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G9" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H9" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G10" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H10" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I10" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G11" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H11" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I11" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="12">
@@ -885,49 +885,49 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G13" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H13" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -936,98 +936,98 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G14" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H14" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I14" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G15" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H15" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I15" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G16" t="n">
-        <v>268179335000</v>
+        <v>1970276000</v>
       </c>
       <c r="H16" t="n">
-        <v>16430.4430802409</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I16" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="17">
@@ -1070,38 +1070,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G18" t="n">
-        <v>1831405000</v>
+        <v>268179335000</v>
       </c>
       <c r="H18" t="n">
-        <v>3321.975331035734</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I18" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="19">
@@ -1144,12 +1144,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1158,72 +1158,72 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G20" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H20" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I20" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G21" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H21" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1232,21 +1232,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H22" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1255,12 +1255,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H23" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1292,12 +1292,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H24" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H25" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1366,12 +1366,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1380,98 +1380,98 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H26" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G27" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H27" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I27" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G28" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H28" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I28" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="29">
@@ -1514,308 +1514,308 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G30" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H30" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I30" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5331</v>
+        <v>6104</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1481600</v>
+        <v>1297500</v>
       </c>
       <c r="G31" t="n">
-        <v>5294365000</v>
+        <v>4476090000</v>
       </c>
       <c r="H31" t="n">
-        <v>3573.410502159827</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G32" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H32" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I32" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G33" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H33" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H34" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I34" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G35" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H35" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I35" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G36" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H36" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G37" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H37" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1824,170 +1824,170 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G38" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H38" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I38" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G39" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H39" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I39" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G42" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H42" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I42" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="43">
@@ -2030,12 +2030,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2044,72 +2044,72 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G44" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H44" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I44" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G45" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H45" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2118,21 +2118,21 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H46" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2141,58 +2141,58 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4849</v>
+        <v>6332</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>5148132000</v>
+        <v>141000</v>
       </c>
       <c r="H47" t="n">
-        <v>1746.940387696806</v>
+        <v>1410</v>
       </c>
       <c r="I47" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6927</v>
+        <v>4849</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2200,175 +2200,175 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1142700</v>
+        <v>2946942</v>
       </c>
       <c r="G48" t="n">
-        <v>1023871000</v>
+        <v>5148132000</v>
       </c>
       <c r="H48" t="n">
-        <v>896.0103264198827</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I48" t="n">
-        <v>5.01</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4676</v>
+        <v>6927</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>1142700</v>
       </c>
       <c r="G49" t="n">
-        <v>242000</v>
+        <v>1023871000</v>
       </c>
       <c r="H49" t="n">
-        <v>2420</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H50" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G51" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H51" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I51" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G52" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H52" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2377,172 +2377,172 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H53" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I53" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G54" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H54" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I54" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G55" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H55" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I55" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G56" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H56" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I56" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4626</v>
+        <v>9006</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G57" t="n">
-        <v>16652257000</v>
+        <v>34824000</v>
       </c>
       <c r="H57" t="n">
-        <v>3565.648720929983</v>
+        <v>1160.8</v>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="58">
@@ -2585,12 +2585,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2599,72 +2599,72 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G59" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H59" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I59" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G60" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H60" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2673,21 +2673,21 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H61" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -2696,49 +2696,49 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H62" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I62" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2747,146 +2747,146 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G63" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H63" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I63" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G64" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H64" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H65" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I65" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G66" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H66" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I66" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2895,35 +2895,35 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G67" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H67" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I67" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2932,192 +2932,192 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G68" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H68" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I68" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G69" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H69" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I69" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G70" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H70" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I70" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G71" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H71" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I71" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G72" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H72" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I72" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8141</v>
+        <v>4272</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3125,27 +3125,27 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G73" t="n">
-        <v>93000</v>
+        <v>29860350000</v>
       </c>
       <c r="H73" t="n">
-        <v>930</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3154,21 +3154,21 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H74" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -3177,44 +3177,44 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4205</v>
+        <v>6145</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G75" t="n">
-        <v>24829312000</v>
+        <v>171000</v>
       </c>
       <c r="H75" t="n">
-        <v>1721.078563209627</v>
+        <v>1710</v>
       </c>
       <c r="I75" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3569</v>
+        <v>4205</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3236,175 +3236,175 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4271704</v>
+        <v>14426600</v>
       </c>
       <c r="G76" t="n">
-        <v>5808044000</v>
+        <v>24829312000</v>
       </c>
       <c r="H76" t="n">
-        <v>1359.655069733296</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I76" t="n">
-        <v>6.279999999999999</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G77" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H77" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I77" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G78" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H78" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G79" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H79" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G80" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H80" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3413,72 +3413,72 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G81" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H81" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I81" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G82" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H82" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I82" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3487,81 +3487,81 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G83" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H83" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I83" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5541</v>
+        <v>7305</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>100</v>
+        <v>309800</v>
       </c>
       <c r="G84" t="n">
-        <v>127000</v>
+        <v>1321438000</v>
       </c>
       <c r="H84" t="n">
-        <v>1270</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3569,27 +3569,27 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G85" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H85" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I85" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3598,44 +3598,44 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G86" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H86" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3643,36 +3643,36 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G87" t="n">
-        <v>8729143000</v>
+        <v>361000</v>
       </c>
       <c r="H87" t="n">
-        <v>2148.936934940886</v>
+        <v>3610</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3680,175 +3680,175 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G88" t="n">
-        <v>361000</v>
+        <v>20578848000</v>
       </c>
       <c r="H88" t="n">
-        <v>3610</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G89" t="n">
-        <v>5292086000</v>
+        <v>8729143000</v>
       </c>
       <c r="H89" t="n">
-        <v>2112.609181636727</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I89" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G90" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H90" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I90" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G91" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H91" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I91" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G92" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H92" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I92" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3857,172 +3857,172 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G93" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H93" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I93" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G94" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H94" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I94" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G95" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H95" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I95" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G96" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H96" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I96" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3591</v>
+        <v>7278</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2846091</v>
+        <v>115400</v>
       </c>
       <c r="G97" t="n">
-        <v>6888596000</v>
+        <v>302115000</v>
       </c>
       <c r="H97" t="n">
-        <v>2420.370957920882</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I97" t="n">
-        <v>5.13</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="98">
@@ -4065,234 +4065,234 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G99" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H99" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G100" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H100" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I100" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G101" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H101" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I101" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G102" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H102" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I102" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G103" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H103" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G104" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H104" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I104" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4301,21 +4301,21 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G105" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H105" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I105" t="n">
         <v>5.02</v>
@@ -4324,197 +4324,197 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G106" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H106" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G107" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H107" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I107" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G108" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H108" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I108" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G109" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H109" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H110" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I110" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4527,142 +4527,142 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G111" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H111" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I111" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G112" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H112" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I112" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G113" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H113" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G114" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H114" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I114" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4671,35 +4671,35 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G115" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H115" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I115" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4708,24 +4708,24 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G116" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H116" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I116" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="117">
@@ -4768,334 +4768,334 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5449</v>
+        <v>4631</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>2114100</v>
+        <v>6563759</v>
       </c>
       <c r="G118" t="n">
-        <v>3695597000</v>
+        <v>16844475000</v>
       </c>
       <c r="H118" t="n">
-        <v>1748.071046781136</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G119" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H119" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I119" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G120" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H120" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I120" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G121" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H121" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I121" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G122" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H122" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I122" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G123" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H123" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I123" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G124" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H124" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G125" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H125" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I125" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5947</v>
+        <v>5844</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>7446200</v>
+        <v>4998800</v>
       </c>
       <c r="G126" t="n">
-        <v>21182239000</v>
+        <v>24949147000</v>
       </c>
       <c r="H126" t="n">
-        <v>2844.704547285864</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I126" t="n">
-        <v>4.96</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="127">
@@ -5138,452 +5138,452 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G128" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H128" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I128" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G129" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I129" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5451</v>
+        <v>2812</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1752800</v>
-      </c>
-      <c r="G130" t="n">
-        <v>5669831000</v>
-      </c>
-      <c r="H130" t="n">
-        <v>3234.727863989046</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>5.029999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>9072</v>
+        <v>5451</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>8377400</v>
+        <v>1752800</v>
       </c>
       <c r="G131" t="n">
-        <v>13394541000</v>
+        <v>5669831000</v>
       </c>
       <c r="H131" t="n">
-        <v>1598.889989734285</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I131" t="n">
-        <v>12.74</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5194</v>
+        <v>9072</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1068798</v>
+        <v>8377400</v>
       </c>
       <c r="G132" t="n">
-        <v>997342000</v>
+        <v>13394541000</v>
       </c>
       <c r="H132" t="n">
-        <v>933.1435874692879</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I132" t="n">
-        <v>9.77</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8871</v>
+        <v>5194</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1807700</v>
+        <v>1068798</v>
       </c>
       <c r="G133" t="n">
-        <v>3235548000</v>
+        <v>997342000</v>
       </c>
       <c r="H133" t="n">
-        <v>1789.870000553189</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I133" t="n">
-        <v>5.050000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5929</v>
+        <v>8871</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>11571500</v>
+        <v>1807700</v>
       </c>
       <c r="G134" t="n">
-        <v>15114770000</v>
+        <v>3235548000</v>
       </c>
       <c r="H134" t="n">
-        <v>1306.206628354146</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I134" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>8140</v>
+        <v>5929</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1322800</v>
+        <v>11571500</v>
       </c>
       <c r="G135" t="n">
-        <v>4536170000</v>
+        <v>15114770000</v>
       </c>
       <c r="H135" t="n">
-        <v>3429.218324765649</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I135" t="n">
-        <v>5.29</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1878</v>
+        <v>8140</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3452100</v>
+        <v>1322800</v>
       </c>
       <c r="G136" t="n">
-        <v>44793976000</v>
+        <v>4536170000</v>
       </c>
       <c r="H136" t="n">
-        <v>12975.86280814577</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I136" t="n">
-        <v>5.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>533500</v>
+        <v>3452100</v>
       </c>
       <c r="G137" t="n">
-        <v>2009924000</v>
+        <v>44793976000</v>
       </c>
       <c r="H137" t="n">
-        <v>3767.430178069353</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I137" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3593</v>
+        <v>1882</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1637060</v>
+        <v>533500</v>
       </c>
       <c r="G138" t="n">
-        <v>5502657000</v>
+        <v>2009924000</v>
       </c>
       <c r="H138" t="n">
-        <v>3361.304411567078</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I138" t="n">
-        <v>6.48</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>7157</v>
+        <v>3593</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>4536300</v>
+        <v>1637060</v>
       </c>
       <c r="G139" t="n">
-        <v>4025006000</v>
+        <v>5502657000</v>
       </c>
       <c r="H139" t="n">
-        <v>887.288318673809</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I139" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1861</v>
+        <v>7157</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5600,143 +5600,143 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3102784</v>
+        <v>4536300</v>
       </c>
       <c r="G140" t="n">
-        <v>8614573000</v>
+        <v>4025006000</v>
       </c>
       <c r="H140" t="n">
-        <v>2776.401128792723</v>
+        <v>887.288318673809</v>
       </c>
       <c r="I140" t="n">
-        <v>7.07</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7350</v>
+        <v>1861</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
+        <v>3102784</v>
+      </c>
+      <c r="G141" t="n">
+        <v>8614573000</v>
+      </c>
+      <c r="H141" t="n">
+        <v>2776.401128792723</v>
+      </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3549</v>
+        <v>7350</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1735200</v>
-      </c>
-      <c r="G142" t="n">
-        <v>11532479000</v>
-      </c>
-      <c r="H142" t="n">
-        <v>6646.195827570309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6770</v>
+        <v>3549</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>11259700</v>
+        <v>1735200</v>
       </c>
       <c r="G143" t="n">
-        <v>14161429000</v>
+        <v>11532479000</v>
       </c>
       <c r="H143" t="n">
-        <v>1257.709264012363</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I143" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3391</v>
+        <v>6770</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5744,101 +5744,101 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>6354522</v>
+        <v>11259700</v>
       </c>
       <c r="G144" t="n">
-        <v>28876223000</v>
+        <v>14161429000</v>
       </c>
       <c r="H144" t="n">
-        <v>4544.200649553184</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I144" t="n">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1951</v>
+        <v>3391</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>5561200</v>
+        <v>6354522</v>
       </c>
       <c r="G145" t="n">
-        <v>12623472000</v>
+        <v>28876223000</v>
       </c>
       <c r="H145" t="n">
-        <v>2269.918722577861</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I145" t="n">
-        <v>5.06</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QNRY.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3085</v>
+        <v>1951</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1756300</v>
+        <v>5561200</v>
       </c>
       <c r="G146" t="n">
-        <v>4694343000</v>
+        <v>12623472000</v>
       </c>
       <c r="H146" t="n">
-        <v>2672.859420372374</v>
+        <v>2269.918722577861</v>
       </c>
       <c r="I146" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QJNN.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5847,131 +5847,135 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>9842</v>
+        <v>3085</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2082200</v>
+        <v>1756300</v>
       </c>
       <c r="G147" t="n">
-        <v>3059101000</v>
+        <v>4694343000</v>
       </c>
       <c r="H147" t="n">
-        <v>1469.167707232735</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I147" t="n">
-        <v>5.029999999999999</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100QI52.zip</t>
+          <t>S100QJNN.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
+          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>9672</v>
+        <v>9842</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2410900</v>
+        <v>2082200</v>
       </c>
       <c r="G148" t="n">
-        <v>9382590000</v>
+        <v>3059101000</v>
       </c>
       <c r="H148" t="n">
-        <v>3891.73752540545</v>
+        <v>1469.167707232735</v>
       </c>
       <c r="I148" t="n">
-        <v>8.380000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QGUZ.zip</t>
+          <t>S100QI52.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3558</v>
+        <v>9672</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1214200</v>
+        <v>2410900</v>
       </c>
       <c r="G149" t="n">
-        <v>1538785000</v>
+        <v>9382590000</v>
       </c>
       <c r="H149" t="n">
-        <v>1267.324164058639</v>
+        <v>3891.73752540545</v>
       </c>
       <c r="I149" t="n">
-        <v>10.57</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QGUZ.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2329</v>
+        <v>3558</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+        <v>1214200</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1538785000</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1267.324164058639</v>
+      </c>
       <c r="I150" t="n">
-        <v>9.550000000000001</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="151">
@@ -6010,112 +6014,108 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QDGW.zip</t>
+          <t>S100QF0T.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4324</v>
+        <v>2329</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>13655200</v>
-      </c>
-      <c r="G152" t="n">
-        <v>56753467000</v>
-      </c>
-      <c r="H152" t="n">
-        <v>4156.179843576074</v>
-      </c>
+        <v>4463000</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>5.050000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QBB7.zip</t>
+          <t>S100QDGW.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3608</v>
+        <v>4324</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>4569000</v>
+        <v>13655200</v>
       </c>
       <c r="G153" t="n">
-        <v>2005111000</v>
+        <v>56753467000</v>
       </c>
       <c r="H153" t="n">
-        <v>438.851170934559</v>
+        <v>4156.179843576074</v>
       </c>
       <c r="I153" t="n">
-        <v>5.07</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100Q8UN.zip</t>
+          <t>S100QBB7.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-02-13_01_2023-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>6804</v>
+        <v>3608</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>3315900</v>
+        <v>4569000</v>
       </c>
       <c r="G154" t="n">
-        <v>4322098000</v>
+        <v>2005111000</v>
       </c>
       <c r="H154" t="n">
-        <v>1303.446424801713</v>
+        <v>438.851170934559</v>
       </c>
       <c r="I154" t="n">
-        <v>5.26</v>
+        <v>5.07</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -1033,12 +1033,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1058,10 +1058,10 @@
         <v>16322100</v>
       </c>
       <c r="G17" t="n">
-        <v>268179335457000</v>
+        <v>268179335000</v>
       </c>
       <c r="H17" t="n">
-        <v>16430443.10823975</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I17" t="n">
         <v>5.01</v>
@@ -1070,12 +1070,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1095,10 +1095,10 @@
         <v>16322100</v>
       </c>
       <c r="G18" t="n">
-        <v>268179335000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H18" t="n">
-        <v>16430.4430802409</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I18" t="n">
         <v>5.01</v>
@@ -1107,21 +1107,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1129,36 +1129,36 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G19" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H19" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I19" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G20" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H20" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I20" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="21">
@@ -1477,12 +1477,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1514,12 +1514,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2548,21 +2548,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9987</v>
+        <v>4626</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2570,36 +2570,36 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3888200</v>
+        <v>4670190</v>
       </c>
       <c r="G58" t="n">
-        <v>16086019000</v>
+        <v>16652257000</v>
       </c>
       <c r="H58" t="n">
-        <v>4137.137750115735</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4626</v>
+        <v>9987</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2607,16 +2607,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4670190</v>
+        <v>3888200</v>
       </c>
       <c r="G59" t="n">
-        <v>16652257000</v>
+        <v>16086019000</v>
       </c>
       <c r="H59" t="n">
-        <v>3565.648720929983</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -3621,21 +3621,21 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3643,27 +3643,27 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G87" t="n">
-        <v>361000</v>
+        <v>20578848000</v>
       </c>
       <c r="H87" t="n">
-        <v>3610</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3683,10 +3683,10 @@
         <v>4062075</v>
       </c>
       <c r="G88" t="n">
-        <v>20578848000</v>
+        <v>8729143000</v>
       </c>
       <c r="H88" t="n">
-        <v>5066.092575838703</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I88" t="n">
         <v>5.2</v>
@@ -3695,21 +3695,21 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3717,16 +3717,16 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G89" t="n">
-        <v>8729143000</v>
+        <v>361000</v>
       </c>
       <c r="H89" t="n">
-        <v>2148.936934940886</v>
+        <v>3610</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4731,7 +4731,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4293</v>
+        <v>4631</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4753,22 +4753,22 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>20896886</v>
+        <v>6563759</v>
       </c>
       <c r="G117" t="n">
-        <v>9376038000</v>
+        <v>16844475000</v>
       </c>
       <c r="H117" t="n">
-        <v>448.6811097117532</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I117" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4631</v>
+        <v>4293</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>6563759</v>
+        <v>20896886</v>
       </c>
       <c r="G118" t="n">
-        <v>16844475000</v>
+        <v>9376038000</v>
       </c>
       <c r="H118" t="n">
-        <v>2566.284807227078</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I118" t="n">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="119">
@@ -5981,12 +5981,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QF8K.zip</t>
+          <t>S100QF0T.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6014,12 +6014,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QF8K.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,391 +515,391 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7745</v>
+        <v>3549</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1458700</v>
+        <v>13408159</v>
       </c>
       <c r="G3" t="n">
-        <v>3040190000</v>
+        <v>40855887000</v>
       </c>
       <c r="H3" t="n">
-        <v>2084.177692465894</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I3" t="n">
-        <v>5.24</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G4" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H4" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G5" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H5" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I5" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G6" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H6" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I6" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G7" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H7" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H8" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I8" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G9" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H9" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I9" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G10" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H10" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G11" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H11" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I11" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2432</v>
+        <v>2371</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>10372003</v>
       </c>
       <c r="G12" t="n">
-        <v>226000</v>
+        <v>24045569000</v>
       </c>
       <c r="H12" t="n">
-        <v>2260</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7378</v>
+        <v>2432</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -907,64 +907,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>500400</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>698873000</v>
+        <v>226000</v>
       </c>
       <c r="H13" t="n">
-        <v>1396.628697042366</v>
+        <v>2260</v>
       </c>
       <c r="I13" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G14" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H14" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,109 +973,109 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G15" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H15" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I15" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G16" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H16" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I16" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G17" t="n">
-        <v>268179335000</v>
+        <v>1970276000</v>
       </c>
       <c r="H17" t="n">
-        <v>16430.4430802409</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I17" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1095,10 +1095,10 @@
         <v>16322100</v>
       </c>
       <c r="G18" t="n">
-        <v>268179335457000</v>
+        <v>268179335000</v>
       </c>
       <c r="H18" t="n">
-        <v>16430443.10823975</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I18" t="n">
         <v>5.01</v>
@@ -1107,38 +1107,38 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G19" t="n">
-        <v>1831405000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H19" t="n">
-        <v>3321.975331035734</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I19" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="20">
@@ -1181,12 +1181,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1195,72 +1195,72 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G21" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H21" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I21" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G22" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H22" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H23" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1292,12 +1292,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H24" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H25" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1366,12 +1366,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H26" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1403,12 +1403,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1417,109 +1417,109 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H27" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I27" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G28" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H28" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I28" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G29" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H29" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I29" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1551,308 +1551,308 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G31" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H31" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I31" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5331</v>
+        <v>6104</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1481600</v>
+        <v>1297500</v>
       </c>
       <c r="G32" t="n">
-        <v>5294365000</v>
+        <v>4476090000</v>
       </c>
       <c r="H32" t="n">
-        <v>3573.410502159827</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G33" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H33" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I33" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G34" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H34" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H35" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I35" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G36" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H36" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I36" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G37" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H37" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G38" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H38" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1861,170 +1861,170 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G39" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H39" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I39" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G40" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H40" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I40" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G43" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H43" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="44">
@@ -2067,86 +2067,86 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9684</v>
+        <v>3106</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6704059</v>
+        <v>900156</v>
       </c>
       <c r="G45" t="n">
-        <v>42054369000</v>
+        <v>4095263000</v>
       </c>
       <c r="H45" t="n">
-        <v>6272.971195510064</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I45" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G46" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H46" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2155,21 +2155,21 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H47" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2178,58 +2178,58 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4849</v>
+        <v>6332</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>5148132000</v>
+        <v>141000</v>
       </c>
       <c r="H48" t="n">
-        <v>1746.940387696806</v>
+        <v>1410</v>
       </c>
       <c r="I48" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6927</v>
+        <v>4849</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2237,175 +2237,175 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1142700</v>
+        <v>2946942</v>
       </c>
       <c r="G49" t="n">
-        <v>1023871000</v>
+        <v>5148132000</v>
       </c>
       <c r="H49" t="n">
-        <v>896.0103264198827</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I49" t="n">
-        <v>5.01</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4676</v>
+        <v>6927</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>1142700</v>
       </c>
       <c r="G50" t="n">
-        <v>242000</v>
+        <v>1023871000</v>
       </c>
       <c r="H50" t="n">
-        <v>2420</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H51" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G52" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H52" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I52" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G53" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H53" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2414,172 +2414,172 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G54" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H54" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I54" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G55" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H55" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I55" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G56" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H56" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I56" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G57" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H57" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I57" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4626</v>
+        <v>9006</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G58" t="n">
-        <v>16652257000</v>
+        <v>34824000</v>
       </c>
       <c r="H58" t="n">
-        <v>3565.648720929983</v>
+        <v>1160.8</v>
       </c>
       <c r="I58" t="n">
-        <v>8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="59">
@@ -2622,12 +2622,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2636,72 +2636,72 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G60" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H60" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I60" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G61" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H61" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H62" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -2733,49 +2733,49 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H63" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I63" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2784,146 +2784,146 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G64" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H64" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I64" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G65" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H65" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H66" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I66" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G67" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H67" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I67" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2932,35 +2932,35 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G68" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H68" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I68" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2969,172 +2969,172 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G69" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H69" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I69" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G70" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H70" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I70" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G71" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H71" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I71" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G72" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H72" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I72" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G73" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H73" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I73" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="74">
@@ -3177,81 +3177,81 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6145</v>
+        <v>4272</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G75" t="n">
-        <v>171000</v>
+        <v>29860350000</v>
       </c>
       <c r="H75" t="n">
-        <v>1710</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4205</v>
+        <v>6145</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G76" t="n">
-        <v>24829312000</v>
+        <v>171000</v>
       </c>
       <c r="H76" t="n">
-        <v>1721.078563209627</v>
+        <v>1710</v>
       </c>
       <c r="I76" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3569</v>
+        <v>4205</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3273,175 +3273,175 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4271704</v>
+        <v>14426600</v>
       </c>
       <c r="G77" t="n">
-        <v>5808044000</v>
+        <v>24829312000</v>
       </c>
       <c r="H77" t="n">
-        <v>1359.655069733296</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I77" t="n">
-        <v>6.279999999999999</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G78" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H78" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I78" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G79" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H79" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G80" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H80" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G81" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H81" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3450,72 +3450,72 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G82" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H82" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I82" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G83" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H83" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I83" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3524,81 +3524,81 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G84" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H84" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I84" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5541</v>
+        <v>7305</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>100</v>
+        <v>309800</v>
       </c>
       <c r="G85" t="n">
-        <v>127000</v>
+        <v>1321438000</v>
       </c>
       <c r="H85" t="n">
-        <v>1270</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3606,27 +3606,27 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G86" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H86" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I86" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3635,44 +3635,44 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G87" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H87" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3680,36 +3680,36 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G88" t="n">
-        <v>8729143000</v>
+        <v>361000</v>
       </c>
       <c r="H88" t="n">
-        <v>2148.936934940886</v>
+        <v>3610</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3717,175 +3717,175 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G89" t="n">
-        <v>361000</v>
+        <v>20578848000</v>
       </c>
       <c r="H89" t="n">
-        <v>3610</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G90" t="n">
-        <v>5292086000</v>
+        <v>8729143000</v>
       </c>
       <c r="H90" t="n">
-        <v>2112.609181636727</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I90" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G91" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H91" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I91" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G92" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H92" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I92" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G93" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H93" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I93" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3894,172 +3894,172 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G94" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H94" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I94" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G95" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H95" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I95" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G96" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H96" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I96" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G97" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H97" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I97" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G98" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H98" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I98" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="99">
@@ -4102,234 +4102,234 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4521</v>
+        <v>4042</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>100</v>
+        <v>16459200</v>
       </c>
       <c r="G100" t="n">
-        <v>353000</v>
+        <v>33451116000</v>
       </c>
       <c r="H100" t="n">
-        <v>3530</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G101" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H101" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I101" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G102" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H102" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I102" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G103" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H103" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I103" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G104" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H104" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G105" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H105" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I105" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4338,21 +4338,21 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G106" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H106" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I106" t="n">
         <v>5.02</v>
@@ -4361,197 +4361,197 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G107" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H107" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G108" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H108" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I108" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G109" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H109" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I109" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G110" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H110" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G111" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H111" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I111" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4564,142 +4564,142 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G112" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H112" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I112" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G113" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H113" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I113" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G114" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H114" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G115" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H115" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I115" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4708,35 +4708,35 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G116" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H116" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I116" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4745,24 +4745,24 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G117" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H117" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I117" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="118">
@@ -4805,334 +4805,334 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5449</v>
+        <v>4631</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2114100</v>
+        <v>6563759</v>
       </c>
       <c r="G119" t="n">
-        <v>3695597000</v>
+        <v>16844475000</v>
       </c>
       <c r="H119" t="n">
-        <v>1748.071046781136</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I119" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G120" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H120" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I120" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G121" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H121" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I121" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G122" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H122" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I122" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G123" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H123" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I123" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G124" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H124" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I124" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G125" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H125" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G126" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H126" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I126" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G127" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H127" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I127" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="128">
@@ -5175,441 +5175,441 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>8303</v>
+        <v>5186</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>20000000</v>
+        <v>1536900</v>
       </c>
       <c r="G129" t="n">
-        <v>56014500000</v>
+        <v>4758738000</v>
       </c>
       <c r="H129" t="n">
-        <v>2800.725</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I129" t="n">
-        <v>9.75</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G130" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I130" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5451</v>
+        <v>2812</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1752800</v>
-      </c>
-      <c r="G131" t="n">
-        <v>5669831000</v>
-      </c>
-      <c r="H131" t="n">
-        <v>3234.727863989046</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>5.029999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>9072</v>
+        <v>5451</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>8377400</v>
+        <v>1752800</v>
       </c>
       <c r="G132" t="n">
-        <v>13394541000</v>
+        <v>5669831000</v>
       </c>
       <c r="H132" t="n">
-        <v>1598.889989734285</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I132" t="n">
-        <v>12.74</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5194</v>
+        <v>9072</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1068798</v>
+        <v>8377400</v>
       </c>
       <c r="G133" t="n">
-        <v>997342000</v>
+        <v>13394541000</v>
       </c>
       <c r="H133" t="n">
-        <v>933.1435874692879</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I133" t="n">
-        <v>9.77</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>8871</v>
+        <v>5194</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1807700</v>
+        <v>1068798</v>
       </c>
       <c r="G134" t="n">
-        <v>3235548000</v>
+        <v>997342000</v>
       </c>
       <c r="H134" t="n">
-        <v>1789.870000553189</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I134" t="n">
-        <v>5.050000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5929</v>
+        <v>8871</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>11571500</v>
+        <v>1807700</v>
       </c>
       <c r="G135" t="n">
-        <v>15114770000</v>
+        <v>3235548000</v>
       </c>
       <c r="H135" t="n">
-        <v>1306.206628354146</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I135" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>8140</v>
+        <v>5929</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1322800</v>
+        <v>11571500</v>
       </c>
       <c r="G136" t="n">
-        <v>4536170000</v>
+        <v>15114770000</v>
       </c>
       <c r="H136" t="n">
-        <v>3429.218324765649</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I136" t="n">
-        <v>5.29</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1878</v>
+        <v>8140</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3452100</v>
+        <v>1322800</v>
       </c>
       <c r="G137" t="n">
-        <v>44793976000</v>
+        <v>4536170000</v>
       </c>
       <c r="H137" t="n">
-        <v>12975.86280814577</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I137" t="n">
-        <v>5.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>533500</v>
+        <v>3452100</v>
       </c>
       <c r="G138" t="n">
-        <v>2009924000</v>
+        <v>44793976000</v>
       </c>
       <c r="H138" t="n">
-        <v>3767.430178069353</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I138" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3593</v>
+        <v>1882</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1637060</v>
+        <v>533500</v>
       </c>
       <c r="G139" t="n">
-        <v>5502657000</v>
+        <v>2009924000</v>
       </c>
       <c r="H139" t="n">
-        <v>3361.304411567078</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I139" t="n">
-        <v>6.48</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>7157</v>
+        <v>3593</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>4536300</v>
+        <v>1637060</v>
       </c>
       <c r="G140" t="n">
-        <v>4025006000</v>
+        <v>5502657000</v>
       </c>
       <c r="H140" t="n">
-        <v>887.288318673809</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I140" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="141">
@@ -5652,128 +5652,128 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>7350</v>
+        <v>7157</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+        <v>4536300</v>
+      </c>
+      <c r="G142" t="n">
+        <v>4025006000</v>
+      </c>
+      <c r="H142" t="n">
+        <v>887.288318673809</v>
+      </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3549</v>
+        <v>7350</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1735200</v>
-      </c>
-      <c r="G143" t="n">
-        <v>11532479000</v>
-      </c>
-      <c r="H143" t="n">
-        <v>6646.195827570309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>6770</v>
+        <v>3549</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>11259700</v>
+        <v>1735200</v>
       </c>
       <c r="G144" t="n">
-        <v>14161429000</v>
+        <v>11532479000</v>
       </c>
       <c r="H144" t="n">
-        <v>1257.709264012363</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I144" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3391</v>
+        <v>6770</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5781,101 +5781,101 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>6354522</v>
+        <v>11259700</v>
       </c>
       <c r="G145" t="n">
-        <v>28876223000</v>
+        <v>14161429000</v>
       </c>
       <c r="H145" t="n">
-        <v>4544.200649553184</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I145" t="n">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1951</v>
+        <v>3391</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>5561200</v>
+        <v>6354522</v>
       </c>
       <c r="G146" t="n">
-        <v>12623472000</v>
+        <v>28876223000</v>
       </c>
       <c r="H146" t="n">
-        <v>2269.918722577861</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I146" t="n">
-        <v>5.06</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QNRY.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3085</v>
+        <v>1951</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1756300</v>
+        <v>5561200</v>
       </c>
       <c r="G147" t="n">
-        <v>4694343000</v>
+        <v>12623472000</v>
       </c>
       <c r="H147" t="n">
-        <v>2672.859420372374</v>
+        <v>2269.918722577861</v>
       </c>
       <c r="I147" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100QJNN.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5884,142 +5884,146 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>9842</v>
+        <v>3085</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2082200</v>
+        <v>1756300</v>
       </c>
       <c r="G148" t="n">
-        <v>3059101000</v>
+        <v>4694343000</v>
       </c>
       <c r="H148" t="n">
-        <v>1469.167707232735</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I148" t="n">
-        <v>5.029999999999999</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QI52.zip</t>
+          <t>S100QJNN.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
+          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>9672</v>
+        <v>9842</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2410900</v>
+        <v>2082200</v>
       </c>
       <c r="G149" t="n">
-        <v>9382590000</v>
+        <v>3059101000</v>
       </c>
       <c r="H149" t="n">
-        <v>3891.73752540545</v>
+        <v>1469.167707232735</v>
       </c>
       <c r="I149" t="n">
-        <v>8.380000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QGUZ.zip</t>
+          <t>S100QI52.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3558</v>
+        <v>9672</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1214200</v>
+        <v>2410900</v>
       </c>
       <c r="G150" t="n">
-        <v>1538785000</v>
+        <v>9382590000</v>
       </c>
       <c r="H150" t="n">
-        <v>1267.324164058639</v>
+        <v>3891.73752540545</v>
       </c>
       <c r="I150" t="n">
-        <v>10.57</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QGUZ.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2329</v>
+        <v>3558</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+        <v>1214200</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1538785000</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1267.324164058639</v>
+      </c>
       <c r="I151" t="n">
-        <v>9.550000000000001</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QF8K.zip</t>
+          <t>S100QF0T.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6047,74 +6051,107 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QDGW.zip</t>
+          <t>S100QF8K.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4324</v>
+        <v>2329</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>13655200</v>
-      </c>
-      <c r="G153" t="n">
-        <v>56753467000</v>
-      </c>
-      <c r="H153" t="n">
-        <v>4156.179843576074</v>
-      </c>
+        <v>4463000</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>5.050000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>S100QDGW.zip</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>4324</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>13655200</v>
+      </c>
+      <c r="G154" t="n">
+        <v>56753467000</v>
+      </c>
+      <c r="H154" t="n">
+        <v>4156.179843576074</v>
+      </c>
+      <c r="I154" t="n">
+        <v>5.050000000000001</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>S100QBB7.zip</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
-      <c r="D154" t="n">
+      <c r="D155" t="n">
         <v>3608</v>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="F154" t="n">
+      <c r="F155" t="n">
         <v>4569000</v>
       </c>
-      <c r="G154" t="n">
+      <c r="G155" t="n">
         <v>2005111000</v>
       </c>
-      <c r="H154" t="n">
+      <c r="H155" t="n">
         <v>438.851170934559</v>
       </c>
-      <c r="I154" t="n">
+      <c r="I155" t="n">
         <v>5.07</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -478,21 +478,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6675</v>
+        <v>3549</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -500,36 +500,36 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>314400</v>
+        <v>13408159</v>
       </c>
       <c r="G2" t="n">
-        <v>1717778000</v>
+        <v>40855887000</v>
       </c>
       <c r="H2" t="n">
-        <v>5463.67048346056</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I2" t="n">
-        <v>5.029999999999999</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3549</v>
+        <v>6675</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -537,16 +537,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13408159</v>
+        <v>314400</v>
       </c>
       <c r="G3" t="n">
-        <v>40855887000</v>
+        <v>1717778000</v>
       </c>
       <c r="H3" t="n">
-        <v>3047.091476167608</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I3" t="n">
-        <v>14.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1144,21 +1144,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1166,36 +1166,36 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G20" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H20" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I20" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1203,16 +1203,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G21" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H21" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I21" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="22">
@@ -1514,12 +1514,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2030,21 +2030,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9302</v>
+        <v>3106</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2052,36 +2052,36 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3799000</v>
+        <v>900156</v>
       </c>
       <c r="G44" t="n">
-        <v>5671170000</v>
+        <v>4095263000</v>
       </c>
       <c r="H44" t="n">
-        <v>1492.806001579363</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I44" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3106</v>
+        <v>9302</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>900156</v>
+        <v>3799000</v>
       </c>
       <c r="G45" t="n">
-        <v>4095263000</v>
+        <v>5671170000</v>
       </c>
       <c r="H45" t="n">
-        <v>4549.503641591014</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="46">
@@ -3140,21 +3140,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>8141</v>
+        <v>4272</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3162,36 +3162,36 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G74" t="n">
-        <v>93000</v>
+        <v>29860350000</v>
       </c>
       <c r="H74" t="n">
-        <v>930</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4272</v>
+        <v>8141</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3199,16 +3199,16 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>26855100</v>
+        <v>100</v>
       </c>
       <c r="G75" t="n">
-        <v>29860350000</v>
+        <v>93000</v>
       </c>
       <c r="H75" t="n">
-        <v>1111.90611839092</v>
+        <v>930</v>
       </c>
       <c r="I75" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3584,21 +3584,21 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5541</v>
+        <v>2168</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3606,36 +3606,36 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G86" t="n">
-        <v>127000</v>
+        <v>4445105000</v>
       </c>
       <c r="H86" t="n">
-        <v>1270</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3643,16 +3643,16 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G87" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H87" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I87" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4065,21 +4065,21 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3591</v>
+        <v>4042</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -4087,36 +4087,36 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2846091</v>
+        <v>16459200</v>
       </c>
       <c r="G99" t="n">
-        <v>6888596000</v>
+        <v>33451116000</v>
       </c>
       <c r="H99" t="n">
-        <v>2420.370957920882</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I99" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4042</v>
+        <v>3591</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>16459200</v>
+        <v>2846091</v>
       </c>
       <c r="G100" t="n">
-        <v>33451116000</v>
+        <v>6888596000</v>
       </c>
       <c r="H100" t="n">
-        <v>2032.365850102071</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I100" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="101">
@@ -5138,7 +5138,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5947</v>
+        <v>5186</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5160,22 +5160,22 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>7446200</v>
+        <v>1536900</v>
       </c>
       <c r="G128" t="n">
-        <v>21182239000</v>
+        <v>4758738000</v>
       </c>
       <c r="H128" t="n">
-        <v>2844.704547285864</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I128" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5197,16 +5197,16 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G129" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H129" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I129" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="130">
@@ -5615,12 +5615,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1861</v>
+        <v>7157</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5637,27 +5637,27 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3102784</v>
+        <v>4536300</v>
       </c>
       <c r="G141" t="n">
-        <v>8614573000</v>
+        <v>4025006000</v>
       </c>
       <c r="H141" t="n">
-        <v>2776.401128792723</v>
+        <v>887.288318673809</v>
       </c>
       <c r="I141" t="n">
-        <v>7.07</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>7157</v>
+        <v>1861</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5674,16 +5674,16 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>4536300</v>
+        <v>3102784</v>
       </c>
       <c r="G142" t="n">
-        <v>4025006000</v>
+        <v>8614573000</v>
       </c>
       <c r="H142" t="n">
-        <v>887.288318673809</v>
+        <v>2776.401128792723</v>
       </c>
       <c r="I142" t="n">
-        <v>6.5</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="143">
@@ -6018,12 +6018,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QF8K.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6051,12 +6051,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QF8K.zip</t>
+          <t>S100QF0T.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,21 +885,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2432</v>
+        <v>7378</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -907,36 +907,36 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>500400</v>
       </c>
       <c r="G13" t="n">
-        <v>226000</v>
+        <v>698873000</v>
       </c>
       <c r="H13" t="n">
-        <v>2260</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7378</v>
+        <v>2432</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -944,16 +944,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>500400</v>
+        <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>698873000</v>
+        <v>226000</v>
       </c>
       <c r="H14" t="n">
-        <v>1396.628697042366</v>
+        <v>2260</v>
       </c>
       <c r="I14" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1144,21 +1144,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1166,36 +1166,36 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G20" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H20" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I20" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1203,16 +1203,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G21" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H21" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I21" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="22">
@@ -3658,21 +3658,21 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3680,16 +3680,16 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G88" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H88" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="89">
@@ -3732,21 +3732,21 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3754,16 +3754,16 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G90" t="n">
-        <v>8729143000</v>
+        <v>361000</v>
       </c>
       <c r="H90" t="n">
-        <v>2148.936934940886</v>
+        <v>3610</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4065,21 +4065,21 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4042</v>
+        <v>3591</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -4087,36 +4087,36 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>16459200</v>
+        <v>2846091</v>
       </c>
       <c r="G99" t="n">
-        <v>33451116000</v>
+        <v>6888596000</v>
       </c>
       <c r="H99" t="n">
-        <v>2032.365850102071</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I99" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3591</v>
+        <v>4042</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>2846091</v>
+        <v>16459200</v>
       </c>
       <c r="G100" t="n">
-        <v>6888596000</v>
+        <v>33451116000</v>
       </c>
       <c r="H100" t="n">
-        <v>2420.370957920882</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I100" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="101">
@@ -6018,12 +6018,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QF8K.zip</t>
+          <t>S100QF0T.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6051,12 +6051,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QF8K.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6118,43 +6118,6 @@
         <v>5.050000000000001</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>S100QBB7.zip</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-02-24_01_2023-03-01.csv</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>3608</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>4569000</v>
-      </c>
-      <c r="G155" t="n">
-        <v>2005111000</v>
-      </c>
-      <c r="H155" t="n">
-        <v>438.851170934559</v>
-      </c>
-      <c r="I155" t="n">
-        <v>5.07</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,12 +478,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,44 +492,44 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3549</v>
+        <v>1721</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>13408159</v>
+        <v>7462000</v>
       </c>
       <c r="G2" t="n">
-        <v>40855887000</v>
+        <v>27875864000</v>
       </c>
       <c r="H2" t="n">
-        <v>3047.091476167608</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I2" t="n">
-        <v>14.02</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6675</v>
+        <v>3549</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -537,406 +537,406 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>314400</v>
+        <v>13408159</v>
       </c>
       <c r="G3" t="n">
-        <v>1717778000</v>
+        <v>40855887000</v>
       </c>
       <c r="H3" t="n">
-        <v>5463.67048346056</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I3" t="n">
-        <v>5.029999999999999</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7745</v>
+        <v>6675</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1458700</v>
+        <v>314400</v>
       </c>
       <c r="G4" t="n">
-        <v>3040190000</v>
+        <v>1717778000</v>
       </c>
       <c r="H4" t="n">
-        <v>2084.177692465894</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I4" t="n">
-        <v>5.24</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G5" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H5" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G6" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H6" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I6" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G7" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H7" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I7" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G8" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H8" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H9" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I9" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G10" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H10" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I10" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G11" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H11" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G12" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H12" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I12" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G13" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H13" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I13" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2432</v>
+        <v>7378</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -944,64 +944,64 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
+        <v>500400</v>
       </c>
       <c r="G14" t="n">
-        <v>226000</v>
+        <v>698873000</v>
       </c>
       <c r="H14" t="n">
-        <v>2260</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8570</v>
+        <v>2432</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11014402</v>
+        <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>14194389000</v>
+        <v>226000</v>
       </c>
       <c r="H15" t="n">
-        <v>1288.711724885291</v>
+        <v>2260</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1010,98 +1010,98 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G16" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H16" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I16" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G17" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H17" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I17" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G18" t="n">
-        <v>268179335000</v>
+        <v>1970276000</v>
       </c>
       <c r="H18" t="n">
-        <v>16430.4430802409</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I18" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="19">
@@ -1144,58 +1144,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G20" t="n">
-        <v>49662804000</v>
+        <v>268179335000</v>
       </c>
       <c r="H20" t="n">
-        <v>11879.91675437757</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I20" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1203,27 +1203,27 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G21" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H21" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I21" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1232,72 +1232,72 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G22" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H22" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I22" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G23" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H23" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H24" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H25" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1366,12 +1366,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H26" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1403,12 +1403,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1417,21 +1417,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H27" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1454,98 +1454,98 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H28" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G29" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H29" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I29" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G30" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H30" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I30" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="31">
@@ -1588,308 +1588,308 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G32" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H32" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I32" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5331</v>
+        <v>6104</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1481600</v>
+        <v>1297500</v>
       </c>
       <c r="G33" t="n">
-        <v>5294365000</v>
+        <v>4476090000</v>
       </c>
       <c r="H33" t="n">
-        <v>3573.410502159827</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G34" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H34" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I34" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G35" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H35" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H36" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I36" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G37" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H37" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I37" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G38" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H38" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G39" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H39" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1898,170 +1898,170 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G40" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H40" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I40" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G41" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H41" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I41" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H43" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G44" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H44" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="45">
@@ -2104,86 +2104,86 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9684</v>
+        <v>3106</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6704059</v>
+        <v>900156</v>
       </c>
       <c r="G46" t="n">
-        <v>42054369000</v>
+        <v>4095263000</v>
       </c>
       <c r="H46" t="n">
-        <v>6272.971195510064</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I46" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G47" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H47" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2192,21 +2192,21 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H48" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2215,38 +2215,38 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4849</v>
+        <v>6332</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>5148132000</v>
+        <v>141000</v>
       </c>
       <c r="H49" t="n">
-        <v>1746.940387696806</v>
+        <v>1410</v>
       </c>
       <c r="I49" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2289,160 +2289,160 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G51" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H51" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H52" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G53" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H53" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I53" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G54" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H54" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2451,172 +2451,172 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G55" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H55" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I55" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G56" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H56" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I56" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G57" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H57" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I57" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G58" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H58" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I58" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G59" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H59" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="60">
@@ -2659,86 +2659,86 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7732</v>
+        <v>9987</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>7995900</v>
+        <v>3888200</v>
       </c>
       <c r="G61" t="n">
-        <v>16678425000</v>
+        <v>16086019000</v>
       </c>
       <c r="H61" t="n">
-        <v>2085.872134468915</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I61" t="n">
-        <v>7.380000000000001</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G62" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H62" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H63" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -2770,49 +2770,49 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H64" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I64" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2821,146 +2821,146 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G65" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H65" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I65" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G66" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H66" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H67" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I67" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G68" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H68" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I68" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2969,35 +2969,35 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G69" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H69" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I69" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3006,192 +3006,192 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G70" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H70" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I70" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G71" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H71" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I71" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G72" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H72" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I72" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G73" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H73" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I73" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G74" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H74" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I74" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>8141</v>
+        <v>4272</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3199,27 +3199,27 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G75" t="n">
-        <v>93000</v>
+        <v>29860350000</v>
       </c>
       <c r="H75" t="n">
-        <v>930</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>100</v>
       </c>
       <c r="G76" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H76" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -3251,44 +3251,44 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4205</v>
+        <v>6145</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G77" t="n">
-        <v>24829312000</v>
+        <v>171000</v>
       </c>
       <c r="H77" t="n">
-        <v>1721.078563209627</v>
+        <v>1710</v>
       </c>
       <c r="I77" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3569</v>
+        <v>4205</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3310,175 +3310,175 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>4271704</v>
+        <v>14426600</v>
       </c>
       <c r="G78" t="n">
-        <v>5808044000</v>
+        <v>24829312000</v>
       </c>
       <c r="H78" t="n">
-        <v>1359.655069733296</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I78" t="n">
-        <v>6.279999999999999</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G79" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H79" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I79" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G80" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H80" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I80" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G81" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H81" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G82" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H82" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3487,72 +3487,72 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G83" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H83" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I83" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G84" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H84" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I84" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3561,81 +3561,81 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G85" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H85" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I85" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G86" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H86" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I86" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5541</v>
+        <v>2168</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3643,73 +3643,73 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G87" t="n">
-        <v>127000</v>
+        <v>4445105000</v>
       </c>
       <c r="H87" t="n">
-        <v>1270</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G88" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H88" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3717,36 +3717,36 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G89" t="n">
-        <v>20578848000</v>
+        <v>361000</v>
       </c>
       <c r="H89" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3754,175 +3754,175 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G90" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H90" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G91" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H91" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I91" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G92" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H92" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I92" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G93" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H93" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I93" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G94" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H94" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I94" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3931,172 +3931,172 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G95" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H95" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I95" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G96" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H96" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I96" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G97" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H97" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I97" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G98" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H98" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I98" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3591</v>
+        <v>7278</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2846091</v>
+        <v>115400</v>
       </c>
       <c r="G99" t="n">
-        <v>6888596000</v>
+        <v>302115000</v>
       </c>
       <c r="H99" t="n">
-        <v>2420.370957920882</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I99" t="n">
-        <v>5.13</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="100">
@@ -4139,234 +4139,234 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G101" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H101" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G102" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H102" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I102" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G103" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H103" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I103" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G104" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H104" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I104" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G105" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H105" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G106" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H106" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I106" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G107" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H107" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I107" t="n">
         <v>5.02</v>
@@ -4398,197 +4398,197 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G108" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H108" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G109" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H109" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I109" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G110" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H110" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I110" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G111" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H111" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G112" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H112" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I112" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4601,142 +4601,142 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G113" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H113" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I113" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G114" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H114" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I114" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G115" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H115" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G116" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H116" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I116" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4745,35 +4745,35 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G117" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H117" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I117" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4782,24 +4782,24 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4293</v>
+        <v>4837</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>20896886</v>
+        <v>5428600</v>
       </c>
       <c r="G118" t="n">
-        <v>9376038000</v>
+        <v>4378021000</v>
       </c>
       <c r="H118" t="n">
-        <v>448.6811097117532</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I118" t="n">
-        <v>9.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="119">
@@ -4842,340 +4842,340 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G120" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H120" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G121" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H121" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I121" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G122" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H122" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I122" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G123" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H123" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I123" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G124" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H124" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I124" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G125" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H125" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I125" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G126" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H126" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G127" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H127" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I127" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G128" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H128" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I128" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5947</v>
+        <v>5186</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5197,456 +5197,456 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>7446200</v>
+        <v>1536900</v>
       </c>
       <c r="G129" t="n">
-        <v>21182239000</v>
+        <v>4758738000</v>
       </c>
       <c r="H129" t="n">
-        <v>2844.704547285864</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I129" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G130" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H130" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I130" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G131" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I131" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5451</v>
+        <v>2812</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1752800</v>
-      </c>
-      <c r="G132" t="n">
-        <v>5669831000</v>
-      </c>
-      <c r="H132" t="n">
-        <v>3234.727863989046</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>5.029999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>9072</v>
+        <v>5451</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>8377400</v>
+        <v>1752800</v>
       </c>
       <c r="G133" t="n">
-        <v>13394541000</v>
+        <v>5669831000</v>
       </c>
       <c r="H133" t="n">
-        <v>1598.889989734285</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I133" t="n">
-        <v>12.74</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5194</v>
+        <v>9072</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1068798</v>
+        <v>8377400</v>
       </c>
       <c r="G134" t="n">
-        <v>997342000</v>
+        <v>13394541000</v>
       </c>
       <c r="H134" t="n">
-        <v>933.1435874692879</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I134" t="n">
-        <v>9.77</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>8871</v>
+        <v>5194</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1807700</v>
+        <v>1068798</v>
       </c>
       <c r="G135" t="n">
-        <v>3235548000</v>
+        <v>997342000</v>
       </c>
       <c r="H135" t="n">
-        <v>1789.870000553189</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I135" t="n">
-        <v>5.050000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5929</v>
+        <v>8871</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>11571500</v>
+        <v>1807700</v>
       </c>
       <c r="G136" t="n">
-        <v>15114770000</v>
+        <v>3235548000</v>
       </c>
       <c r="H136" t="n">
-        <v>1306.206628354146</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I136" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8140</v>
+        <v>5929</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1322800</v>
+        <v>11571500</v>
       </c>
       <c r="G137" t="n">
-        <v>4536170000</v>
+        <v>15114770000</v>
       </c>
       <c r="H137" t="n">
-        <v>3429.218324765649</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I137" t="n">
-        <v>5.29</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1878</v>
+        <v>8140</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3452100</v>
+        <v>1322800</v>
       </c>
       <c r="G138" t="n">
-        <v>44793976000</v>
+        <v>4536170000</v>
       </c>
       <c r="H138" t="n">
-        <v>12975.86280814577</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I138" t="n">
-        <v>5.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>533500</v>
+        <v>3452100</v>
       </c>
       <c r="G139" t="n">
-        <v>2009924000</v>
+        <v>44793976000</v>
       </c>
       <c r="H139" t="n">
-        <v>3767.430178069353</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I139" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3593</v>
+        <v>1882</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1637060</v>
+        <v>533500</v>
       </c>
       <c r="G140" t="n">
-        <v>5502657000</v>
+        <v>2009924000</v>
       </c>
       <c r="H140" t="n">
-        <v>3361.304411567078</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I140" t="n">
-        <v>6.48</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7157</v>
+        <v>3593</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>4536300</v>
+        <v>1637060</v>
       </c>
       <c r="G141" t="n">
-        <v>4025006000</v>
+        <v>5502657000</v>
       </c>
       <c r="H141" t="n">
-        <v>887.288318673809</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I141" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="142">
@@ -5689,128 +5689,128 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7350</v>
+        <v>7157</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
+        <v>4536300</v>
+      </c>
+      <c r="G143" t="n">
+        <v>4025006000</v>
+      </c>
+      <c r="H143" t="n">
+        <v>887.288318673809</v>
+      </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3549</v>
+        <v>7350</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1735200</v>
-      </c>
-      <c r="G144" t="n">
-        <v>11532479000</v>
-      </c>
-      <c r="H144" t="n">
-        <v>6646.195827570309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6770</v>
+        <v>3549</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>11259700</v>
+        <v>1735200</v>
       </c>
       <c r="G145" t="n">
-        <v>14161429000</v>
+        <v>11532479000</v>
       </c>
       <c r="H145" t="n">
-        <v>1257.709264012363</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I145" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3391</v>
+        <v>6770</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5818,101 +5818,101 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>6354522</v>
+        <v>11259700</v>
       </c>
       <c r="G146" t="n">
-        <v>28876223000</v>
+        <v>14161429000</v>
       </c>
       <c r="H146" t="n">
-        <v>4544.200649553184</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I146" t="n">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1951</v>
+        <v>3391</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>5561200</v>
+        <v>6354522</v>
       </c>
       <c r="G147" t="n">
-        <v>12623472000</v>
+        <v>28876223000</v>
       </c>
       <c r="H147" t="n">
-        <v>2269.918722577861</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I147" t="n">
-        <v>5.06</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QNRY.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3085</v>
+        <v>1951</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1756300</v>
+        <v>5561200</v>
       </c>
       <c r="G148" t="n">
-        <v>4694343000</v>
+        <v>12623472000</v>
       </c>
       <c r="H148" t="n">
-        <v>2672.859420372374</v>
+        <v>2269.918722577861</v>
       </c>
       <c r="I148" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QJNN.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5921,142 +5921,146 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>9842</v>
+        <v>3085</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2082200</v>
+        <v>1756300</v>
       </c>
       <c r="G149" t="n">
-        <v>3059101000</v>
+        <v>4694343000</v>
       </c>
       <c r="H149" t="n">
-        <v>1469.167707232735</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I149" t="n">
-        <v>5.029999999999999</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QI52.zip</t>
+          <t>S100QJNN.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
+          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>9672</v>
+        <v>9842</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2410900</v>
+        <v>2082200</v>
       </c>
       <c r="G150" t="n">
-        <v>9382590000</v>
+        <v>3059101000</v>
       </c>
       <c r="H150" t="n">
-        <v>3891.73752540545</v>
+        <v>1469.167707232735</v>
       </c>
       <c r="I150" t="n">
-        <v>8.380000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QGUZ.zip</t>
+          <t>S100QI52.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3558</v>
+        <v>9672</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1214200</v>
+        <v>2410900</v>
       </c>
       <c r="G151" t="n">
-        <v>1538785000</v>
+        <v>9382590000</v>
       </c>
       <c r="H151" t="n">
-        <v>1267.324164058639</v>
+        <v>3891.73752540545</v>
       </c>
       <c r="I151" t="n">
-        <v>10.57</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QGUZ.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2329</v>
+        <v>3558</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
+        <v>1214200</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1538785000</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1267.324164058639</v>
+      </c>
       <c r="I152" t="n">
-        <v>9.550000000000001</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QF8K.zip</t>
+          <t>S100QF0T.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6084,37 +6088,70 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>S100QF8K.zip</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2329</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>4463000</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="n">
+        <v>9.550000000000001</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>S100QDGW.zip</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
-      <c r="D154" t="n">
+      <c r="D155" t="n">
         <v>4324</v>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>2023-03-10</t>
         </is>
       </c>
-      <c r="F154" t="n">
+      <c r="F155" t="n">
         <v>13655200</v>
       </c>
-      <c r="G154" t="n">
+      <c r="G155" t="n">
         <v>56753467000</v>
       </c>
-      <c r="H154" t="n">
+      <c r="H155" t="n">
         <v>4156.179843576074</v>
       </c>
-      <c r="I154" t="n">
+      <c r="I155" t="n">
         <v>5.050000000000001</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,12 +478,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,35 +492,35 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1721</v>
+        <v>6594</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7462000</v>
+        <v>80322406</v>
       </c>
       <c r="G2" t="n">
-        <v>27875864000</v>
+        <v>178330543000</v>
       </c>
       <c r="H2" t="n">
-        <v>3735.709461270437</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I2" t="n">
-        <v>5.609999999999999</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -529,24 +529,24 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3549</v>
+        <v>1721</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13408159</v>
+        <v>7462000</v>
       </c>
       <c r="G3" t="n">
-        <v>40855887000</v>
+        <v>27875864000</v>
       </c>
       <c r="H3" t="n">
-        <v>3047.091476167608</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I3" t="n">
-        <v>14.02</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -589,391 +589,391 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7745</v>
+        <v>3549</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1458700</v>
+        <v>13408159</v>
       </c>
       <c r="G5" t="n">
-        <v>3040190000</v>
+        <v>40855887000</v>
       </c>
       <c r="H5" t="n">
-        <v>2084.177692465894</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I5" t="n">
-        <v>5.24</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G6" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H6" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G7" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H7" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I7" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G8" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H8" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I8" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G9" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H9" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H10" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I10" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G11" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H11" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I11" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G12" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H12" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G13" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H13" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I13" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G14" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H14" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I14" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2432</v>
+        <v>7378</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -981,64 +981,64 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>500400</v>
       </c>
       <c r="G15" t="n">
-        <v>226000</v>
+        <v>698873000</v>
       </c>
       <c r="H15" t="n">
-        <v>2260</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8570</v>
+        <v>2432</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11014402</v>
+        <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>14194389000</v>
+        <v>226000</v>
       </c>
       <c r="H16" t="n">
-        <v>1288.711724885291</v>
+        <v>2260</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1047,98 +1047,98 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G17" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H17" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I17" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G18" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H18" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I18" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G19" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H19" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I19" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="20">
@@ -1181,58 +1181,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G21" t="n">
-        <v>49662804000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H21" t="n">
-        <v>11879.91675437757</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I21" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1240,27 +1240,27 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G22" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H22" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I22" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1269,72 +1269,72 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G23" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H23" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I23" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G24" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H24" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H25" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1366,12 +1366,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H26" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1403,12 +1403,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1417,21 +1417,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H27" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H28" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1477,12 +1477,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1491,109 +1491,109 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H29" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I29" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G30" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H30" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I30" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G31" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H31" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I31" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1625,308 +1625,308 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G33" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H33" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I33" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5331</v>
+        <v>6104</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1481600</v>
+        <v>1297500</v>
       </c>
       <c r="G34" t="n">
-        <v>5294365000</v>
+        <v>4476090000</v>
       </c>
       <c r="H34" t="n">
-        <v>3573.410502159827</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G35" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H35" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I35" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G36" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H36" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H37" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I37" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G38" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H38" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I38" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G39" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H39" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G40" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H40" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1935,170 +1935,170 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G41" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H41" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I41" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G42" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H42" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I42" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G45" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H45" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I45" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="46">
@@ -2141,12 +2141,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2155,72 +2155,72 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G47" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H47" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I47" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G48" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H48" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2229,21 +2229,21 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H49" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2252,38 +2252,38 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H50" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I50" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2326,160 +2326,160 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4676</v>
+        <v>6927</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>1142700</v>
       </c>
       <c r="G52" t="n">
-        <v>242000</v>
+        <v>1023871000</v>
       </c>
       <c r="H52" t="n">
-        <v>2420</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H53" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G54" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H54" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I54" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G55" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H55" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2488,192 +2488,192 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H56" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I56" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G57" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H57" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I57" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G58" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H58" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I58" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G59" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H59" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4626</v>
+        <v>9006</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G60" t="n">
-        <v>16652257000</v>
+        <v>34824000</v>
       </c>
       <c r="H60" t="n">
-        <v>3565.648720929983</v>
+        <v>1160.8</v>
       </c>
       <c r="I60" t="n">
-        <v>8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9987</v>
+        <v>4626</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2681,101 +2681,101 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3888200</v>
+        <v>4670190</v>
       </c>
       <c r="G61" t="n">
-        <v>16086019000</v>
+        <v>16652257000</v>
       </c>
       <c r="H61" t="n">
-        <v>4137.137750115735</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7732</v>
+        <v>9987</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>7995900</v>
+        <v>3888200</v>
       </c>
       <c r="G62" t="n">
-        <v>16678425000</v>
+        <v>16086019000</v>
       </c>
       <c r="H62" t="n">
-        <v>2085.872134468915</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I62" t="n">
-        <v>7.380000000000001</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G63" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H63" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H64" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -2807,49 +2807,49 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H65" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I65" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2858,146 +2858,146 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G66" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H66" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I66" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G67" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H67" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H68" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I68" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G69" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H69" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I69" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3006,35 +3006,35 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G70" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H70" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I70" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3043,172 +3043,172 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G71" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H71" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I71" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G72" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H72" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I72" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G73" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H73" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I73" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G74" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H74" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I74" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G75" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H75" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I75" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="76">
@@ -3251,81 +3251,81 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6145</v>
+        <v>4272</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G77" t="n">
-        <v>171000</v>
+        <v>29860350000</v>
       </c>
       <c r="H77" t="n">
-        <v>1710</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4205</v>
+        <v>6145</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G78" t="n">
-        <v>24829312000</v>
+        <v>171000</v>
       </c>
       <c r="H78" t="n">
-        <v>1721.078563209627</v>
+        <v>1710</v>
       </c>
       <c r="I78" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3569</v>
+        <v>4205</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3347,175 +3347,175 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4271704</v>
+        <v>14426600</v>
       </c>
       <c r="G79" t="n">
-        <v>5808044000</v>
+        <v>24829312000</v>
       </c>
       <c r="H79" t="n">
-        <v>1359.655069733296</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I79" t="n">
-        <v>6.279999999999999</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G80" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H80" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I80" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G81" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H81" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G82" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H82" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G83" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H83" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3524,72 +3524,72 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G84" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H84" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I84" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G85" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H85" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I85" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3598,81 +3598,81 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G86" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H86" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I86" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G87" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H87" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I87" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5541</v>
+        <v>2168</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3680,27 +3680,27 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G88" t="n">
-        <v>127000</v>
+        <v>4445105000</v>
       </c>
       <c r="H88" t="n">
-        <v>1270</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3709,21 +3709,21 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>8803</v>
+        <v>5541</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>100</v>
       </c>
       <c r="G89" t="n">
-        <v>361000</v>
+        <v>127000</v>
       </c>
       <c r="H89" t="n">
-        <v>3610</v>
+        <v>1270</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -3732,21 +3732,21 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3754,27 +3754,27 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G90" t="n">
-        <v>8729143000</v>
+        <v>361000</v>
       </c>
       <c r="H90" t="n">
-        <v>2148.936934940886</v>
+        <v>3610</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3794,10 +3794,10 @@
         <v>4062075</v>
       </c>
       <c r="G91" t="n">
-        <v>20578848000</v>
+        <v>8729143000</v>
       </c>
       <c r="H91" t="n">
-        <v>5066.092575838703</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I91" t="n">
         <v>5.2</v>
@@ -3806,160 +3806,160 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G92" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H92" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I92" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G93" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H93" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I93" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G94" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H94" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I94" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G95" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H95" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I95" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3968,192 +3968,192 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G96" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H96" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I96" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G97" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H97" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I97" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G98" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H98" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I98" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G99" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H99" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I99" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G100" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H100" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I100" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3591</v>
+        <v>4042</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4161,249 +4161,249 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2846091</v>
+        <v>16459200</v>
       </c>
       <c r="G101" t="n">
-        <v>6888596000</v>
+        <v>33451116000</v>
       </c>
       <c r="H101" t="n">
-        <v>2420.370957920882</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I101" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G102" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H102" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G103" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H103" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I103" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G104" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H104" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I104" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G105" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H105" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I105" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G106" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H106" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G107" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H107" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I107" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4412,21 +4412,21 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G108" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H108" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I108" t="n">
         <v>5.02</v>
@@ -4435,197 +4435,197 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G109" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H109" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H110" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I110" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G111" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H111" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I111" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G112" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H112" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G113" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H113" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I113" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4638,142 +4638,142 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G114" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H114" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I114" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G115" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H115" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I115" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G116" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H116" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G117" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H117" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I117" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4782,35 +4782,35 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G118" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H118" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I118" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4819,30 +4819,30 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G119" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H119" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I119" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4293</v>
+        <v>4631</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4864,349 +4864,349 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>20896886</v>
+        <v>6563759</v>
       </c>
       <c r="G120" t="n">
-        <v>9376038000</v>
+        <v>16844475000</v>
       </c>
       <c r="H120" t="n">
-        <v>448.6811097117532</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I120" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G121" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H121" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G122" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H122" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I122" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G123" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H123" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I123" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G124" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H124" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I124" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G125" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H125" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I125" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G126" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H126" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I126" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G127" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H127" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G128" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H128" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I128" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G129" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H129" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I129" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="130">
@@ -5249,441 +5249,441 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>8303</v>
+        <v>5186</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>20000000</v>
+        <v>1536900</v>
       </c>
       <c r="G131" t="n">
-        <v>56014500000</v>
+        <v>4758738000</v>
       </c>
       <c r="H131" t="n">
-        <v>2800.725</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I131" t="n">
-        <v>9.75</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G132" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H132" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I132" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5451</v>
+        <v>2812</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1752800</v>
-      </c>
-      <c r="G133" t="n">
-        <v>5669831000</v>
-      </c>
-      <c r="H133" t="n">
-        <v>3234.727863989046</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
-        <v>5.029999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>9072</v>
+        <v>5451</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>8377400</v>
+        <v>1752800</v>
       </c>
       <c r="G134" t="n">
-        <v>13394541000</v>
+        <v>5669831000</v>
       </c>
       <c r="H134" t="n">
-        <v>1598.889989734285</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I134" t="n">
-        <v>12.74</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5194</v>
+        <v>9072</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1068798</v>
+        <v>8377400</v>
       </c>
       <c r="G135" t="n">
-        <v>997342000</v>
+        <v>13394541000</v>
       </c>
       <c r="H135" t="n">
-        <v>933.1435874692879</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I135" t="n">
-        <v>9.77</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>8871</v>
+        <v>5194</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1807700</v>
+        <v>1068798</v>
       </c>
       <c r="G136" t="n">
-        <v>3235548000</v>
+        <v>997342000</v>
       </c>
       <c r="H136" t="n">
-        <v>1789.870000553189</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I136" t="n">
-        <v>5.050000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5929</v>
+        <v>8871</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>11571500</v>
+        <v>1807700</v>
       </c>
       <c r="G137" t="n">
-        <v>15114770000</v>
+        <v>3235548000</v>
       </c>
       <c r="H137" t="n">
-        <v>1306.206628354146</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I137" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>8140</v>
+        <v>5929</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1322800</v>
+        <v>11571500</v>
       </c>
       <c r="G138" t="n">
-        <v>4536170000</v>
+        <v>15114770000</v>
       </c>
       <c r="H138" t="n">
-        <v>3429.218324765649</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I138" t="n">
-        <v>5.29</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1878</v>
+        <v>8140</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3452100</v>
+        <v>1322800</v>
       </c>
       <c r="G139" t="n">
-        <v>44793976000</v>
+        <v>4536170000</v>
       </c>
       <c r="H139" t="n">
-        <v>12975.86280814577</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I139" t="n">
-        <v>5.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>533500</v>
+        <v>3452100</v>
       </c>
       <c r="G140" t="n">
-        <v>2009924000</v>
+        <v>44793976000</v>
       </c>
       <c r="H140" t="n">
-        <v>3767.430178069353</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I140" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3593</v>
+        <v>1882</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1637060</v>
+        <v>533500</v>
       </c>
       <c r="G141" t="n">
-        <v>5502657000</v>
+        <v>2009924000</v>
       </c>
       <c r="H141" t="n">
-        <v>3361.304411567078</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I141" t="n">
-        <v>6.48</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1861</v>
+        <v>3593</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3102784</v>
+        <v>1637060</v>
       </c>
       <c r="G142" t="n">
-        <v>8614573000</v>
+        <v>5502657000</v>
       </c>
       <c r="H142" t="n">
-        <v>2776.401128792723</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I142" t="n">
-        <v>7.07</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="143">
@@ -5726,108 +5726,108 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>7350</v>
+        <v>1861</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
+        <v>3102784</v>
+      </c>
+      <c r="G144" t="n">
+        <v>8614573000</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2776.401128792723</v>
+      </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3549</v>
+        <v>7350</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1735200</v>
-      </c>
-      <c r="G145" t="n">
-        <v>11532479000</v>
-      </c>
-      <c r="H145" t="n">
-        <v>6646.195827570309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>6770</v>
+        <v>3549</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>11259700</v>
+        <v>1735200</v>
       </c>
       <c r="G146" t="n">
-        <v>14161429000</v>
+        <v>11532479000</v>
       </c>
       <c r="H146" t="n">
-        <v>1257.709264012363</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I146" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="147">
@@ -5870,86 +5870,86 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1951</v>
+        <v>6770</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>5561200</v>
+        <v>11259700</v>
       </c>
       <c r="G148" t="n">
-        <v>12623472000</v>
+        <v>14161429000</v>
       </c>
       <c r="H148" t="n">
-        <v>2269.918722577861</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I148" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QNRY.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3085</v>
+        <v>1951</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1756300</v>
+        <v>5561200</v>
       </c>
       <c r="G149" t="n">
-        <v>4694343000</v>
+        <v>12623472000</v>
       </c>
       <c r="H149" t="n">
-        <v>2672.859420372374</v>
+        <v>2269.918722577861</v>
       </c>
       <c r="I149" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QJNN.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5958,142 +5958,146 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>9842</v>
+        <v>3085</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2082200</v>
+        <v>1756300</v>
       </c>
       <c r="G150" t="n">
-        <v>3059101000</v>
+        <v>4694343000</v>
       </c>
       <c r="H150" t="n">
-        <v>1469.167707232735</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I150" t="n">
-        <v>5.029999999999999</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QI52.zip</t>
+          <t>S100QJNN.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
+          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>9672</v>
+        <v>9842</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2410900</v>
+        <v>2082200</v>
       </c>
       <c r="G151" t="n">
-        <v>9382590000</v>
+        <v>3059101000</v>
       </c>
       <c r="H151" t="n">
-        <v>3891.73752540545</v>
+        <v>1469.167707232735</v>
       </c>
       <c r="I151" t="n">
-        <v>8.380000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QGUZ.zip</t>
+          <t>S100QI52.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3558</v>
+        <v>9672</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1214200</v>
+        <v>2410900</v>
       </c>
       <c r="G152" t="n">
-        <v>1538785000</v>
+        <v>9382590000</v>
       </c>
       <c r="H152" t="n">
-        <v>1267.324164058639</v>
+        <v>3891.73752540545</v>
       </c>
       <c r="I152" t="n">
-        <v>10.57</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QGUZ.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2329</v>
+        <v>3558</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
+        <v>1214200</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1538785000</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1267.324164058639</v>
+      </c>
       <c r="I153" t="n">
-        <v>9.550000000000001</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100QF8K.zip</t>
+          <t>S100QF0T.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6121,37 +6125,70 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>S100QF8K.zip</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2329</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>4463000</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="n">
+        <v>9.550000000000001</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>S100QDGW.zip</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
-      <c r="D155" t="n">
+      <c r="D156" t="n">
         <v>4324</v>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>2023-03-10</t>
         </is>
       </c>
-      <c r="F155" t="n">
+      <c r="F156" t="n">
         <v>13655200</v>
       </c>
-      <c r="G155" t="n">
+      <c r="G156" t="n">
         <v>56753467000</v>
       </c>
-      <c r="H155" t="n">
+      <c r="H156" t="n">
         <v>4156.179843576074</v>
       </c>
-      <c r="I155" t="n">
+      <c r="I156" t="n">
         <v>5.050000000000001</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,21 +552,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6675</v>
+        <v>3549</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -574,36 +574,36 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>314400</v>
+        <v>13408159</v>
       </c>
       <c r="G4" t="n">
-        <v>1717778000</v>
+        <v>40855887000</v>
       </c>
       <c r="H4" t="n">
-        <v>5463.67048346056</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I4" t="n">
-        <v>5.029999999999999</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3549</v>
+        <v>6675</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -611,16 +611,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13408159</v>
+        <v>314400</v>
       </c>
       <c r="G5" t="n">
-        <v>40855887000</v>
+        <v>1717778000</v>
       </c>
       <c r="H5" t="n">
-        <v>3047.091476167608</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I5" t="n">
-        <v>14.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1169,10 +1169,10 @@
         <v>16322100</v>
       </c>
       <c r="G20" t="n">
-        <v>268179335000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H20" t="n">
-        <v>16430.4430802409</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I20" t="n">
         <v>5.01</v>
@@ -1181,12 +1181,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1206,10 +1206,10 @@
         <v>16322100</v>
       </c>
       <c r="G21" t="n">
-        <v>268179335457000</v>
+        <v>268179335000</v>
       </c>
       <c r="H21" t="n">
-        <v>16430443.10823975</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I21" t="n">
         <v>5.01</v>
@@ -2289,21 +2289,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4849</v>
+        <v>6927</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2311,36 +2311,36 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2946942</v>
+        <v>1142700</v>
       </c>
       <c r="G51" t="n">
-        <v>5148132000</v>
+        <v>1023871000</v>
       </c>
       <c r="H51" t="n">
-        <v>1746.940387696806</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I51" t="n">
-        <v>5.93</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6927</v>
+        <v>4849</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2348,16 +2348,16 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1142700</v>
+        <v>2946942</v>
       </c>
       <c r="G52" t="n">
-        <v>1023871000</v>
+        <v>5148132000</v>
       </c>
       <c r="H52" t="n">
-        <v>896.0103264198827</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I52" t="n">
-        <v>5.01</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="53">
@@ -3214,21 +3214,21 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8141</v>
+        <v>4272</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3236,36 +3236,36 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G76" t="n">
-        <v>93000</v>
+        <v>29860350000</v>
       </c>
       <c r="H76" t="n">
-        <v>930</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4272</v>
+        <v>8141</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3273,16 +3273,16 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>26855100</v>
+        <v>100</v>
       </c>
       <c r="G77" t="n">
-        <v>29860350000</v>
+        <v>93000</v>
       </c>
       <c r="H77" t="n">
-        <v>1111.90611839092</v>
+        <v>930</v>
       </c>
       <c r="I77" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3658,21 +3658,21 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3680,36 +3680,36 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G88" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H88" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I88" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5541</v>
+        <v>2168</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3717,36 +3717,36 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G89" t="n">
-        <v>127000</v>
+        <v>4445105000</v>
       </c>
       <c r="H89" t="n">
-        <v>1270</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3754,16 +3754,16 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G90" t="n">
-        <v>361000</v>
+        <v>20578848000</v>
       </c>
       <c r="H90" t="n">
-        <v>3610</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="91">
@@ -3806,21 +3806,21 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3828,16 +3828,16 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G92" t="n">
-        <v>20578848000</v>
+        <v>361000</v>
       </c>
       <c r="H92" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4842,7 +4842,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4631</v>
+        <v>4293</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4864,22 +4864,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>6563759</v>
+        <v>20896886</v>
       </c>
       <c r="G120" t="n">
-        <v>16844475000</v>
+        <v>9376038000</v>
       </c>
       <c r="H120" t="n">
-        <v>2566.284807227078</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I120" t="n">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4293</v>
+        <v>4631</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4901,16 +4901,16 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>20896886</v>
+        <v>6563759</v>
       </c>
       <c r="G121" t="n">
-        <v>9376038000</v>
+        <v>16844475000</v>
       </c>
       <c r="H121" t="n">
-        <v>448.6811097117532</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I121" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="122">
@@ -5212,7 +5212,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5947</v>
+        <v>5186</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5234,22 +5234,22 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>7446200</v>
+        <v>1536900</v>
       </c>
       <c r="G130" t="n">
-        <v>21182239000</v>
+        <v>4758738000</v>
       </c>
       <c r="H130" t="n">
-        <v>2844.704547285864</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I130" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5271,16 +5271,16 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G131" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H131" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I131" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="132">
@@ -6155,43 +6155,6 @@
         <v>9.550000000000001</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>S100QDGW.zip</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-03-10_01_2023-03-13.csv</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>4324</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>2023-03-10</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>13655200</v>
-      </c>
-      <c r="G156" t="n">
-        <v>56753467000</v>
-      </c>
-      <c r="H156" t="n">
-        <v>4156.179843576074</v>
-      </c>
-      <c r="I156" t="n">
-        <v>5.050000000000001</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,49 +478,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6594</v>
+        <v>3132</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>80322406</v>
+        <v>14653542</v>
       </c>
       <c r="G2" t="n">
-        <v>178330543000</v>
+        <v>23038030000</v>
       </c>
       <c r="H2" t="n">
-        <v>2220.184278344451</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I2" t="n">
-        <v>6.74</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -529,35 +529,35 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1721</v>
+        <v>6594</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7462000</v>
+        <v>80322406</v>
       </c>
       <c r="G3" t="n">
-        <v>27875864000</v>
+        <v>178330543000</v>
       </c>
       <c r="H3" t="n">
-        <v>3735.709461270437</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I3" t="n">
-        <v>5.609999999999999</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -566,44 +566,44 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3549</v>
+        <v>1721</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13408159</v>
+        <v>7462000</v>
       </c>
       <c r="G4" t="n">
-        <v>40855887000</v>
+        <v>27875864000</v>
       </c>
       <c r="H4" t="n">
-        <v>3047.091476167608</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I4" t="n">
-        <v>14.02</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6675</v>
+        <v>3549</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -611,386 +611,386 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>314400</v>
+        <v>13408159</v>
       </c>
       <c r="G5" t="n">
-        <v>1717778000</v>
+        <v>40855887000</v>
       </c>
       <c r="H5" t="n">
-        <v>5463.67048346056</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I5" t="n">
-        <v>5.029999999999999</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7745</v>
+        <v>6675</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1458700</v>
+        <v>314400</v>
       </c>
       <c r="G6" t="n">
-        <v>3040190000</v>
+        <v>1717778000</v>
       </c>
       <c r="H6" t="n">
-        <v>2084.177692465894</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I6" t="n">
-        <v>5.24</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G7" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H7" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I7" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G8" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H8" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I8" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G9" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H9" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I9" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G10" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H10" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H11" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I11" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G12" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H12" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I12" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G13" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H13" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G14" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H14" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I14" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G15" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H15" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I15" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="16">
@@ -1033,49 +1033,49 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G17" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H17" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1084,98 +1084,98 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G18" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H18" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I18" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G19" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H19" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I19" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G20" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H20" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I20" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="21">
@@ -1218,58 +1218,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G22" t="n">
-        <v>49662804000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H22" t="n">
-        <v>11879.91675437757</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I22" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1277,27 +1277,27 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G23" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H23" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I23" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1306,72 +1306,72 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G24" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H24" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I24" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G25" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H25" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H26" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1403,12 +1403,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1417,21 +1417,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H27" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H28" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1477,12 +1477,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1491,21 +1491,21 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H29" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1514,12 +1514,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1528,98 +1528,98 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H30" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G31" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H31" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I31" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G32" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H32" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I32" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="33">
@@ -1662,308 +1662,308 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G34" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H34" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I34" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5331</v>
+        <v>6104</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1481600</v>
+        <v>1297500</v>
       </c>
       <c r="G35" t="n">
-        <v>5294365000</v>
+        <v>4476090000</v>
       </c>
       <c r="H35" t="n">
-        <v>3573.410502159827</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G36" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H36" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I36" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G37" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H37" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H38" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I38" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G39" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H39" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I39" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G40" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H40" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G41" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H41" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1972,190 +1972,190 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G42" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H42" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I42" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G43" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H43" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I43" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G46" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H46" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9302</v>
+        <v>3106</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2163,27 +2163,27 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3799000</v>
+        <v>900156</v>
       </c>
       <c r="G47" t="n">
-        <v>5671170000</v>
+        <v>4095263000</v>
       </c>
       <c r="H47" t="n">
-        <v>1492.806001579363</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I47" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2192,72 +2192,72 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G48" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H48" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I48" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G49" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H49" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2266,21 +2266,21 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H50" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2289,38 +2289,38 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H51" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I51" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2363,160 +2363,160 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4676</v>
+        <v>6927</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>1142700</v>
       </c>
       <c r="G53" t="n">
-        <v>242000</v>
+        <v>1023871000</v>
       </c>
       <c r="H53" t="n">
-        <v>2420</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G54" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H54" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G55" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H55" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I55" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G56" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H56" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2525,172 +2525,172 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H57" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I57" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G58" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H58" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I58" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G59" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H59" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I59" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G60" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H60" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I60" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4626</v>
+        <v>9006</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G61" t="n">
-        <v>16652257000</v>
+        <v>34824000</v>
       </c>
       <c r="H61" t="n">
-        <v>3565.648720929983</v>
+        <v>1160.8</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="62">
@@ -2733,12 +2733,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2747,72 +2747,72 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G63" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H63" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I63" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G64" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H64" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H65" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -2844,49 +2844,49 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H66" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I66" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2895,146 +2895,146 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G67" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H67" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I67" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G68" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H68" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H69" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I69" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G70" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H70" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I70" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3043,35 +3043,35 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G71" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H71" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I71" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3080,192 +3080,192 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G72" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H72" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I72" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G73" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H73" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I73" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G74" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H74" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I74" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G75" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H75" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I75" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G76" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H76" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I76" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>8141</v>
+        <v>4272</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3273,27 +3273,27 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G77" t="n">
-        <v>93000</v>
+        <v>29860350000</v>
       </c>
       <c r="H77" t="n">
-        <v>930</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>100</v>
       </c>
       <c r="G78" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H78" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -3325,44 +3325,44 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4205</v>
+        <v>6145</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G79" t="n">
-        <v>24829312000</v>
+        <v>171000</v>
       </c>
       <c r="H79" t="n">
-        <v>1721.078563209627</v>
+        <v>1710</v>
       </c>
       <c r="I79" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3569</v>
+        <v>4205</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3384,175 +3384,175 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4271704</v>
+        <v>14426600</v>
       </c>
       <c r="G80" t="n">
-        <v>5808044000</v>
+        <v>24829312000</v>
       </c>
       <c r="H80" t="n">
-        <v>1359.655069733296</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I80" t="n">
-        <v>6.279999999999999</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G81" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H81" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I81" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G82" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H82" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G83" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H83" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G84" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H84" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3561,72 +3561,72 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G85" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H85" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I85" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G86" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H86" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I86" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3635,81 +3635,81 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G87" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H87" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I87" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5541</v>
+        <v>7305</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>100</v>
+        <v>309800</v>
       </c>
       <c r="G88" t="n">
-        <v>127000</v>
+        <v>1321438000</v>
       </c>
       <c r="H88" t="n">
-        <v>1270</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3717,27 +3717,27 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G89" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H89" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I89" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3746,24 +3746,24 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G90" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H90" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="91">
@@ -3843,160 +3843,160 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G93" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H93" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I93" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G94" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H94" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I94" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G95" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H95" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I95" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G96" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H96" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I96" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4005,192 +4005,192 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G97" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H97" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I97" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G98" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H98" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I98" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G99" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H99" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I99" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G100" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H100" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I100" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G101" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H101" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I101" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3591</v>
+        <v>4042</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4198,249 +4198,249 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2846091</v>
+        <v>16459200</v>
       </c>
       <c r="G102" t="n">
-        <v>6888596000</v>
+        <v>33451116000</v>
       </c>
       <c r="H102" t="n">
-        <v>2420.370957920882</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I102" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G103" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H103" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G104" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H104" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I104" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G105" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H105" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I105" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G106" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H106" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I106" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G107" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H107" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G108" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H108" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I108" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4449,21 +4449,21 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G109" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H109" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I109" t="n">
         <v>5.02</v>
@@ -4472,197 +4472,197 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G110" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H110" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G111" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H111" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I111" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G112" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H112" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I112" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G113" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H113" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G114" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H114" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I114" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4675,142 +4675,142 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G115" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H115" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I115" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G116" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H116" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I116" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G117" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H117" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G118" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H118" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I118" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4819,35 +4819,35 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G119" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H119" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I119" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4856,24 +4856,24 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4293</v>
+        <v>4837</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>20896886</v>
+        <v>5428600</v>
       </c>
       <c r="G120" t="n">
-        <v>9376038000</v>
+        <v>4378021000</v>
       </c>
       <c r="H120" t="n">
-        <v>448.6811097117532</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I120" t="n">
-        <v>9.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="121">
@@ -4916,340 +4916,340 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G122" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H122" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I122" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G123" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H123" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I123" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G124" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H124" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I124" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G125" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H125" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I125" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G126" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H126" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I126" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G127" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H127" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I127" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G128" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H128" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G129" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H129" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I129" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G130" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H130" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I130" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5947</v>
+        <v>5186</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5271,467 +5271,467 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>7446200</v>
+        <v>1536900</v>
       </c>
       <c r="G131" t="n">
-        <v>21182239000</v>
+        <v>4758738000</v>
       </c>
       <c r="H131" t="n">
-        <v>2844.704547285864</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I131" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G132" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H132" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I132" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G133" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I133" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5451</v>
+        <v>2812</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1752800</v>
-      </c>
-      <c r="G134" t="n">
-        <v>5669831000</v>
-      </c>
-      <c r="H134" t="n">
-        <v>3234.727863989046</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
-        <v>5.029999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>9072</v>
+        <v>5451</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>8377400</v>
+        <v>1752800</v>
       </c>
       <c r="G135" t="n">
-        <v>13394541000</v>
+        <v>5669831000</v>
       </c>
       <c r="H135" t="n">
-        <v>1598.889989734285</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I135" t="n">
-        <v>12.74</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5194</v>
+        <v>9072</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1068798</v>
+        <v>8377400</v>
       </c>
       <c r="G136" t="n">
-        <v>997342000</v>
+        <v>13394541000</v>
       </c>
       <c r="H136" t="n">
-        <v>933.1435874692879</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I136" t="n">
-        <v>9.77</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8871</v>
+        <v>5194</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1807700</v>
+        <v>1068798</v>
       </c>
       <c r="G137" t="n">
-        <v>3235548000</v>
+        <v>997342000</v>
       </c>
       <c r="H137" t="n">
-        <v>1789.870000553189</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I137" t="n">
-        <v>5.050000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5929</v>
+        <v>8871</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>11571500</v>
+        <v>1807700</v>
       </c>
       <c r="G138" t="n">
-        <v>15114770000</v>
+        <v>3235548000</v>
       </c>
       <c r="H138" t="n">
-        <v>1306.206628354146</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I138" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>8140</v>
+        <v>5929</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1322800</v>
+        <v>11571500</v>
       </c>
       <c r="G139" t="n">
-        <v>4536170000</v>
+        <v>15114770000</v>
       </c>
       <c r="H139" t="n">
-        <v>3429.218324765649</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I139" t="n">
-        <v>5.29</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1878</v>
+        <v>8140</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3452100</v>
+        <v>1322800</v>
       </c>
       <c r="G140" t="n">
-        <v>44793976000</v>
+        <v>4536170000</v>
       </c>
       <c r="H140" t="n">
-        <v>12975.86280814577</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I140" t="n">
-        <v>5.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>533500</v>
+        <v>3452100</v>
       </c>
       <c r="G141" t="n">
-        <v>2009924000</v>
+        <v>44793976000</v>
       </c>
       <c r="H141" t="n">
-        <v>3767.430178069353</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I141" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3593</v>
+        <v>1882</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1637060</v>
+        <v>533500</v>
       </c>
       <c r="G142" t="n">
-        <v>5502657000</v>
+        <v>2009924000</v>
       </c>
       <c r="H142" t="n">
-        <v>3361.304411567078</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I142" t="n">
-        <v>6.48</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7157</v>
+        <v>3593</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>4536300</v>
+        <v>1637060</v>
       </c>
       <c r="G143" t="n">
-        <v>4025006000</v>
+        <v>5502657000</v>
       </c>
       <c r="H143" t="n">
-        <v>887.288318673809</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I143" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1861</v>
+        <v>7157</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5748,97 +5748,97 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3102784</v>
+        <v>4536300</v>
       </c>
       <c r="G144" t="n">
-        <v>8614573000</v>
+        <v>4025006000</v>
       </c>
       <c r="H144" t="n">
-        <v>2776.401128792723</v>
+        <v>887.288318673809</v>
       </c>
       <c r="I144" t="n">
-        <v>7.07</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>7350</v>
+        <v>1861</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
+        <v>3102784</v>
+      </c>
+      <c r="G145" t="n">
+        <v>8614573000</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2776.401128792723</v>
+      </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3549</v>
+        <v>7350</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1735200</v>
-      </c>
-      <c r="G146" t="n">
-        <v>11532479000</v>
-      </c>
-      <c r="H146" t="n">
-        <v>6646.195827570309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5847,24 +5847,24 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3391</v>
+        <v>3549</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>6354522</v>
+        <v>1735200</v>
       </c>
       <c r="G147" t="n">
-        <v>28876223000</v>
+        <v>11532479000</v>
       </c>
       <c r="H147" t="n">
-        <v>4544.200649553184</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I147" t="n">
-        <v>12.84</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="148">
@@ -5907,86 +5907,86 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1951</v>
+        <v>3391</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>5561200</v>
+        <v>6354522</v>
       </c>
       <c r="G149" t="n">
-        <v>12623472000</v>
+        <v>28876223000</v>
       </c>
       <c r="H149" t="n">
-        <v>2269.918722577861</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I149" t="n">
-        <v>5.06</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QNRY.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3085</v>
+        <v>1951</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1756300</v>
+        <v>5561200</v>
       </c>
       <c r="G150" t="n">
-        <v>4694343000</v>
+        <v>12623472000</v>
       </c>
       <c r="H150" t="n">
-        <v>2672.859420372374</v>
+        <v>2269.918722577861</v>
       </c>
       <c r="I150" t="n">
-        <v>5.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QJNN.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5995,142 +5995,146 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>9842</v>
+        <v>3085</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2082200</v>
+        <v>1756300</v>
       </c>
       <c r="G151" t="n">
-        <v>3059101000</v>
+        <v>4694343000</v>
       </c>
       <c r="H151" t="n">
-        <v>1469.167707232735</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I151" t="n">
-        <v>5.029999999999999</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QI52.zip</t>
+          <t>S100QJNN.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
+          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>9672</v>
+        <v>9842</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2410900</v>
+        <v>2082200</v>
       </c>
       <c r="G152" t="n">
-        <v>9382590000</v>
+        <v>3059101000</v>
       </c>
       <c r="H152" t="n">
-        <v>3891.73752540545</v>
+        <v>1469.167707232735</v>
       </c>
       <c r="I152" t="n">
-        <v>8.380000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QGUZ.zip</t>
+          <t>S100QI52.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3558</v>
+        <v>9672</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1214200</v>
+        <v>2410900</v>
       </c>
       <c r="G153" t="n">
-        <v>1538785000</v>
+        <v>9382590000</v>
       </c>
       <c r="H153" t="n">
-        <v>1267.324164058639</v>
+        <v>3891.73752540545</v>
       </c>
       <c r="I153" t="n">
-        <v>10.57</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QGUZ.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2329</v>
+        <v>3558</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
+        <v>1214200</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1538785000</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1267.324164058639</v>
+      </c>
       <c r="I154" t="n">
-        <v>9.550000000000001</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100QF8K.zip</t>
+          <t>S100QF0T.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6155,6 +6159,39 @@
         <v>9.550000000000001</v>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>S100QF8K.zip</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2329</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>4463000</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="n">
+        <v>9.550000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,49 +478,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XRXF.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3132</v>
+        <v>4676</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14653542</v>
+        <v>2662900</v>
       </c>
       <c r="G2" t="n">
-        <v>23038030000</v>
+        <v>8365298000</v>
       </c>
       <c r="H2" t="n">
-        <v>1572.181660925393</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I2" t="n">
-        <v>8.18</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -529,72 +529,72 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6594</v>
+        <v>9468</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>80322406</v>
+        <v>13197300</v>
       </c>
       <c r="G3" t="n">
-        <v>178330543000</v>
+        <v>39531520000</v>
       </c>
       <c r="H3" t="n">
-        <v>2220.184278344451</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I3" t="n">
-        <v>6.74</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1721</v>
+        <v>3132</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7462000</v>
+        <v>14653542</v>
       </c>
       <c r="G4" t="n">
-        <v>27875864000</v>
+        <v>23038030000</v>
       </c>
       <c r="H4" t="n">
-        <v>3735.709461270437</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I4" t="n">
-        <v>5.609999999999999</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -603,146 +603,146 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3549</v>
+        <v>6594</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13408159</v>
+        <v>80322406</v>
       </c>
       <c r="G5" t="n">
-        <v>40855887000</v>
+        <v>178330543000</v>
       </c>
       <c r="H5" t="n">
-        <v>3047.091476167608</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I5" t="n">
-        <v>14.02</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6675</v>
+        <v>1721</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>314400</v>
+        <v>7462000</v>
       </c>
       <c r="G6" t="n">
-        <v>1717778000</v>
+        <v>27875864000</v>
       </c>
       <c r="H6" t="n">
-        <v>5463.67048346056</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I6" t="n">
-        <v>5.029999999999999</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7745</v>
+        <v>3549</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1458700</v>
+        <v>13408159</v>
       </c>
       <c r="G7" t="n">
-        <v>3040190000</v>
+        <v>40855887000</v>
       </c>
       <c r="H7" t="n">
-        <v>2084.177692465894</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I7" t="n">
-        <v>5.24</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9072</v>
+        <v>6675</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8985002</v>
+        <v>314400</v>
       </c>
       <c r="G8" t="n">
-        <v>24970571000</v>
+        <v>1717778000</v>
       </c>
       <c r="H8" t="n">
-        <v>2779.139169918938</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -751,257 +751,257 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4189</v>
+        <v>7745</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2040400</v>
+        <v>1458700</v>
       </c>
       <c r="G9" t="n">
-        <v>5203426000</v>
+        <v>3040190000</v>
       </c>
       <c r="H9" t="n">
-        <v>2550.198980592041</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I9" t="n">
-        <v>5.489999999999999</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6794</v>
+        <v>9072</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1252600</v>
+        <v>8985002</v>
       </c>
       <c r="G10" t="n">
-        <v>3359425000</v>
+        <v>24970571000</v>
       </c>
       <c r="H10" t="n">
-        <v>2681.96152003832</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I10" t="n">
-        <v>5.01</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2972</v>
+        <v>4189</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2040400</v>
       </c>
       <c r="G11" t="n">
-        <v>125000</v>
+        <v>5203426000</v>
       </c>
       <c r="H11" t="n">
-        <v>125000</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2175</v>
+        <v>6794</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6792424</v>
+        <v>1252600</v>
       </c>
       <c r="G12" t="n">
-        <v>10040067000</v>
+        <v>3359425000</v>
       </c>
       <c r="H12" t="n">
-        <v>1478.127248828989</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I12" t="n">
-        <v>7.76</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3106</v>
+        <v>2972</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>853156</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>4849339000</v>
+        <v>125000</v>
       </c>
       <c r="H13" t="n">
-        <v>5684.0003469471</v>
+        <v>125000</v>
       </c>
       <c r="I13" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8233</v>
+        <v>2175</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>261400</v>
+        <v>6792424</v>
       </c>
       <c r="G14" t="n">
-        <v>287906000</v>
+        <v>10040067000</v>
       </c>
       <c r="H14" t="n">
-        <v>1101.400153022188</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2371</v>
+        <v>3106</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10372003</v>
+        <v>853156</v>
       </c>
       <c r="G15" t="n">
-        <v>24045569000</v>
+        <v>4849339000</v>
       </c>
       <c r="H15" t="n">
-        <v>2318.314890576102</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I15" t="n">
-        <v>5.23</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1010,442 +1010,442 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2432</v>
+        <v>8233</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
+        <v>261400</v>
       </c>
       <c r="G16" t="n">
-        <v>226000</v>
+        <v>287906000</v>
       </c>
       <c r="H16" t="n">
-        <v>2260</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G17" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H17" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I17" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G18" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H18" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6890</v>
+        <v>2432</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4038389</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>15954609000</v>
+        <v>226000</v>
       </c>
       <c r="H19" t="n">
-        <v>3950.736048458928</v>
+        <v>2260</v>
       </c>
       <c r="I19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9742</v>
+        <v>8570</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1048500</v>
+        <v>11014402</v>
       </c>
       <c r="G20" t="n">
-        <v>1970276000</v>
+        <v>14194389000</v>
       </c>
       <c r="H20" t="n">
-        <v>1879.137815927515</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I20" t="n">
-        <v>5.02</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6201</v>
+        <v>6890</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>16322100</v>
+        <v>4038389</v>
       </c>
       <c r="G21" t="n">
-        <v>268179335000</v>
+        <v>15954609000</v>
       </c>
       <c r="H21" t="n">
-        <v>16430.4430802409</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I21" t="n">
-        <v>5.01</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G22" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H22" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I22" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G23" t="n">
-        <v>49662804000</v>
+        <v>268179335000</v>
       </c>
       <c r="H23" t="n">
-        <v>11879.91675437757</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I23" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G24" t="n">
-        <v>1831405000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H24" t="n">
-        <v>3321.975331035734</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I24" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4549</v>
+        <v>6856</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2546351</v>
+        <v>4180400</v>
       </c>
       <c r="G25" t="n">
-        <v>4958319000</v>
+        <v>49662804000</v>
       </c>
       <c r="H25" t="n">
-        <v>1947.225264702313</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I25" t="n">
-        <v>7.37</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7940</v>
+        <v>8011</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>551300</v>
       </c>
       <c r="G26" t="n">
-        <v>101000</v>
+        <v>1831405000</v>
       </c>
       <c r="H26" t="n">
-        <v>1010</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6890</v>
+        <v>4549</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G27" t="n">
-        <v>203000</v>
+        <v>4958319000</v>
       </c>
       <c r="H27" t="n">
-        <v>2030</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2432</v>
+        <v>7940</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>226000</v>
+        <v>101000</v>
       </c>
       <c r="H28" t="n">
-        <v>2260</v>
+        <v>1010</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1477,12 +1477,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1491,21 +1491,21 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6875</v>
+        <v>6890</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>487000</v>
+        <v>203000</v>
       </c>
       <c r="H29" t="n">
-        <v>4870</v>
+        <v>2030</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1514,12 +1514,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4917</v>
+        <v>2432</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>204000</v>
+        <v>226000</v>
       </c>
       <c r="H30" t="n">
-        <v>2040</v>
+        <v>2260</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1565,220 +1565,220 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8233</v>
+        <v>6875</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>287906000</v>
+        <v>487000</v>
       </c>
       <c r="H31" t="n">
-        <v>1101.400153022188</v>
+        <v>4870</v>
       </c>
       <c r="I31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2229</v>
+        <v>4917</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8012900</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>23390757000</v>
+        <v>204000</v>
       </c>
       <c r="H32" t="n">
-        <v>2919.137515755844</v>
+        <v>2040</v>
       </c>
       <c r="I32" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5983</v>
+        <v>8233</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>44800</v>
+        <v>261400</v>
       </c>
       <c r="G33" t="n">
-        <v>315399000</v>
+        <v>287906000</v>
       </c>
       <c r="H33" t="n">
-        <v>7040.15625</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I33" t="n">
-        <v>4.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G34" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H34" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I34" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G35" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H35" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I35" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5331</v>
+        <v>5983</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1481600</v>
+        <v>44800</v>
       </c>
       <c r="G36" t="n">
-        <v>5294365000</v>
+        <v>315399000</v>
       </c>
       <c r="H36" t="n">
-        <v>3573.410502159827</v>
+        <v>7040.15625</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1787,366 +1787,368 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6952</v>
+        <v>6104</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>12332900</v>
+        <v>1297500</v>
       </c>
       <c r="G37" t="n">
-        <v>14653495000</v>
+        <v>4476090000</v>
       </c>
       <c r="H37" t="n">
-        <v>1188.162962482466</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I37" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G38" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H38" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G39" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H39" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I39" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H40" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I40" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G41" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H41" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G42" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H42" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G43" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H43" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I43" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G44" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H44" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I44" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G46" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H46" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I46" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2155,72 +2157,70 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3106</v>
+        <v>3328</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>900156</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>4095263000</v>
-      </c>
-      <c r="H47" t="n">
-        <v>4549.503641591014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G48" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H48" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I48" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2229,294 +2229,294 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G49" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H49" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I49" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4619</v>
+        <v>3106</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>900156</v>
       </c>
       <c r="G50" t="n">
-        <v>119000</v>
+        <v>4095263000</v>
       </c>
       <c r="H50" t="n">
-        <v>1190</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G51" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H51" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H52" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I52" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H53" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I53" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4676</v>
+        <v>6927</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>1142700</v>
       </c>
       <c r="G54" t="n">
-        <v>242000</v>
+        <v>1023871000</v>
       </c>
       <c r="H54" t="n">
-        <v>2420</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1776</v>
+        <v>4849</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>126500</v>
+        <v>2946942</v>
       </c>
       <c r="G55" t="n">
-        <v>153399000</v>
+        <v>5148132000</v>
       </c>
       <c r="H55" t="n">
-        <v>1212.640316205534</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I55" t="n">
-        <v>1.36</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H56" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I56" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2525,257 +2525,257 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G57" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H57" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G58" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H58" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I58" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H59" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I59" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G60" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H60" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I60" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G61" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H61" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I61" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9987</v>
+        <v>4512</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3888200</v>
+        <v>2137400</v>
       </c>
       <c r="G62" t="n">
-        <v>16086019000</v>
+        <v>620573000</v>
       </c>
       <c r="H62" t="n">
-        <v>4137.137750115735</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4626</v>
+        <v>9006</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G63" t="n">
-        <v>16652257000</v>
+        <v>34824000</v>
       </c>
       <c r="H63" t="n">
-        <v>3565.648720929983</v>
+        <v>1160.8</v>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2784,331 +2784,331 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G64" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H64" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I64" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3861</v>
+        <v>9987</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G65" t="n">
-        <v>59000</v>
+        <v>16086019000</v>
       </c>
       <c r="H65" t="n">
-        <v>590</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G66" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H66" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3978</v>
+        <v>3861</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>3425686000</v>
+        <v>59000</v>
       </c>
       <c r="H67" t="n">
-        <v>1184.661617733513</v>
+        <v>590</v>
       </c>
       <c r="I67" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4452</v>
+        <v>5715</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>24347342</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>148917027000</v>
+        <v>160000</v>
       </c>
       <c r="H68" t="n">
-        <v>6116.356643776557</v>
+        <v>1600</v>
       </c>
       <c r="I68" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G69" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H69" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>9531</v>
+        <v>4452</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>19554300</v>
+        <v>24347342</v>
       </c>
       <c r="G70" t="n">
-        <v>64960321000</v>
+        <v>148917027000</v>
       </c>
       <c r="H70" t="n">
-        <v>3322.047887165483</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I70" t="n">
-        <v>5.029999999999999</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4385</v>
+        <v>9257</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>8815360</v>
+        <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>17684138000</v>
+        <v>57000</v>
       </c>
       <c r="H71" t="n">
-        <v>2006.059650428343</v>
+        <v>570</v>
       </c>
       <c r="I71" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G72" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H72" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I72" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3117,109 +3117,109 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G73" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H73" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I73" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G74" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H74" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I74" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G75" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H75" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I75" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3228,72 +3228,72 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G76" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H76" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I76" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4272</v>
+        <v>3765</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>26855100</v>
+        <v>4552900</v>
       </c>
       <c r="G77" t="n">
-        <v>29860350000</v>
+        <v>13383536000</v>
       </c>
       <c r="H77" t="n">
-        <v>1111.90611839092</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I77" t="n">
-        <v>15.75</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3302,35 +3302,35 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>8141</v>
+        <v>5482</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>100</v>
+        <v>433300</v>
       </c>
       <c r="G78" t="n">
-        <v>93000</v>
+        <v>1367192000</v>
       </c>
       <c r="H78" t="n">
-        <v>930</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3339,21 +3339,21 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>100</v>
       </c>
       <c r="G79" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H79" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -3362,493 +3362,493 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4205</v>
+        <v>4272</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>14426600</v>
+        <v>26855100</v>
       </c>
       <c r="G80" t="n">
-        <v>24829312000</v>
+        <v>29860350000</v>
       </c>
       <c r="H80" t="n">
-        <v>1721.078563209627</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I80" t="n">
-        <v>6.29</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G81" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H81" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I81" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G82" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H82" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I82" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2327</v>
+        <v>4205</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>9154320</v>
+        <v>14426600</v>
       </c>
       <c r="G83" t="n">
-        <v>23450671000</v>
+        <v>24829312000</v>
       </c>
       <c r="H83" t="n">
-        <v>2561.705402476645</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G84" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H84" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G85" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H85" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G86" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H86" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I86" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G87" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H87" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I87" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G88" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H88" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I88" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G89" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H89" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G90" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H90" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I90" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G91" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H91" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>8803</v>
+        <v>2168</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G92" t="n">
-        <v>361000</v>
+        <v>4445105000</v>
       </c>
       <c r="H92" t="n">
-        <v>3610</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3868,10 +3868,10 @@
         <v>4062075</v>
       </c>
       <c r="G93" t="n">
-        <v>20578848000</v>
+        <v>8729143000</v>
       </c>
       <c r="H93" t="n">
-        <v>5066.092575838703</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I93" t="n">
         <v>5.2</v>
@@ -3880,234 +3880,234 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>9882</v>
+        <v>8803</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2505000</v>
+        <v>100</v>
       </c>
       <c r="G94" t="n">
-        <v>5292086000</v>
+        <v>361000</v>
       </c>
       <c r="H94" t="n">
-        <v>2112.609181636727</v>
+        <v>3610</v>
       </c>
       <c r="I94" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8129</v>
+        <v>4967</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>7258230</v>
+        <v>4062075</v>
       </c>
       <c r="G95" t="n">
-        <v>24720910000</v>
+        <v>20578848000</v>
       </c>
       <c r="H95" t="n">
-        <v>3405.914389596362</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I95" t="n">
-        <v>9.460000000000001</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G96" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H96" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I96" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G97" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H97" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I97" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G98" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H98" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I98" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G99" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H99" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I99" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4116,775 +4116,775 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G100" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H100" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I100" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G101" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H101" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I101" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4042</v>
+        <v>8929</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>16459200</v>
+        <v>1260812</v>
       </c>
       <c r="G102" t="n">
-        <v>33451116000</v>
+        <v>1699255000</v>
       </c>
       <c r="H102" t="n">
-        <v>2032.365850102071</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I102" t="n">
-        <v>5.06</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3591</v>
+        <v>7278</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2846091</v>
+        <v>115400</v>
       </c>
       <c r="G103" t="n">
-        <v>6888596000</v>
+        <v>302115000</v>
       </c>
       <c r="H103" t="n">
-        <v>2420.370957920882</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I103" t="n">
-        <v>5.13</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G104" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H104" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>8923</v>
+        <v>4042</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2445600</v>
+        <v>16459200</v>
       </c>
       <c r="G105" t="n">
-        <v>3856031000</v>
+        <v>33451116000</v>
       </c>
       <c r="H105" t="n">
-        <v>1576.721867844292</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I105" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G106" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H106" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I106" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G107" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H107" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I107" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G108" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H108" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G109" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H109" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I109" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H110" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I110" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G111" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H111" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G112" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H112" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I112" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G113" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H113" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I113" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G114" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H114" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G115" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H115" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I115" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G116" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H116" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I116" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G117" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H117" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I117" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G118" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H118" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G119" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H119" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I119" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G120" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H120" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I120" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4893,35 +4893,35 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4631</v>
+        <v>7315</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6563759</v>
+        <v>6994900</v>
       </c>
       <c r="G121" t="n">
-        <v>16844475000</v>
+        <v>5874641000</v>
       </c>
       <c r="H121" t="n">
-        <v>2566.284807227078</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I121" t="n">
-        <v>6.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4930,72 +4930,72 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4293</v>
+        <v>4837</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>20896886</v>
+        <v>5428600</v>
       </c>
       <c r="G122" t="n">
-        <v>9376038000</v>
+        <v>4378021000</v>
       </c>
       <c r="H122" t="n">
-        <v>448.6811097117532</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I122" t="n">
-        <v>9.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G123" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H123" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5004,646 +5004,646 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6232</v>
+        <v>4631</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1499000</v>
+        <v>6563759</v>
       </c>
       <c r="G124" t="n">
-        <v>1369002000</v>
+        <v>16844475000</v>
       </c>
       <c r="H124" t="n">
-        <v>913.2768512341561</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I124" t="n">
-        <v>10.47</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G125" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H125" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I125" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G126" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H126" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I126" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G127" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H127" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I127" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G128" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H128" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I128" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G129" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H129" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G130" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H130" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I130" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5186</v>
+        <v>4023</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1536900</v>
+        <v>100</v>
       </c>
       <c r="G131" t="n">
-        <v>4758738000</v>
+        <v>796000</v>
       </c>
       <c r="H131" t="n">
-        <v>3096.322467304314</v>
+        <v>7960</v>
       </c>
       <c r="I131" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5947</v>
+        <v>5844</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>7446200</v>
+        <v>4998800</v>
       </c>
       <c r="G132" t="n">
-        <v>21182239000</v>
+        <v>24949147000</v>
       </c>
       <c r="H132" t="n">
-        <v>2844.704547285864</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I132" t="n">
-        <v>4.96</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8303</v>
+        <v>5186</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>20000000</v>
+        <v>1536900</v>
       </c>
       <c r="G133" t="n">
-        <v>56014500000</v>
+        <v>4758738000</v>
       </c>
       <c r="H133" t="n">
-        <v>2800.725</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I133" t="n">
-        <v>9.75</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2812</v>
+        <v>5947</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+        <v>7446200</v>
+      </c>
+      <c r="G134" t="n">
+        <v>21182239000</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2844.704547285864</v>
+      </c>
       <c r="I134" t="n">
-        <v>9.779999999999999</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5451</v>
+        <v>8303</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1752800</v>
+        <v>20000000</v>
       </c>
       <c r="G135" t="n">
-        <v>5669831000</v>
+        <v>56014500000</v>
       </c>
       <c r="H135" t="n">
-        <v>3234.727863989046</v>
+        <v>2800.725</v>
       </c>
       <c r="I135" t="n">
-        <v>5.029999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>9072</v>
+        <v>2812</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>8377400</v>
-      </c>
-      <c r="G136" t="n">
-        <v>13394541000</v>
-      </c>
-      <c r="H136" t="n">
-        <v>1598.889989734285</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
-        <v>12.74</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5194</v>
+        <v>5451</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1068798</v>
+        <v>1752800</v>
       </c>
       <c r="G137" t="n">
-        <v>997342000</v>
+        <v>5669831000</v>
       </c>
       <c r="H137" t="n">
-        <v>933.1435874692879</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I137" t="n">
-        <v>9.77</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>8871</v>
+        <v>9072</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1807700</v>
+        <v>8377400</v>
       </c>
       <c r="G138" t="n">
-        <v>3235548000</v>
+        <v>13394541000</v>
       </c>
       <c r="H138" t="n">
-        <v>1789.870000553189</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I138" t="n">
-        <v>5.050000000000001</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>5929</v>
+        <v>5194</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>11571500</v>
+        <v>1068798</v>
       </c>
       <c r="G139" t="n">
-        <v>15114770000</v>
+        <v>997342000</v>
       </c>
       <c r="H139" t="n">
-        <v>1306.206628354146</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I139" t="n">
-        <v>5.01</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>8140</v>
+        <v>8871</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1322800</v>
+        <v>1807700</v>
       </c>
       <c r="G140" t="n">
-        <v>4536170000</v>
+        <v>3235548000</v>
       </c>
       <c r="H140" t="n">
-        <v>3429.218324765649</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I140" t="n">
-        <v>5.29</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1878</v>
+        <v>5929</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3452100</v>
+        <v>11571500</v>
       </c>
       <c r="G141" t="n">
-        <v>44793976000</v>
+        <v>15114770000</v>
       </c>
       <c r="H141" t="n">
-        <v>12975.86280814577</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I141" t="n">
         <v>5.01</v>
@@ -5652,193 +5652,197 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1882</v>
+        <v>8140</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>533500</v>
+        <v>1322800</v>
       </c>
       <c r="G142" t="n">
-        <v>2009924000</v>
+        <v>4536170000</v>
       </c>
       <c r="H142" t="n">
-        <v>3767.430178069353</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I142" t="n">
-        <v>5.11</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3593</v>
+        <v>1878</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1637060</v>
+        <v>3452100</v>
       </c>
       <c r="G143" t="n">
-        <v>5502657000</v>
+        <v>44793976000</v>
       </c>
       <c r="H143" t="n">
-        <v>3361.304411567078</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I143" t="n">
-        <v>6.48</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>7157</v>
+        <v>1882</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>4536300</v>
+        <v>533500</v>
       </c>
       <c r="G144" t="n">
-        <v>4025006000</v>
+        <v>2009924000</v>
       </c>
       <c r="H144" t="n">
-        <v>887.288318673809</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I144" t="n">
-        <v>6.5</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1861</v>
+        <v>3593</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>3102784</v>
+        <v>1637060</v>
       </c>
       <c r="G145" t="n">
-        <v>8614573000</v>
+        <v>5502657000</v>
       </c>
       <c r="H145" t="n">
-        <v>2776.401128792723</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I145" t="n">
-        <v>7.07</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7350</v>
+        <v>7157</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+        <v>4536300</v>
+      </c>
+      <c r="G146" t="n">
+        <v>4025006000</v>
+      </c>
+      <c r="H146" t="n">
+        <v>887.288318673809</v>
+      </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5847,72 +5851,68 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3549</v>
+        <v>1861</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1735200</v>
+        <v>3102784</v>
       </c>
       <c r="G147" t="n">
-        <v>11532479000</v>
+        <v>8614573000</v>
       </c>
       <c r="H147" t="n">
-        <v>6646.195827570309</v>
+        <v>2776.401128792723</v>
       </c>
       <c r="I147" t="n">
-        <v>5.5</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>6770</v>
+        <v>7350</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>11259700</v>
-      </c>
-      <c r="G148" t="n">
-        <v>14161429000</v>
-      </c>
-      <c r="H148" t="n">
-        <v>1257.709264012363</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5921,274 +5921,315 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3391</v>
+        <v>3549</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>6354522</v>
+        <v>1735200</v>
       </c>
       <c r="G149" t="n">
-        <v>28876223000</v>
+        <v>11532479000</v>
       </c>
       <c r="H149" t="n">
-        <v>4544.200649553184</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I149" t="n">
-        <v>12.84</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1951</v>
+        <v>6770</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>5561200</v>
+        <v>11259700</v>
       </c>
       <c r="G150" t="n">
-        <v>12623472000</v>
+        <v>14161429000</v>
       </c>
       <c r="H150" t="n">
-        <v>2269.918722577861</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I150" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3085</v>
+        <v>3391</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1756300</v>
+        <v>6354522</v>
       </c>
       <c r="G151" t="n">
-        <v>4694343000</v>
+        <v>28876223000</v>
       </c>
       <c r="H151" t="n">
-        <v>2672.859420372374</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I151" t="n">
-        <v>5.31</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QJNN.zip</t>
+          <t>S100QNRY.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>9842</v>
+        <v>1951</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2082200</v>
+        <v>5561200</v>
       </c>
       <c r="G152" t="n">
-        <v>3059101000</v>
+        <v>12623472000</v>
       </c>
       <c r="H152" t="n">
-        <v>1469.167707232735</v>
+        <v>2269.918722577861</v>
       </c>
       <c r="I152" t="n">
-        <v>5.029999999999999</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QI52.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>9672</v>
+        <v>3085</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2410900</v>
+        <v>1756300</v>
       </c>
       <c r="G153" t="n">
-        <v>9382590000</v>
+        <v>4694343000</v>
       </c>
       <c r="H153" t="n">
-        <v>3891.73752540545</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I153" t="n">
-        <v>8.380000000000001</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100QGUZ.zip</t>
+          <t>S100QJNN.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3558</v>
+        <v>9842</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1214200</v>
+        <v>2082200</v>
       </c>
       <c r="G154" t="n">
-        <v>1538785000</v>
+        <v>3059101000</v>
       </c>
       <c r="H154" t="n">
-        <v>1267.324164058639</v>
+        <v>1469.167707232735</v>
       </c>
       <c r="I154" t="n">
-        <v>10.57</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100QF0T.zip</t>
+          <t>S100QI52.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_01_2023-03-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2329</v>
+        <v>9672</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
+        <v>2410900</v>
+      </c>
+      <c r="G155" t="n">
+        <v>9382590000</v>
+      </c>
+      <c r="H155" t="n">
+        <v>3891.73752540545</v>
+      </c>
       <c r="I155" t="n">
-        <v>9.550000000000001</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>S100QGUZ.zip</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>3558</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>1214200</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1538785000</v>
+      </c>
+      <c r="H156" t="n">
+        <v>1267.324164058639</v>
+      </c>
+      <c r="I156" t="n">
+        <v>10.57</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
           <t>S100QF8K.zip</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
-      <c r="D156" t="n">
+      <c r="D157" t="n">
         <v>2329</v>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>2023-03-13</t>
         </is>
       </c>
-      <c r="F156" t="n">
+      <c r="F157" t="n">
         <v>4463000</v>
       </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="n">
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="n">
         <v>9.550000000000001</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,21 +1070,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7378</v>
+        <v>2432</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1092,36 +1092,36 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>500400</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>698873000</v>
+        <v>226000</v>
       </c>
       <c r="H18" t="n">
-        <v>1396.628697042366</v>
+        <v>2260</v>
       </c>
       <c r="I18" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2432</v>
+        <v>7378</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1129,16 +1129,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>500400</v>
       </c>
       <c r="G19" t="n">
-        <v>226000</v>
+        <v>698873000</v>
       </c>
       <c r="H19" t="n">
-        <v>2260</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="20">
@@ -1329,21 +1329,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1351,36 +1351,36 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G25" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H25" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I25" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G26" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H26" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I26" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="27">
@@ -1699,12 +1699,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1736,12 +1736,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2400,21 +2400,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6927</v>
+        <v>4849</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2422,36 +2422,36 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1142700</v>
+        <v>2946942</v>
       </c>
       <c r="G54" t="n">
-        <v>1023871000</v>
+        <v>5148132000</v>
       </c>
       <c r="H54" t="n">
-        <v>896.0103264198827</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I54" t="n">
-        <v>5.01</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4849</v>
+        <v>6927</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2946942</v>
+        <v>1142700</v>
       </c>
       <c r="G55" t="n">
-        <v>5148132000</v>
+        <v>1023871000</v>
       </c>
       <c r="H55" t="n">
-        <v>1746.940387696806</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I55" t="n">
-        <v>5.93</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="56">
@@ -3436,7 +3436,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3569</v>
+        <v>4205</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3458,22 +3458,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>4271704</v>
+        <v>14426600</v>
       </c>
       <c r="G82" t="n">
-        <v>5808044000</v>
+        <v>24829312000</v>
       </c>
       <c r="H82" t="n">
-        <v>1359.655069733296</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I82" t="n">
-        <v>6.279999999999999</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4205</v>
+        <v>3569</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3495,16 +3495,16 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>14426600</v>
+        <v>4271704</v>
       </c>
       <c r="G83" t="n">
-        <v>24829312000</v>
+        <v>5808044000</v>
       </c>
       <c r="H83" t="n">
-        <v>1721.078563209627</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I83" t="n">
-        <v>6.29</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3769,21 +3769,21 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5541</v>
+        <v>2168</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3791,36 +3791,36 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G91" t="n">
-        <v>127000</v>
+        <v>4445105000</v>
       </c>
       <c r="H91" t="n">
-        <v>1270</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3828,27 +3828,27 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G92" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H92" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I92" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3868,10 +3868,10 @@
         <v>4062075</v>
       </c>
       <c r="G93" t="n">
-        <v>8729143000</v>
+        <v>20578848000</v>
       </c>
       <c r="H93" t="n">
-        <v>2148.936934940886</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I93" t="n">
         <v>5.2</v>
@@ -3880,21 +3880,21 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3902,36 +3902,36 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G94" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H94" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G95" t="n">
-        <v>20578848000</v>
+        <v>361000</v>
       </c>
       <c r="H95" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5323,7 +5323,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5345,22 +5345,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G133" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H133" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I133" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5947</v>
+        <v>5186</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5382,16 +5382,16 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>7446200</v>
+        <v>1536900</v>
       </c>
       <c r="G134" t="n">
-        <v>21182239000</v>
+        <v>4758738000</v>
       </c>
       <c r="H134" t="n">
-        <v>2844.704547285864</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I134" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="135">
@@ -5800,12 +5800,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7157</v>
+        <v>1861</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5822,27 +5822,27 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>4536300</v>
+        <v>3102784</v>
       </c>
       <c r="G146" t="n">
-        <v>4025006000</v>
+        <v>8614573000</v>
       </c>
       <c r="H146" t="n">
-        <v>887.288318673809</v>
+        <v>2776.401128792723</v>
       </c>
       <c r="I146" t="n">
-        <v>6.5</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1861</v>
+        <v>7157</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5859,16 +5859,16 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3102784</v>
+        <v>4536300</v>
       </c>
       <c r="G147" t="n">
-        <v>8614573000</v>
+        <v>4025006000</v>
       </c>
       <c r="H147" t="n">
-        <v>2776.401128792723</v>
+        <v>887.288318673809</v>
       </c>
       <c r="I147" t="n">
-        <v>7.07</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="148">
@@ -6200,39 +6200,6 @@
         <v>10.57</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>S100QF8K.zip</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-03-13_02_2023-03-22.csv</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>2329</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>2023-03-13</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>4463000</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="n">
-        <v>9.550000000000001</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -478,21 +478,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4676</v>
+        <v>9468</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -500,36 +500,36 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2662900</v>
+        <v>13197300</v>
       </c>
       <c r="G2" t="n">
-        <v>8365298000</v>
+        <v>39531520000</v>
       </c>
       <c r="H2" t="n">
-        <v>3141.424011416125</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I2" t="n">
-        <v>1.57</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9468</v>
+        <v>4676</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -537,16 +537,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13197300</v>
+        <v>2662900</v>
       </c>
       <c r="G3" t="n">
-        <v>39531520000</v>
+        <v>8365298000</v>
       </c>
       <c r="H3" t="n">
-        <v>2995.424821743842</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I3" t="n">
-        <v>8.859999999999999</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="4">
@@ -1070,21 +1070,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2432</v>
+        <v>7378</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1092,36 +1092,36 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>500400</v>
       </c>
       <c r="G18" t="n">
-        <v>226000</v>
+        <v>698873000</v>
       </c>
       <c r="H18" t="n">
-        <v>2260</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7378</v>
+        <v>2432</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1129,16 +1129,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>500400</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>698873000</v>
+        <v>226000</v>
       </c>
       <c r="H19" t="n">
-        <v>1396.628697042366</v>
+        <v>2260</v>
       </c>
       <c r="I19" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1329,21 +1329,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1351,36 +1351,36 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G25" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H25" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I25" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G26" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H26" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I26" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="27">
@@ -1699,12 +1699,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1736,12 +1736,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2215,21 +2215,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>9302</v>
+        <v>3106</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2237,36 +2237,36 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3799000</v>
+        <v>900156</v>
       </c>
       <c r="G49" t="n">
-        <v>5671170000</v>
+        <v>4095263000</v>
       </c>
       <c r="H49" t="n">
-        <v>1492.806001579363</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I49" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3106</v>
+        <v>9302</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>900156</v>
+        <v>3799000</v>
       </c>
       <c r="G50" t="n">
-        <v>4095263000</v>
+        <v>5671170000</v>
       </c>
       <c r="H50" t="n">
-        <v>4549.503641591014</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="51">
@@ -2400,21 +2400,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4849</v>
+        <v>6927</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2422,36 +2422,36 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2946942</v>
+        <v>1142700</v>
       </c>
       <c r="G54" t="n">
-        <v>5148132000</v>
+        <v>1023871000</v>
       </c>
       <c r="H54" t="n">
-        <v>1746.940387696806</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I54" t="n">
-        <v>5.93</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6927</v>
+        <v>4849</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1142700</v>
+        <v>2946942</v>
       </c>
       <c r="G55" t="n">
-        <v>1023871000</v>
+        <v>5148132000</v>
       </c>
       <c r="H55" t="n">
-        <v>896.0103264198827</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I55" t="n">
-        <v>5.01</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="56">
@@ -2770,21 +2770,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4626</v>
+        <v>9987</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2792,36 +2792,36 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>4670190</v>
+        <v>3888200</v>
       </c>
       <c r="G64" t="n">
-        <v>16652257000</v>
+        <v>16086019000</v>
       </c>
       <c r="H64" t="n">
-        <v>3565.648720929983</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I64" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>9987</v>
+        <v>4626</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2829,16 +2829,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3888200</v>
+        <v>4670190</v>
       </c>
       <c r="G65" t="n">
-        <v>16086019000</v>
+        <v>16652257000</v>
       </c>
       <c r="H65" t="n">
-        <v>4137.137750115735</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -3325,21 +3325,21 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8141</v>
+        <v>4272</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3347,36 +3347,36 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G79" t="n">
-        <v>93000</v>
+        <v>29860350000</v>
       </c>
       <c r="H79" t="n">
-        <v>930</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4272</v>
+        <v>8141</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3384,16 +3384,16 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>26855100</v>
+        <v>100</v>
       </c>
       <c r="G80" t="n">
-        <v>29860350000</v>
+        <v>93000</v>
       </c>
       <c r="H80" t="n">
-        <v>1111.90611839092</v>
+        <v>930</v>
       </c>
       <c r="I80" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -3769,21 +3769,21 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3791,36 +3791,36 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G91" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H91" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I91" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5541</v>
+        <v>2168</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3828,36 +3828,36 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G92" t="n">
-        <v>127000</v>
+        <v>4445105000</v>
       </c>
       <c r="H92" t="n">
-        <v>1270</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3865,27 +3865,27 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G93" t="n">
-        <v>20578848000</v>
+        <v>361000</v>
       </c>
       <c r="H93" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3905,10 +3905,10 @@
         <v>4062075</v>
       </c>
       <c r="G94" t="n">
-        <v>8729143000</v>
+        <v>20578848000</v>
       </c>
       <c r="H94" t="n">
-        <v>2148.936934940886</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I94" t="n">
         <v>5.2</v>
@@ -3917,21 +3917,21 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G95" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H95" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="96">
@@ -4250,21 +4250,21 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3591</v>
+        <v>4042</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4272,36 +4272,36 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2846091</v>
+        <v>16459200</v>
       </c>
       <c r="G104" t="n">
-        <v>6888596000</v>
+        <v>33451116000</v>
       </c>
       <c r="H104" t="n">
-        <v>2420.370957920882</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I104" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4042</v>
+        <v>3591</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4309,16 +4309,16 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>16459200</v>
+        <v>2846091</v>
       </c>
       <c r="G105" t="n">
-        <v>33451116000</v>
+        <v>6888596000</v>
       </c>
       <c r="H105" t="n">
-        <v>2032.365850102071</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I105" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="106">
@@ -4953,7 +4953,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4293</v>
+        <v>4631</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4975,22 +4975,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>20896886</v>
+        <v>6563759</v>
       </c>
       <c r="G123" t="n">
-        <v>9376038000</v>
+        <v>16844475000</v>
       </c>
       <c r="H123" t="n">
-        <v>448.6811097117532</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I123" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4631</v>
+        <v>4293</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -5012,16 +5012,16 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>6563759</v>
+        <v>20896886</v>
       </c>
       <c r="G124" t="n">
-        <v>16844475000</v>
+        <v>9376038000</v>
       </c>
       <c r="H124" t="n">
-        <v>2566.284807227078</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I124" t="n">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="125">
@@ -5323,7 +5323,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5947</v>
+        <v>5186</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5345,22 +5345,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>7446200</v>
+        <v>1536900</v>
       </c>
       <c r="G133" t="n">
-        <v>21182239000</v>
+        <v>4758738000</v>
       </c>
       <c r="H133" t="n">
-        <v>2844.704547285864</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I133" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5382,16 +5382,16 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G134" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H134" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I134" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="135">
@@ -5944,21 +5944,21 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>6770</v>
+        <v>3391</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5966,36 +5966,36 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>11259700</v>
+        <v>6354522</v>
       </c>
       <c r="G150" t="n">
-        <v>14161429000</v>
+        <v>28876223000</v>
       </c>
       <c r="H150" t="n">
-        <v>1257.709264012363</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I150" t="n">
-        <v>5.13</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3391</v>
+        <v>6770</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -6003,16 +6003,16 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>6354522</v>
+        <v>11259700</v>
       </c>
       <c r="G151" t="n">
-        <v>28876223000</v>
+        <v>14161429000</v>
       </c>
       <c r="H151" t="n">
-        <v>4544.200649553184</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I151" t="n">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="152">

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,12 +1255,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1280,10 +1280,10 @@
         <v>16322100</v>
       </c>
       <c r="G23" t="n">
-        <v>268179335000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H23" t="n">
-        <v>16430.4430802409</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I23" t="n">
         <v>5.01</v>
@@ -1292,12 +1292,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1317,10 +1317,10 @@
         <v>16322100</v>
       </c>
       <c r="G24" t="n">
-        <v>268179335457000</v>
+        <v>268179335000</v>
       </c>
       <c r="H24" t="n">
-        <v>16430443.10823975</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I24" t="n">
         <v>5.01</v>
@@ -1329,21 +1329,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1351,36 +1351,36 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G25" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H25" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I25" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G26" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H26" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I26" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="27">
@@ -2215,21 +2215,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3106</v>
+        <v>9302</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2237,36 +2237,36 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>900156</v>
+        <v>3799000</v>
       </c>
       <c r="G49" t="n">
-        <v>4095263000</v>
+        <v>5671170000</v>
       </c>
       <c r="H49" t="n">
-        <v>4549.503641591014</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>9302</v>
+        <v>3106</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3799000</v>
+        <v>900156</v>
       </c>
       <c r="G50" t="n">
-        <v>5671170000</v>
+        <v>4095263000</v>
       </c>
       <c r="H50" t="n">
-        <v>1492.806001579363</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I50" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3843,21 +3843,21 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3865,16 +3865,16 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G93" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H93" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="94">
@@ -3917,21 +3917,21 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G95" t="n">
-        <v>8729143000</v>
+        <v>361000</v>
       </c>
       <c r="H95" t="n">
-        <v>2148.936934940886</v>
+        <v>3610</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5323,7 +5323,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5345,22 +5345,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G133" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H133" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I133" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5947</v>
+        <v>5186</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5382,16 +5382,16 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>7446200</v>
+        <v>1536900</v>
       </c>
       <c r="G134" t="n">
-        <v>21182239000</v>
+        <v>4758738000</v>
       </c>
       <c r="H134" t="n">
-        <v>2844.704547285864</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I134" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="135">
@@ -5800,12 +5800,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1861</v>
+        <v>7157</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5822,27 +5822,27 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3102784</v>
+        <v>4536300</v>
       </c>
       <c r="G146" t="n">
-        <v>8614573000</v>
+        <v>4025006000</v>
       </c>
       <c r="H146" t="n">
-        <v>2776.401128792723</v>
+        <v>887.288318673809</v>
       </c>
       <c r="I146" t="n">
-        <v>7.07</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>7157</v>
+        <v>1861</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5859,16 +5859,16 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>4536300</v>
+        <v>3102784</v>
       </c>
       <c r="G147" t="n">
-        <v>4025006000</v>
+        <v>8614573000</v>
       </c>
       <c r="H147" t="n">
-        <v>887.288318673809</v>
+        <v>2776.401128792723</v>
       </c>
       <c r="I147" t="n">
-        <v>6.5</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="148">
@@ -6163,43 +6163,6 @@
         <v>8.380000000000001</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>S100QGUZ.zip</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>jplvh010000-lvh-001_E34595-000_2023-03-22_01_2023-03-28.csv</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>3558</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>2023-03-22</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>1214200</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1538785000</v>
-      </c>
-      <c r="H156" t="n">
-        <v>1267.324164058639</v>
-      </c>
-      <c r="I156" t="n">
-        <v>10.57</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,21 +663,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3549</v>
+        <v>6675</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,36 +685,36 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>13408159</v>
+        <v>314400</v>
       </c>
       <c r="G7" t="n">
-        <v>40855887000</v>
+        <v>1717778000</v>
       </c>
       <c r="H7" t="n">
-        <v>3047.091476167608</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I7" t="n">
-        <v>14.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6675</v>
+        <v>3549</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>314400</v>
+        <v>13408159</v>
       </c>
       <c r="G8" t="n">
-        <v>1717778000</v>
+        <v>40855887000</v>
       </c>
       <c r="H8" t="n">
-        <v>5463.67048346056</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I8" t="n">
-        <v>5.029999999999999</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="9">
@@ -1329,21 +1329,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1351,36 +1351,36 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G25" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H25" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I25" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G26" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H26" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I26" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="27">
@@ -1699,12 +1699,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1736,12 +1736,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2400,21 +2400,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6927</v>
+        <v>4849</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2422,36 +2422,36 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1142700</v>
+        <v>2946942</v>
       </c>
       <c r="G54" t="n">
-        <v>1023871000</v>
+        <v>5148132000</v>
       </c>
       <c r="H54" t="n">
-        <v>896.0103264198827</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I54" t="n">
-        <v>5.01</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4849</v>
+        <v>6927</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2946942</v>
+        <v>1142700</v>
       </c>
       <c r="G55" t="n">
-        <v>5148132000</v>
+        <v>1023871000</v>
       </c>
       <c r="H55" t="n">
-        <v>1746.940387696806</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I55" t="n">
-        <v>5.93</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="56">
@@ -3436,7 +3436,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4205</v>
+        <v>3569</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3458,22 +3458,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>14426600</v>
+        <v>4271704</v>
       </c>
       <c r="G82" t="n">
-        <v>24829312000</v>
+        <v>5808044000</v>
       </c>
       <c r="H82" t="n">
-        <v>1721.078563209627</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I82" t="n">
-        <v>6.29</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3569</v>
+        <v>4205</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3495,16 +3495,16 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4271704</v>
+        <v>14426600</v>
       </c>
       <c r="G83" t="n">
-        <v>5808044000</v>
+        <v>24829312000</v>
       </c>
       <c r="H83" t="n">
-        <v>1359.655069733296</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I83" t="n">
-        <v>6.279999999999999</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="84">
@@ -3843,12 +3843,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3868,10 +3868,10 @@
         <v>4062075</v>
       </c>
       <c r="G93" t="n">
-        <v>8729143000</v>
+        <v>20578848000</v>
       </c>
       <c r="H93" t="n">
-        <v>2148.936934940886</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I93" t="n">
         <v>5.2</v>
@@ -3880,21 +3880,21 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3902,36 +3902,36 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G94" t="n">
-        <v>20578848000</v>
+        <v>361000</v>
       </c>
       <c r="H94" t="n">
-        <v>5066.092575838703</v>
+        <v>3610</v>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G95" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H95" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="96">
@@ -4250,21 +4250,21 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4042</v>
+        <v>3591</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4272,36 +4272,36 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>16459200</v>
+        <v>2846091</v>
       </c>
       <c r="G104" t="n">
-        <v>33451116000</v>
+        <v>6888596000</v>
       </c>
       <c r="H104" t="n">
-        <v>2032.365850102071</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I104" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3591</v>
+        <v>4042</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4309,16 +4309,16 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2846091</v>
+        <v>16459200</v>
       </c>
       <c r="G105" t="n">
-        <v>6888596000</v>
+        <v>33451116000</v>
       </c>
       <c r="H105" t="n">
-        <v>2420.370957920882</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I105" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="106">
@@ -5323,7 +5323,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5947</v>
+        <v>5186</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5345,22 +5345,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>7446200</v>
+        <v>1536900</v>
       </c>
       <c r="G133" t="n">
-        <v>21182239000</v>
+        <v>4758738000</v>
       </c>
       <c r="H133" t="n">
-        <v>2844.704547285864</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I133" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5382,16 +5382,16 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G134" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H134" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I134" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="135">
@@ -5944,21 +5944,21 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3391</v>
+        <v>6770</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5966,36 +5966,36 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>6354522</v>
+        <v>11259700</v>
       </c>
       <c r="G150" t="n">
-        <v>28876223000</v>
+        <v>14161429000</v>
       </c>
       <c r="H150" t="n">
-        <v>4544.200649553184</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I150" t="n">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>6770</v>
+        <v>3391</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -6003,16 +6003,16 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>11259700</v>
+        <v>6354522</v>
       </c>
       <c r="G151" t="n">
-        <v>14161429000</v>
+        <v>28876223000</v>
       </c>
       <c r="H151" t="n">
-        <v>1257.709264012363</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I151" t="n">
-        <v>5.13</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="152">
@@ -6124,43 +6124,6 @@
       </c>
       <c r="I154" t="n">
         <v>5.029999999999999</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>S100QI52.zip</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-03-28_01_2023-03-30.csv</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>9672</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>2023-03-28</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>2410900</v>
-      </c>
-      <c r="G155" t="n">
-        <v>9382590000</v>
-      </c>
-      <c r="H155" t="n">
-        <v>3891.73752540545</v>
-      </c>
-      <c r="I155" t="n">
-        <v>8.380000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>zipファイル</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>csvファイル</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>提出者名</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>証券コード</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>報告義務発生日</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>保有株券等の数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>取得資金合計（円換算）</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>取得単価（円/株）</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>保有割合（報告書記載値％）</t>
         </is>
@@ -478,160 +466,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XW5T.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9468</v>
+        <v>4613</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>13197300</v>
+        <v>8982300</v>
       </c>
       <c r="G2" t="n">
-        <v>39531520000</v>
+        <v>21391558000</v>
       </c>
       <c r="H2" t="n">
-        <v>2995.424821743842</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="I2" t="n">
-        <v>8.859999999999999</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XWKV.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4676</v>
+        <v>6952</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2662900</v>
+        <v>11964800</v>
       </c>
       <c r="G3" t="n">
-        <v>8365298000</v>
+        <v>14335634000</v>
       </c>
       <c r="H3" t="n">
-        <v>3141.424011416125</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="I3" t="n">
-        <v>1.57</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XRXF.zip</t>
+          <t>S100XVQY.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3132</v>
+        <v>5423</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14653542</v>
+        <v>6884398</v>
       </c>
       <c r="G4" t="n">
-        <v>23038030000</v>
+        <v>11052572000</v>
       </c>
       <c r="H4" t="n">
-        <v>1572.181660925393</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="I4" t="n">
-        <v>8.18</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6594</v>
+        <v>4676</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>80322406</v>
+        <v>2662900</v>
       </c>
       <c r="G5" t="n">
-        <v>178330543000</v>
+        <v>8365298000</v>
       </c>
       <c r="H5" t="n">
-        <v>2220.184278344451</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I5" t="n">
-        <v>6.74</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -640,72 +628,72 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1721</v>
+        <v>9468</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7462000</v>
+        <v>13197300</v>
       </c>
       <c r="G6" t="n">
-        <v>27875864000</v>
+        <v>39531520000</v>
       </c>
       <c r="H6" t="n">
-        <v>3735.709461270437</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I6" t="n">
-        <v>5.609999999999999</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6675</v>
+        <v>3132</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>314400</v>
+        <v>14653542</v>
       </c>
       <c r="G7" t="n">
-        <v>1717778000</v>
+        <v>23038030000</v>
       </c>
       <c r="H7" t="n">
-        <v>5463.67048346056</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I7" t="n">
-        <v>5.029999999999999</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -714,257 +702,257 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3549</v>
+        <v>6594</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>13408159</v>
+        <v>80322406</v>
       </c>
       <c r="G8" t="n">
-        <v>40855887000</v>
+        <v>178330543000</v>
       </c>
       <c r="H8" t="n">
-        <v>3047.091476167608</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I8" t="n">
-        <v>14.02</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7745</v>
+        <v>1721</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1458700</v>
+        <v>7462000</v>
       </c>
       <c r="G9" t="n">
-        <v>3040190000</v>
+        <v>27875864000</v>
       </c>
       <c r="H9" t="n">
-        <v>2084.177692465894</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I9" t="n">
-        <v>5.24</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9072</v>
+        <v>6675</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8985002</v>
+        <v>314400</v>
       </c>
       <c r="G10" t="n">
-        <v>24970571000</v>
+        <v>1717778000</v>
       </c>
       <c r="H10" t="n">
-        <v>2779.139169918938</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I10" t="n">
-        <v>7.1</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4189</v>
+        <v>3549</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2040400</v>
+        <v>13408159</v>
       </c>
       <c r="G11" t="n">
-        <v>5203426000</v>
+        <v>40855887000</v>
       </c>
       <c r="H11" t="n">
-        <v>2550.198980592041</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I11" t="n">
-        <v>5.489999999999999</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6794</v>
+        <v>7745</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1252600</v>
+        <v>1458700</v>
       </c>
       <c r="G12" t="n">
-        <v>3359425000</v>
+        <v>3040190000</v>
       </c>
       <c r="H12" t="n">
-        <v>2681.96152003832</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I12" t="n">
-        <v>5.01</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2972</v>
+        <v>9072</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>8985002</v>
       </c>
       <c r="G13" t="n">
-        <v>125000</v>
+        <v>24970571000</v>
       </c>
       <c r="H13" t="n">
-        <v>125000</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2175</v>
+        <v>4189</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6792424</v>
+        <v>2040400</v>
       </c>
       <c r="G14" t="n">
-        <v>10040067000</v>
+        <v>5203426000</v>
       </c>
       <c r="H14" t="n">
-        <v>1478.127248828989</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I14" t="n">
-        <v>7.76</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,35 +961,35 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3106</v>
+        <v>6794</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>853156</v>
+        <v>1252600</v>
       </c>
       <c r="G15" t="n">
-        <v>4849339000</v>
+        <v>3359425000</v>
       </c>
       <c r="H15" t="n">
-        <v>5684.0003469471</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I15" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1010,35 +998,35 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8233</v>
+        <v>2972</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>261400</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>287906000</v>
+        <v>125000</v>
       </c>
       <c r="H16" t="n">
-        <v>1101.400153022188</v>
+        <v>125000</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1047,35 +1035,35 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2371</v>
+        <v>2175</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10372003</v>
+        <v>6792424</v>
       </c>
       <c r="G17" t="n">
-        <v>24045569000</v>
+        <v>10040067000</v>
       </c>
       <c r="H17" t="n">
-        <v>2318.314890576102</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I17" t="n">
-        <v>5.23</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1084,35 +1072,35 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7378</v>
+        <v>3106</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>500400</v>
+        <v>853156</v>
       </c>
       <c r="G18" t="n">
-        <v>698873000</v>
+        <v>4849339000</v>
       </c>
       <c r="H18" t="n">
-        <v>1396.628697042366</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I18" t="n">
-        <v>6.78</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1121,35 +1109,35 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2432</v>
+        <v>8233</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>261400</v>
       </c>
       <c r="G19" t="n">
-        <v>226000</v>
+        <v>287906000</v>
       </c>
       <c r="H19" t="n">
-        <v>2260</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1158,72 +1146,72 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8570</v>
+        <v>2371</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11014402</v>
+        <v>10372003</v>
       </c>
       <c r="G20" t="n">
-        <v>14194389000</v>
+        <v>24045569000</v>
       </c>
       <c r="H20" t="n">
-        <v>1288.711724885291</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6890</v>
+        <v>2432</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4038389</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>15954609000</v>
+        <v>226000</v>
       </c>
       <c r="H21" t="n">
-        <v>3950.736048458928</v>
+        <v>2260</v>
       </c>
       <c r="I21" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1232,331 +1220,331 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9742</v>
+        <v>7378</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1048500</v>
+        <v>500400</v>
       </c>
       <c r="G22" t="n">
-        <v>1970276000</v>
+        <v>698873000</v>
       </c>
       <c r="H22" t="n">
-        <v>1879.137815927515</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I22" t="n">
-        <v>5.02</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6201</v>
+        <v>8570</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>16322100</v>
+        <v>11014402</v>
       </c>
       <c r="G23" t="n">
-        <v>268179335457000</v>
+        <v>14194389000</v>
       </c>
       <c r="H23" t="n">
-        <v>16430443.10823975</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I23" t="n">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6201</v>
+        <v>6890</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>16322100</v>
+        <v>4038389</v>
       </c>
       <c r="G24" t="n">
-        <v>268179335000</v>
+        <v>15954609000</v>
       </c>
       <c r="H24" t="n">
-        <v>16430.4430802409</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I24" t="n">
-        <v>5.01</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6856</v>
+        <v>9742</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4180400</v>
+        <v>1048500</v>
       </c>
       <c r="G25" t="n">
-        <v>49662804000</v>
+        <v>1970276000</v>
       </c>
       <c r="H25" t="n">
-        <v>11879.91675437757</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I25" t="n">
-        <v>9.9</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G26" t="n">
-        <v>1831405000</v>
+        <v>268179335000</v>
       </c>
       <c r="H26" t="n">
-        <v>3321.975331035734</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I26" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4549</v>
+        <v>6201</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2546351</v>
+        <v>16322100</v>
       </c>
       <c r="G27" t="n">
-        <v>4958319000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H27" t="n">
-        <v>1947.225264702313</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I27" t="n">
-        <v>7.37</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7940</v>
+        <v>6856</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>4180400</v>
       </c>
       <c r="G28" t="n">
-        <v>101000</v>
+        <v>49662804000</v>
       </c>
       <c r="H28" t="n">
-        <v>1010</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6890</v>
+        <v>8011</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>551300</v>
       </c>
       <c r="G29" t="n">
-        <v>203000</v>
+        <v>1831405000</v>
       </c>
       <c r="H29" t="n">
-        <v>2030</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2432</v>
+        <v>4549</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G30" t="n">
-        <v>226000</v>
+        <v>4958319000</v>
       </c>
       <c r="H30" t="n">
-        <v>2260</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1565,21 +1553,21 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6875</v>
+        <v>7940</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>487000</v>
+        <v>101000</v>
       </c>
       <c r="H31" t="n">
-        <v>4870</v>
+        <v>1010</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1588,12 +1576,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1602,21 +1590,21 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4917</v>
+        <v>6890</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>204000</v>
+        <v>203000</v>
       </c>
       <c r="H32" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -1625,12 +1613,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1639,146 +1627,146 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8233</v>
+        <v>2432</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>287906000</v>
+        <v>226000</v>
       </c>
       <c r="H33" t="n">
-        <v>1101.400153022188</v>
+        <v>2260</v>
       </c>
       <c r="I33" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2229</v>
+        <v>6875</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8012900</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>23390757000</v>
+        <v>487000</v>
       </c>
       <c r="H34" t="n">
-        <v>2919.137515755844</v>
+        <v>4870</v>
       </c>
       <c r="I34" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5983</v>
+        <v>4917</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>44800</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>315399000</v>
+        <v>204000</v>
       </c>
       <c r="H35" t="n">
-        <v>7040.15625</v>
+        <v>2040</v>
       </c>
       <c r="I35" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5983</v>
+        <v>8233</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>44800</v>
+        <v>261400</v>
       </c>
       <c r="G36" t="n">
-        <v>315399000</v>
+        <v>287906000</v>
       </c>
       <c r="H36" t="n">
-        <v>7040.15625</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I36" t="n">
-        <v>4.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1787,220 +1775,220 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6104</v>
+        <v>2229</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1297500</v>
+        <v>8012900</v>
       </c>
       <c r="G37" t="n">
-        <v>4476090000</v>
+        <v>23390757000</v>
       </c>
       <c r="H37" t="n">
-        <v>3449.780346820809</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I37" t="n">
-        <v>5.23</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5331</v>
+        <v>5983</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1481600</v>
+        <v>44800</v>
       </c>
       <c r="G38" t="n">
-        <v>5294365000</v>
+        <v>315399000</v>
       </c>
       <c r="H38" t="n">
-        <v>3573.410502159827</v>
+        <v>7040.15625</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6952</v>
+        <v>5983</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>12332900</v>
+        <v>44800</v>
       </c>
       <c r="G39" t="n">
-        <v>14653495000</v>
+        <v>315399000</v>
       </c>
       <c r="H39" t="n">
-        <v>1188.162962482466</v>
+        <v>7040.15625</v>
       </c>
       <c r="I39" t="n">
-        <v>5.19</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6145</v>
+        <v>6104</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>1297500</v>
       </c>
       <c r="G40" t="n">
-        <v>171000</v>
+        <v>4476090000</v>
       </c>
       <c r="H40" t="n">
-        <v>1710</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8715</v>
+        <v>5331</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3810400</v>
+        <v>1481600</v>
       </c>
       <c r="G41" t="n">
-        <v>2500615000</v>
+        <v>5294365000</v>
       </c>
       <c r="H41" t="n">
-        <v>656.2604975855553</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I41" t="n">
-        <v>5.08</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8585</v>
+        <v>6952</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>8986800</v>
+        <v>12332900</v>
       </c>
       <c r="G42" t="n">
-        <v>7174886000</v>
+        <v>14653495000</v>
       </c>
       <c r="H42" t="n">
-        <v>798.3805136422309</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I42" t="n">
-        <v>5.23</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2009,21 +1997,21 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6908</v>
+        <v>6145</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>992000</v>
+        <v>171000</v>
       </c>
       <c r="H43" t="n">
-        <v>2480</v>
+        <v>1710</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2032,12 +2020,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2046,144 +2034,146 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8923</v>
+        <v>8715</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2434800</v>
+        <v>3810400</v>
       </c>
       <c r="G44" t="n">
-        <v>4266809000</v>
+        <v>2500615000</v>
       </c>
       <c r="H44" t="n">
-        <v>1752.426893379333</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9069</v>
+        <v>8585</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8793900</v>
+        <v>8986800</v>
       </c>
       <c r="G45" t="n">
-        <v>13684104000</v>
+        <v>7174886000</v>
       </c>
       <c r="H45" t="n">
-        <v>1556.090471804319</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I45" t="n">
-        <v>5.01</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1878</v>
+        <v>6908</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3475000</v>
+        <v>400</v>
       </c>
       <c r="G46" t="n">
-        <v>47745269000</v>
+        <v>992000</v>
       </c>
       <c r="H46" t="n">
-        <v>13739.64575539568</v>
+        <v>2480</v>
       </c>
       <c r="I46" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3328</v>
+        <v>8923</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2434800</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>4266809000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1752.426893379333</v>
+      </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2192,72 +2182,72 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3076</v>
+        <v>9069</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2841700</v>
+        <v>8793900</v>
       </c>
       <c r="G48" t="n">
-        <v>5705436000</v>
+        <v>13684104000</v>
       </c>
       <c r="H48" t="n">
-        <v>2007.754513143541</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I48" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>9302</v>
+        <v>1878</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3799000</v>
+        <v>3475000</v>
       </c>
       <c r="G49" t="n">
-        <v>5671170000</v>
+        <v>47745269000</v>
       </c>
       <c r="H49" t="n">
-        <v>1492.806001579363</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I49" t="n">
-        <v>5.07</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2266,243 +2256,241 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3106</v>
+        <v>3328</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>900156</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>4095263000</v>
-      </c>
-      <c r="H50" t="n">
-        <v>4549.503641591014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>9684</v>
+        <v>3076</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6704059</v>
+        <v>2841700</v>
       </c>
       <c r="G51" t="n">
-        <v>42054369000</v>
+        <v>5705436000</v>
       </c>
       <c r="H51" t="n">
-        <v>6272.971195510064</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I51" t="n">
-        <v>5.47</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4619</v>
+        <v>3106</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>900156</v>
       </c>
       <c r="G52" t="n">
-        <v>119000</v>
+        <v>4095263000</v>
       </c>
       <c r="H52" t="n">
-        <v>1190</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6332</v>
+        <v>9302</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>3799000</v>
       </c>
       <c r="G53" t="n">
-        <v>141000</v>
+        <v>5671170000</v>
       </c>
       <c r="H53" t="n">
-        <v>1410</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4849</v>
+        <v>9684</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2946942</v>
+        <v>6704059</v>
       </c>
       <c r="G54" t="n">
-        <v>5148132000</v>
+        <v>42054369000</v>
       </c>
       <c r="H54" t="n">
-        <v>1746.940387696806</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I54" t="n">
-        <v>5.93</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6927</v>
+        <v>4619</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G55" t="n">
-        <v>1023871000</v>
+        <v>119000</v>
       </c>
       <c r="H55" t="n">
-        <v>896.0103264198827</v>
+        <v>1190</v>
       </c>
       <c r="I55" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4676</v>
+        <v>6332</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>242000</v>
+        <v>141000</v>
       </c>
       <c r="H56" t="n">
-        <v>2420</v>
+        <v>1410</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -2511,109 +2499,109 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G57" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H57" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I57" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3963</v>
+        <v>4849</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1507900</v>
+        <v>2946942</v>
       </c>
       <c r="G58" t="n">
-        <v>635874000</v>
+        <v>5148132000</v>
       </c>
       <c r="H58" t="n">
-        <v>421.6950726175476</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I58" t="n">
-        <v>5.18</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6923</v>
+        <v>4676</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>256000</v>
+        <v>242000</v>
       </c>
       <c r="H59" t="n">
-        <v>2560</v>
+        <v>2420</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2622,12 +2610,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2636,109 +2624,109 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6890</v>
+        <v>1776</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>30000</v>
+        <v>126500</v>
       </c>
       <c r="G60" t="n">
-        <v>71610000</v>
+        <v>153399000</v>
       </c>
       <c r="H60" t="n">
-        <v>2387</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I60" t="n">
-        <v>0.06</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3132</v>
+        <v>3963</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>8970900</v>
+        <v>1507900</v>
       </c>
       <c r="G61" t="n">
-        <v>10240398000</v>
+        <v>635874000</v>
       </c>
       <c r="H61" t="n">
-        <v>1141.512891683109</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I61" t="n">
-        <v>5.01</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4512</v>
+        <v>6923</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2137400</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>620573000</v>
+        <v>256000</v>
       </c>
       <c r="H62" t="n">
-        <v>290.3401328717133</v>
+        <v>2560</v>
       </c>
       <c r="I62" t="n">
-        <v>6.140000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2747,220 +2735,220 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9006</v>
+        <v>6890</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>30000</v>
       </c>
       <c r="G63" t="n">
-        <v>34824000</v>
+        <v>71610000</v>
       </c>
       <c r="H63" t="n">
-        <v>1160.8</v>
+        <v>2387</v>
       </c>
       <c r="I63" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>9987</v>
+        <v>3132</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3888200</v>
+        <v>8970900</v>
       </c>
       <c r="G64" t="n">
-        <v>16086019000</v>
+        <v>10240398000</v>
       </c>
       <c r="H64" t="n">
-        <v>4137.137750115735</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4626</v>
+        <v>4512</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4670190</v>
+        <v>2137400</v>
       </c>
       <c r="G65" t="n">
-        <v>16652257000</v>
+        <v>620573000</v>
       </c>
       <c r="H65" t="n">
-        <v>3565.648720929983</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I65" t="n">
-        <v>8</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7732</v>
+        <v>9006</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>7995900</v>
+        <v>30000</v>
       </c>
       <c r="G66" t="n">
-        <v>16678425000</v>
+        <v>34824000</v>
       </c>
       <c r="H66" t="n">
-        <v>2085.872134468915</v>
+        <v>1160.8</v>
       </c>
       <c r="I66" t="n">
-        <v>7.380000000000001</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3861</v>
+        <v>9987</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G67" t="n">
-        <v>59000</v>
+        <v>16086019000</v>
       </c>
       <c r="H67" t="n">
-        <v>590</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5715</v>
+        <v>4626</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>100</v>
+        <v>4670190</v>
       </c>
       <c r="G68" t="n">
-        <v>160000</v>
+        <v>16652257000</v>
       </c>
       <c r="H68" t="n">
-        <v>1600</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2969,72 +2957,72 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3978</v>
+        <v>7732</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2891700</v>
+        <v>7995900</v>
       </c>
       <c r="G69" t="n">
-        <v>3425686000</v>
+        <v>16678425000</v>
       </c>
       <c r="H69" t="n">
-        <v>1184.661617733513</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I69" t="n">
-        <v>7.12</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4452</v>
+        <v>3861</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>24347342</v>
+        <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>148917027000</v>
+        <v>59000</v>
       </c>
       <c r="H70" t="n">
-        <v>6116.356643776557</v>
+        <v>590</v>
       </c>
       <c r="I70" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3043,21 +3031,21 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>9257</v>
+        <v>5715</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>57000</v>
+        <v>160000</v>
       </c>
       <c r="H71" t="n">
-        <v>570</v>
+        <v>1600</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -3066,49 +3054,49 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>9531</v>
+        <v>3978</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>19554300</v>
+        <v>2891700</v>
       </c>
       <c r="G72" t="n">
-        <v>64960321000</v>
+        <v>3425686000</v>
       </c>
       <c r="H72" t="n">
-        <v>3322.047887165483</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I72" t="n">
-        <v>5.029999999999999</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3117,294 +3105,294 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4385</v>
+        <v>4452</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>8815360</v>
+        <v>24347342</v>
       </c>
       <c r="G73" t="n">
-        <v>17684138000</v>
+        <v>148917027000</v>
       </c>
       <c r="H73" t="n">
-        <v>2006.059650428343</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I73" t="n">
-        <v>5.37</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7984</v>
+        <v>9257</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6096500</v>
+        <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>13153972000</v>
+        <v>57000</v>
       </c>
       <c r="H74" t="n">
-        <v>2157.626835069302</v>
+        <v>570</v>
       </c>
       <c r="I74" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1973</v>
+        <v>9531</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>8973383</v>
+        <v>19554300</v>
       </c>
       <c r="G75" t="n">
-        <v>24947403000</v>
+        <v>64960321000</v>
       </c>
       <c r="H75" t="n">
-        <v>2780.155823060266</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I75" t="n">
-        <v>6.01</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6908</v>
+        <v>4385</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>502000</v>
+        <v>8815360</v>
       </c>
       <c r="G76" t="n">
-        <v>1257178000</v>
+        <v>17684138000</v>
       </c>
       <c r="H76" t="n">
-        <v>2504.338645418327</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I76" t="n">
-        <v>2.04</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3765</v>
+        <v>7984</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4552900</v>
+        <v>6096500</v>
       </c>
       <c r="G77" t="n">
-        <v>13383536000</v>
+        <v>13153972000</v>
       </c>
       <c r="H77" t="n">
-        <v>2939.562915943684</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I77" t="n">
-        <v>5.47</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5482</v>
+        <v>1973</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>433300</v>
+        <v>8973383</v>
       </c>
       <c r="G78" t="n">
-        <v>1367192000</v>
+        <v>24947403000</v>
       </c>
       <c r="H78" t="n">
-        <v>3155.301177013616</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I78" t="n">
-        <v>2.18</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4272</v>
+        <v>6908</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>26855100</v>
+        <v>502000</v>
       </c>
       <c r="G79" t="n">
-        <v>29860350000</v>
+        <v>1257178000</v>
       </c>
       <c r="H79" t="n">
-        <v>1111.90611839092</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I79" t="n">
-        <v>15.75</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G80" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H80" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3413,294 +3401,294 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6145</v>
+        <v>5482</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>100</v>
+        <v>433300</v>
       </c>
       <c r="G81" t="n">
-        <v>171000</v>
+        <v>1367192000</v>
       </c>
       <c r="H81" t="n">
-        <v>1710</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3569</v>
+        <v>4272</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>4271704</v>
+        <v>26855100</v>
       </c>
       <c r="G82" t="n">
-        <v>5808044000</v>
+        <v>29860350000</v>
       </c>
       <c r="H82" t="n">
-        <v>1359.655069733296</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I82" t="n">
-        <v>6.279999999999999</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4205</v>
+        <v>8141</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G83" t="n">
-        <v>24829312000</v>
+        <v>93000</v>
       </c>
       <c r="H83" t="n">
-        <v>1721.078563209627</v>
+        <v>930</v>
       </c>
       <c r="I83" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6516</v>
+        <v>6145</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>679500</v>
+        <v>100</v>
       </c>
       <c r="G84" t="n">
-        <v>4792335000</v>
+        <v>171000</v>
       </c>
       <c r="H84" t="n">
-        <v>7052.737306843267</v>
+        <v>1710</v>
       </c>
       <c r="I84" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2327</v>
+        <v>4205</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>9154320</v>
+        <v>14426600</v>
       </c>
       <c r="G85" t="n">
-        <v>23450671000</v>
+        <v>24829312000</v>
       </c>
       <c r="H85" t="n">
-        <v>2561.705402476645</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3989</v>
+        <v>3569</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1206000</v>
+        <v>4271704</v>
       </c>
       <c r="G86" t="n">
-        <v>787604000</v>
+        <v>5808044000</v>
       </c>
       <c r="H86" t="n">
-        <v>653.0713101160862</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I86" t="n">
-        <v>5.2</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6908</v>
+        <v>6516</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>100</v>
+        <v>679500</v>
       </c>
       <c r="G87" t="n">
-        <v>288000</v>
+        <v>4792335000</v>
       </c>
       <c r="H87" t="n">
-        <v>2880</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5988</v>
+        <v>2327</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>527300</v>
+        <v>9154320</v>
       </c>
       <c r="G88" t="n">
-        <v>1212090000</v>
+        <v>23450671000</v>
       </c>
       <c r="H88" t="n">
-        <v>2298.672482457804</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I88" t="n">
-        <v>1.42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3709,72 +3697,72 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3529</v>
+        <v>3989</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>998000</v>
+        <v>1206000</v>
       </c>
       <c r="G89" t="n">
-        <v>667598000</v>
+        <v>787604000</v>
       </c>
       <c r="H89" t="n">
-        <v>668.9358717434869</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I89" t="n">
-        <v>5.76</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7305</v>
+        <v>6908</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>309800</v>
+        <v>100</v>
       </c>
       <c r="G90" t="n">
-        <v>1321438000</v>
+        <v>288000</v>
       </c>
       <c r="H90" t="n">
-        <v>4265.455132343447</v>
+        <v>2880</v>
       </c>
       <c r="I90" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3783,391 +3771,391 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5541</v>
+        <v>5988</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>100</v>
+        <v>527300</v>
       </c>
       <c r="G91" t="n">
-        <v>127000</v>
+        <v>1212090000</v>
       </c>
       <c r="H91" t="n">
-        <v>1270</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2168</v>
+        <v>3529</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2094200</v>
+        <v>998000</v>
       </c>
       <c r="G92" t="n">
-        <v>4445105000</v>
+        <v>667598000</v>
       </c>
       <c r="H92" t="n">
-        <v>2122.579027791042</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I92" t="n">
-        <v>5.02</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4967</v>
+        <v>7305</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>4062075</v>
+        <v>309800</v>
       </c>
       <c r="G93" t="n">
-        <v>20578848000</v>
+        <v>1321438000</v>
       </c>
       <c r="H93" t="n">
-        <v>5066.092575838703</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8803</v>
+        <v>2168</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G94" t="n">
-        <v>361000</v>
+        <v>4445105000</v>
       </c>
       <c r="H94" t="n">
-        <v>3610</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G95" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H95" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G96" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H96" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I96" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8129</v>
+        <v>8803</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>7258230</v>
+        <v>100</v>
       </c>
       <c r="G97" t="n">
-        <v>24720910000</v>
+        <v>361000</v>
       </c>
       <c r="H97" t="n">
-        <v>3405.914389596362</v>
+        <v>3610</v>
       </c>
       <c r="I97" t="n">
-        <v>9.460000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2206</v>
+        <v>4967</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3462600</v>
+        <v>4062075</v>
       </c>
       <c r="G98" t="n">
-        <v>14385811000</v>
+        <v>8729143000</v>
       </c>
       <c r="H98" t="n">
-        <v>4154.626869982095</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I98" t="n">
-        <v>5.06</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3666</v>
+        <v>9882</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1053200</v>
+        <v>2505000</v>
       </c>
       <c r="G99" t="n">
-        <v>663809000</v>
+        <v>5292086000</v>
       </c>
       <c r="H99" t="n">
-        <v>630.278199772123</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I99" t="n">
-        <v>5.16</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4347</v>
+        <v>8129</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>614893</v>
+        <v>7258230</v>
       </c>
       <c r="G100" t="n">
-        <v>940560000</v>
+        <v>24720910000</v>
       </c>
       <c r="H100" t="n">
-        <v>1529.631984751819</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I100" t="n">
-        <v>8.200000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>8129</v>
+        <v>2206</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3886330</v>
+        <v>3462600</v>
       </c>
       <c r="G101" t="n">
-        <v>10549885000</v>
+        <v>14385811000</v>
       </c>
       <c r="H101" t="n">
-        <v>2714.613787300615</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I101" t="n">
         <v>5.06</v>
@@ -4176,12 +4164,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4190,72 +4178,72 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8929</v>
+        <v>3666</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1260812</v>
+        <v>1053200</v>
       </c>
       <c r="G102" t="n">
-        <v>1699255000</v>
+        <v>663809000</v>
       </c>
       <c r="H102" t="n">
-        <v>1347.74653160027</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I102" t="n">
-        <v>5.140000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>7278</v>
+        <v>4347</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>115400</v>
+        <v>614893</v>
       </c>
       <c r="G103" t="n">
-        <v>302115000</v>
+        <v>940560000</v>
       </c>
       <c r="H103" t="n">
-        <v>2617.980935875217</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I103" t="n">
-        <v>0.24</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4264,72 +4252,72 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3591</v>
+        <v>8129</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2846091</v>
+        <v>3886330</v>
       </c>
       <c r="G104" t="n">
-        <v>6888596000</v>
+        <v>10549885000</v>
       </c>
       <c r="H104" t="n">
-        <v>2420.370957920882</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I104" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4042</v>
+        <v>8929</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>16459200</v>
+        <v>1260812</v>
       </c>
       <c r="G105" t="n">
-        <v>33451116000</v>
+        <v>1699255000</v>
       </c>
       <c r="H105" t="n">
-        <v>2032.365850102071</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I105" t="n">
-        <v>5.06</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4338,257 +4326,257 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4521</v>
+        <v>7278</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>100</v>
+        <v>115400</v>
       </c>
       <c r="G106" t="n">
-        <v>353000</v>
+        <v>302115000</v>
       </c>
       <c r="H106" t="n">
-        <v>3530</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>8923</v>
+        <v>4042</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2445600</v>
+        <v>16459200</v>
       </c>
       <c r="G107" t="n">
-        <v>3856031000</v>
+        <v>33451116000</v>
       </c>
       <c r="H107" t="n">
-        <v>1576.721867844292</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I107" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4347</v>
+        <v>3591</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>400493</v>
+        <v>2846091</v>
       </c>
       <c r="G108" t="n">
-        <v>580713000</v>
+        <v>6888596000</v>
       </c>
       <c r="H108" t="n">
-        <v>1449.995380693296</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I108" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>9024</v>
+        <v>4521</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>16207437</v>
+        <v>100</v>
       </c>
       <c r="G109" t="n">
-        <v>27823532000</v>
+        <v>353000</v>
       </c>
       <c r="H109" t="n">
-        <v>1716.713876475349</v>
+        <v>3530</v>
       </c>
       <c r="I109" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1518</v>
+        <v>8923</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>100</v>
+        <v>2445600</v>
       </c>
       <c r="G110" t="n">
-        <v>292000</v>
+        <v>3856031000</v>
       </c>
       <c r="H110" t="n">
-        <v>2920</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>7731</v>
+        <v>4347</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>17639800</v>
+        <v>400493</v>
       </c>
       <c r="G111" t="n">
-        <v>26675255000</v>
+        <v>580713000</v>
       </c>
       <c r="H111" t="n">
-        <v>1512.21980974841</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I111" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4536</v>
+        <v>9024</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>18290500</v>
+        <v>16207437</v>
       </c>
       <c r="G112" t="n">
-        <v>24591924000</v>
+        <v>27823532000</v>
       </c>
       <c r="H112" t="n">
-        <v>1344.518957928979</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I112" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4597,21 +4585,21 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4185</v>
+        <v>1518</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F113" t="n">
         <v>100</v>
       </c>
       <c r="G113" t="n">
-        <v>405000</v>
+        <v>292000</v>
       </c>
       <c r="H113" t="n">
-        <v>4050</v>
+        <v>2920</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -4620,86 +4608,86 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4549</v>
+        <v>7731</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2006900</v>
+        <v>17639800</v>
       </c>
       <c r="G114" t="n">
-        <v>3367745000</v>
+        <v>26675255000</v>
       </c>
       <c r="H114" t="n">
-        <v>1678.083113259255</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I114" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>9627</v>
+        <v>4536</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3401100</v>
+        <v>18290500</v>
       </c>
       <c r="G115" t="n">
-        <v>9648726000</v>
+        <v>24591924000</v>
       </c>
       <c r="H115" t="n">
-        <v>2836.942753814942</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I115" t="n">
-        <v>9.6</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4708,21 +4696,21 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>8304</v>
+        <v>4185</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F116" t="n">
         <v>100</v>
       </c>
       <c r="G116" t="n">
-        <v>219000</v>
+        <v>405000</v>
       </c>
       <c r="H116" t="n">
-        <v>2190</v>
+        <v>4050</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -4731,12 +4719,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4745,257 +4733,257 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3328</v>
+        <v>4549</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>845300</v>
+        <v>2006900</v>
       </c>
       <c r="G117" t="n">
-        <v>1219326000</v>
+        <v>3367745000</v>
       </c>
       <c r="H117" t="n">
-        <v>1442.477227019993</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I117" t="n">
-        <v>6.54</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>675500</v>
+        <v>3401100</v>
       </c>
       <c r="G118" t="n">
-        <v>976503000</v>
+        <v>9648726000</v>
       </c>
       <c r="H118" t="n">
-        <v>1445.60029607698</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I118" t="n">
-        <v>5.220000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>8818</v>
+        <v>8304</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2505000</v>
+        <v>100</v>
       </c>
       <c r="G119" t="n">
-        <v>3361654000</v>
+        <v>219000</v>
       </c>
       <c r="H119" t="n">
-        <v>1341.977644710579</v>
+        <v>2190</v>
       </c>
       <c r="I119" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>100</v>
+        <v>845300</v>
       </c>
       <c r="G120" t="n">
-        <v>117000</v>
+        <v>1219326000</v>
       </c>
       <c r="H120" t="n">
-        <v>1170</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>7315</v>
+        <v>3328</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6994900</v>
+        <v>675500</v>
       </c>
       <c r="G121" t="n">
-        <v>5874641000</v>
+        <v>976503000</v>
       </c>
       <c r="H121" t="n">
-        <v>839.8463166020958</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I121" t="n">
-        <v>14.23</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4837</v>
+        <v>8818</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>5428600</v>
+        <v>2505000</v>
       </c>
       <c r="G122" t="n">
-        <v>4378021000</v>
+        <v>3361654000</v>
       </c>
       <c r="H122" t="n">
-        <v>806.4733080352208</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I122" t="n">
-        <v>9.74</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4631</v>
+        <v>5541</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>6563759</v>
+        <v>100</v>
       </c>
       <c r="G123" t="n">
-        <v>16844475000</v>
+        <v>117000</v>
       </c>
       <c r="H123" t="n">
-        <v>2566.284807227078</v>
+        <v>1170</v>
       </c>
       <c r="I123" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5004,72 +4992,72 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4293</v>
+        <v>7315</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>20896886</v>
+        <v>6994900</v>
       </c>
       <c r="G124" t="n">
-        <v>9376038000</v>
+        <v>5874641000</v>
       </c>
       <c r="H124" t="n">
-        <v>448.6811097117532</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I124" t="n">
-        <v>9.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5449</v>
+        <v>4837</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2114100</v>
+        <v>5428600</v>
       </c>
       <c r="G125" t="n">
-        <v>3695597000</v>
+        <v>4378021000</v>
       </c>
       <c r="H125" t="n">
-        <v>1748.071046781136</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I125" t="n">
-        <v>5</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5078,109 +5066,109 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6232</v>
+        <v>4293</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1499000</v>
+        <v>20896886</v>
       </c>
       <c r="G126" t="n">
-        <v>1369002000</v>
+        <v>9376038000</v>
       </c>
       <c r="H126" t="n">
-        <v>913.2768512341561</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I126" t="n">
-        <v>10.47</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6237</v>
+        <v>4631</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1129500</v>
+        <v>6563759</v>
       </c>
       <c r="G127" t="n">
-        <v>1537738000</v>
+        <v>16844475000</v>
       </c>
       <c r="H127" t="n">
-        <v>1361.432492253209</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I127" t="n">
-        <v>5.02</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4987</v>
+        <v>5449</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1543800</v>
+        <v>2114100</v>
       </c>
       <c r="G128" t="n">
-        <v>874286000</v>
+        <v>3695597000</v>
       </c>
       <c r="H128" t="n">
-        <v>566.3207669387226</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I128" t="n">
-        <v>5.779999999999999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5189,401 +5177,401 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4739</v>
+        <v>6232</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>15400600</v>
+        <v>1499000</v>
       </c>
       <c r="G129" t="n">
-        <v>66216726000</v>
+        <v>1369002000</v>
       </c>
       <c r="H129" t="n">
-        <v>4299.619884939548</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I129" t="n">
-        <v>6.419999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2501</v>
+        <v>6237</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>4010500</v>
+        <v>1129500</v>
       </c>
       <c r="G130" t="n">
-        <v>10817766000</v>
+        <v>1537738000</v>
       </c>
       <c r="H130" t="n">
-        <v>2697.360927565142</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I130" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4023</v>
+        <v>4987</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>100</v>
+        <v>1543800</v>
       </c>
       <c r="G131" t="n">
-        <v>796000</v>
+        <v>874286000</v>
       </c>
       <c r="H131" t="n">
-        <v>7960</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5844</v>
+        <v>4739</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>4998800</v>
+        <v>15400600</v>
       </c>
       <c r="G132" t="n">
-        <v>24949147000</v>
+        <v>66216726000</v>
       </c>
       <c r="H132" t="n">
-        <v>4991.027246539169</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I132" t="n">
-        <v>6.59</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5186</v>
+        <v>2501</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1536900</v>
+        <v>4010500</v>
       </c>
       <c r="G133" t="n">
-        <v>4758738000</v>
+        <v>10817766000</v>
       </c>
       <c r="H133" t="n">
-        <v>3096.322467304314</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I133" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5947</v>
+        <v>4023</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>7446200</v>
+        <v>100</v>
       </c>
       <c r="G134" t="n">
-        <v>21182239000</v>
+        <v>796000</v>
       </c>
       <c r="H134" t="n">
-        <v>2844.704547285864</v>
+        <v>7960</v>
       </c>
       <c r="I134" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>8303</v>
+        <v>5844</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>20000000</v>
+        <v>4998800</v>
       </c>
       <c r="G135" t="n">
-        <v>56014500000</v>
+        <v>24949147000</v>
       </c>
       <c r="H135" t="n">
-        <v>2800.725</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I135" t="n">
-        <v>9.75</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2812</v>
+        <v>5947</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+        <v>7446200</v>
+      </c>
+      <c r="G136" t="n">
+        <v>21182239000</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2844.704547285864</v>
+      </c>
       <c r="I136" t="n">
-        <v>9.779999999999999</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5451</v>
+        <v>5186</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1752800</v>
+        <v>1536900</v>
       </c>
       <c r="G137" t="n">
-        <v>5669831000</v>
+        <v>4758738000</v>
       </c>
       <c r="H137" t="n">
-        <v>3234.727863989046</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I137" t="n">
-        <v>5.029999999999999</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>9072</v>
+        <v>8303</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>8377400</v>
+        <v>20000000</v>
       </c>
       <c r="G138" t="n">
-        <v>13394541000</v>
+        <v>56014500000</v>
       </c>
       <c r="H138" t="n">
-        <v>1598.889989734285</v>
+        <v>2800.725</v>
       </c>
       <c r="I138" t="n">
-        <v>12.74</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>5194</v>
+        <v>2812</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1068798</v>
-      </c>
-      <c r="G139" t="n">
-        <v>997342000</v>
-      </c>
-      <c r="H139" t="n">
-        <v>933.1435874692879</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5592,327 +5580,331 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>8871</v>
+        <v>5451</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1807700</v>
+        <v>1752800</v>
       </c>
       <c r="G140" t="n">
-        <v>3235548000</v>
+        <v>5669831000</v>
       </c>
       <c r="H140" t="n">
-        <v>1789.870000553189</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I140" t="n">
-        <v>5.050000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>5929</v>
+        <v>9072</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>11571500</v>
+        <v>8377400</v>
       </c>
       <c r="G141" t="n">
-        <v>15114770000</v>
+        <v>13394541000</v>
       </c>
       <c r="H141" t="n">
-        <v>1306.206628354146</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I141" t="n">
-        <v>5.01</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>8140</v>
+        <v>5194</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1322800</v>
+        <v>1068798</v>
       </c>
       <c r="G142" t="n">
-        <v>4536170000</v>
+        <v>997342000</v>
       </c>
       <c r="H142" t="n">
-        <v>3429.218324765649</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I142" t="n">
-        <v>5.29</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1878</v>
+        <v>8871</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3452100</v>
+        <v>1807700</v>
       </c>
       <c r="G143" t="n">
-        <v>44793976000</v>
+        <v>3235548000</v>
       </c>
       <c r="H143" t="n">
-        <v>12975.86280814577</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I143" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1882</v>
+        <v>5929</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>533500</v>
+        <v>11571500</v>
       </c>
       <c r="G144" t="n">
-        <v>2009924000</v>
+        <v>15114770000</v>
       </c>
       <c r="H144" t="n">
-        <v>3767.430178069353</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I144" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3593</v>
+        <v>8140</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1637060</v>
+        <v>1322800</v>
       </c>
       <c r="G145" t="n">
-        <v>5502657000</v>
+        <v>4536170000</v>
       </c>
       <c r="H145" t="n">
-        <v>3361.304411567078</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I145" t="n">
-        <v>6.48</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7157</v>
+        <v>1878</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>4536300</v>
+        <v>3452100</v>
       </c>
       <c r="G146" t="n">
-        <v>4025006000</v>
+        <v>44793976000</v>
       </c>
       <c r="H146" t="n">
-        <v>887.288318673809</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I146" t="n">
-        <v>6.5</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1861</v>
+        <v>1882</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3102784</v>
+        <v>533500</v>
       </c>
       <c r="G147" t="n">
-        <v>8614573000</v>
+        <v>2009924000</v>
       </c>
       <c r="H147" t="n">
-        <v>2776.401128792723</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I147" t="n">
-        <v>7.07</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>7350</v>
+        <v>3593</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
+        <v>1637060</v>
+      </c>
+      <c r="G148" t="n">
+        <v>5502657000</v>
+      </c>
+      <c r="H148" t="n">
+        <v>3361.304411567078</v>
+      </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5921,146 +5913,142 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3549</v>
+        <v>7157</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1735200</v>
+        <v>4536300</v>
       </c>
       <c r="G149" t="n">
-        <v>11532479000</v>
+        <v>4025006000</v>
       </c>
       <c r="H149" t="n">
-        <v>6646.195827570309</v>
+        <v>887.288318673809</v>
       </c>
       <c r="I149" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>6770</v>
+        <v>1861</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>11259700</v>
+        <v>3102784</v>
       </c>
       <c r="G150" t="n">
-        <v>14161429000</v>
+        <v>8614573000</v>
       </c>
       <c r="H150" t="n">
-        <v>1257.709264012363</v>
+        <v>2776.401128792723</v>
       </c>
       <c r="I150" t="n">
-        <v>5.13</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3391</v>
+        <v>7350</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>6354522</v>
-      </c>
-      <c r="G151" t="n">
-        <v>28876223000</v>
-      </c>
-      <c r="H151" t="n">
-        <v>4544.200649553184</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>12.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1951</v>
+        <v>3549</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>5561200</v>
+        <v>1735200</v>
       </c>
       <c r="G152" t="n">
-        <v>12623472000</v>
+        <v>11532479000</v>
       </c>
       <c r="H152" t="n">
-        <v>2269.918722577861</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I152" t="n">
-        <v>5.06</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QNNV.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6069,60 +6057,171 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3085</v>
+        <v>6770</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1756300</v>
+        <v>11259700</v>
       </c>
       <c r="G153" t="n">
-        <v>4694343000</v>
+        <v>14161429000</v>
       </c>
       <c r="H153" t="n">
-        <v>2672.859420372374</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I153" t="n">
-        <v>5.31</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>S100QRUW.zip</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>3391</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>6354522</v>
+      </c>
+      <c r="G154" t="n">
+        <v>28876223000</v>
+      </c>
+      <c r="H154" t="n">
+        <v>4544.200649553184</v>
+      </c>
+      <c r="I154" t="n">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>S100QNRY.zip</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>5561200</v>
+      </c>
+      <c r="G155" t="n">
+        <v>12623472000</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2269.918722577861</v>
+      </c>
+      <c r="I155" t="n">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>S100QNNV.zip</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>3085</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>1756300</v>
+      </c>
+      <c r="G156" t="n">
+        <v>4694343000</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2672.859420372374</v>
+      </c>
+      <c r="I156" t="n">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
           <t>S100QJNN.zip</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="D154" t="n">
+      <c r="D157" t="n">
         <v>9842</v>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>2023-03-30</t>
         </is>
       </c>
-      <c r="F154" t="n">
+      <c r="F157" t="n">
         <v>2082200</v>
       </c>
-      <c r="G154" t="n">
+      <c r="G157" t="n">
         <v>3059101000</v>
       </c>
-      <c r="H154" t="n">
+      <c r="H157" t="n">
         <v>1469.167707232735</v>
       </c>
-      <c r="I154" t="n">
+      <c r="I157" t="n">
         <v>5.029999999999999</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6188,43 +6188,6 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>S100QJNN.zip</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>jplvh020000-lvh-001_E35393-000_2023-03-30_01_2023-04-06.csv</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>9842</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>2023-03-30</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>2082200</v>
-      </c>
-      <c r="G157" t="n">
-        <v>3059101000</v>
-      </c>
-      <c r="H157" t="n">
-        <v>1469.167707232735</v>
-      </c>
-      <c r="I157" t="n">
-        <v>5.029999999999999</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,95 +466,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XW5T.zip</t>
+          <t>S100XXO7.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4613</v>
+        <v>4626</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8982300</v>
+        <v>17384460</v>
       </c>
       <c r="G2" t="n">
-        <v>21391558000</v>
+        <v>38239610000</v>
       </c>
       <c r="H2" t="n">
-        <v>2381.523440544182</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="I2" t="n">
-        <v>5.050000000000001</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XWKV.zip</t>
+          <t>S100XW5T.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6952</v>
+        <v>4613</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11964800</v>
+        <v>8982300</v>
       </c>
       <c r="G3" t="n">
-        <v>14335634000</v>
+        <v>21391558000</v>
       </c>
       <c r="H3" t="n">
-        <v>1198.150742177053</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="I3" t="n">
-        <v>5.029999999999999</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XVQY.zip</t>
+          <t>S100XWKV.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5423</v>
+        <v>6952</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -562,73 +562,73 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6884398</v>
+        <v>11964800</v>
       </c>
       <c r="G4" t="n">
-        <v>11052572000</v>
+        <v>14335634000</v>
       </c>
       <c r="H4" t="n">
-        <v>1605.452212379354</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="I4" t="n">
-        <v>6.25</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XVQY.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4676</v>
+        <v>5423</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2662900</v>
+        <v>6884398</v>
       </c>
       <c r="G5" t="n">
-        <v>8365298000</v>
+        <v>11052572000</v>
       </c>
       <c r="H5" t="n">
-        <v>3141.424011416125</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="I5" t="n">
-        <v>1.57</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9468</v>
+        <v>4676</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -636,101 +636,101 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13197300</v>
+        <v>2662900</v>
       </c>
       <c r="G6" t="n">
-        <v>39531520000</v>
+        <v>8365298000</v>
       </c>
       <c r="H6" t="n">
-        <v>2995.424821743842</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I6" t="n">
-        <v>8.859999999999999</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XRXF.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3132</v>
+        <v>9468</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>14653542</v>
+        <v>13197300</v>
       </c>
       <c r="G7" t="n">
-        <v>23038030000</v>
+        <v>39531520000</v>
       </c>
       <c r="H7" t="n">
-        <v>1572.181660925393</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I7" t="n">
-        <v>8.18</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6594</v>
+        <v>3132</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>80322406</v>
+        <v>14653542</v>
       </c>
       <c r="G8" t="n">
-        <v>178330543000</v>
+        <v>23038030000</v>
       </c>
       <c r="H8" t="n">
-        <v>2220.184278344451</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I8" t="n">
-        <v>6.74</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -739,81 +739,81 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1721</v>
+        <v>6594</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7462000</v>
+        <v>80322406</v>
       </c>
       <c r="G9" t="n">
-        <v>27875864000</v>
+        <v>178330543000</v>
       </c>
       <c r="H9" t="n">
-        <v>3735.709461270437</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I9" t="n">
-        <v>5.609999999999999</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6675</v>
+        <v>1721</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>314400</v>
+        <v>7462000</v>
       </c>
       <c r="G10" t="n">
-        <v>1717778000</v>
+        <v>27875864000</v>
       </c>
       <c r="H10" t="n">
-        <v>5463.67048346056</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I10" t="n">
-        <v>5.029999999999999</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3549</v>
+        <v>6675</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -821,406 +821,406 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>13408159</v>
+        <v>314400</v>
       </c>
       <c r="G11" t="n">
-        <v>40855887000</v>
+        <v>1717778000</v>
       </c>
       <c r="H11" t="n">
-        <v>3047.091476167608</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I11" t="n">
-        <v>14.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7745</v>
+        <v>3549</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1458700</v>
+        <v>13408159</v>
       </c>
       <c r="G12" t="n">
-        <v>3040190000</v>
+        <v>40855887000</v>
       </c>
       <c r="H12" t="n">
-        <v>2084.177692465894</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I12" t="n">
-        <v>5.24</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G13" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H13" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I13" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G14" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H14" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I14" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G15" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H15" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I15" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G16" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H16" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H17" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I17" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G18" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H18" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I18" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G19" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H19" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G20" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H20" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I20" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2432</v>
+        <v>2371</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>10372003</v>
       </c>
       <c r="G21" t="n">
-        <v>226000</v>
+        <v>24045569000</v>
       </c>
       <c r="H21" t="n">
-        <v>2260</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7378</v>
+        <v>2432</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1228,64 +1228,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>500400</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>698873000</v>
+        <v>226000</v>
       </c>
       <c r="H22" t="n">
-        <v>1396.628697042366</v>
+        <v>2260</v>
       </c>
       <c r="I22" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G23" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H23" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1294,109 +1294,109 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G24" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H24" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I24" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G25" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H25" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I25" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G26" t="n">
-        <v>268179335000</v>
+        <v>1970276000</v>
       </c>
       <c r="H26" t="n">
-        <v>16430.4430802409</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I26" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1416,10 +1416,10 @@
         <v>16322100</v>
       </c>
       <c r="G27" t="n">
-        <v>268179335457000</v>
+        <v>268179335000</v>
       </c>
       <c r="H27" t="n">
-        <v>16430443.10823975</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I27" t="n">
         <v>5.01</v>
@@ -1428,58 +1428,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G28" t="n">
-        <v>49662804000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H28" t="n">
-        <v>11879.91675437757</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I28" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1487,27 +1487,27 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G29" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H29" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I29" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1516,72 +1516,72 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G30" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H30" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I30" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G31" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H31" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1590,21 +1590,21 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H32" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -1613,12 +1613,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H33" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -1650,12 +1650,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H34" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -1687,12 +1687,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H35" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -1724,12 +1724,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1738,109 +1738,109 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H36" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G37" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H37" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I37" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G38" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H38" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I38" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1872,308 +1872,308 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G40" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H40" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I40" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5331</v>
+        <v>6104</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1481600</v>
+        <v>1297500</v>
       </c>
       <c r="G41" t="n">
-        <v>5294365000</v>
+        <v>4476090000</v>
       </c>
       <c r="H41" t="n">
-        <v>3573.410502159827</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G42" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H42" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I42" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G43" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H43" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H44" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I44" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G45" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H45" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I45" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G46" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H46" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G47" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H47" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2182,190 +2182,190 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G48" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H48" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I48" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G49" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H49" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I49" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H50" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G52" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H52" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9302</v>
+        <v>3106</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2373,27 +2373,27 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3799000</v>
+        <v>900156</v>
       </c>
       <c r="G53" t="n">
-        <v>5671170000</v>
+        <v>4095263000</v>
       </c>
       <c r="H53" t="n">
-        <v>1492.806001579363</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I53" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2402,72 +2402,72 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G54" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H54" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I54" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G55" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H55" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H56" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -2499,58 +2499,58 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H57" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I57" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4849</v>
+        <v>6927</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2558,175 +2558,175 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2946942</v>
+        <v>1142700</v>
       </c>
       <c r="G58" t="n">
-        <v>5148132000</v>
+        <v>1023871000</v>
       </c>
       <c r="H58" t="n">
-        <v>1746.940387696806</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I58" t="n">
-        <v>5.93</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G59" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H59" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H60" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I60" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G61" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H61" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I61" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G62" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H62" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2735,192 +2735,192 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H63" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I63" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G64" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H64" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I64" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G65" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H65" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I65" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G66" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H66" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I66" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G67" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H67" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4626</v>
+        <v>9987</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2928,27 +2928,27 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>4670190</v>
+        <v>3888200</v>
       </c>
       <c r="G68" t="n">
-        <v>16652257000</v>
+        <v>16086019000</v>
       </c>
       <c r="H68" t="n">
-        <v>3565.648720929983</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2957,72 +2957,72 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G69" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H69" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I69" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G70" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H70" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H71" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -3054,49 +3054,49 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G72" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H72" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I72" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3105,146 +3105,146 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G73" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H73" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I73" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G74" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H74" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G75" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H75" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I75" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G76" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H76" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I76" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3253,35 +3253,35 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G77" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H77" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I77" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3290,192 +3290,192 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G78" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H78" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I78" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G79" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H79" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I79" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G80" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H80" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I80" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G81" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H81" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I81" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G82" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H82" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I82" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8141</v>
+        <v>4272</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3483,27 +3483,27 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G83" t="n">
-        <v>93000</v>
+        <v>29860350000</v>
       </c>
       <c r="H83" t="n">
-        <v>930</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3512,21 +3512,21 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>100</v>
       </c>
       <c r="G84" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H84" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -3535,44 +3535,44 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4205</v>
+        <v>6145</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G85" t="n">
-        <v>24829312000</v>
+        <v>171000</v>
       </c>
       <c r="H85" t="n">
-        <v>1721.078563209627</v>
+        <v>1710</v>
       </c>
       <c r="I85" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3569</v>
+        <v>4205</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3594,175 +3594,175 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4271704</v>
+        <v>14426600</v>
       </c>
       <c r="G86" t="n">
-        <v>5808044000</v>
+        <v>24829312000</v>
       </c>
       <c r="H86" t="n">
-        <v>1359.655069733296</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I86" t="n">
-        <v>6.279999999999999</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G87" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H87" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I87" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G88" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H88" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G89" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H89" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I89" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G90" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H90" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3771,72 +3771,72 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G91" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H91" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I91" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G92" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H92" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I92" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3845,81 +3845,81 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G93" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H93" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I93" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G94" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H94" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I94" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5541</v>
+        <v>2168</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3927,73 +3927,73 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G95" t="n">
-        <v>127000</v>
+        <v>4445105000</v>
       </c>
       <c r="H95" t="n">
-        <v>1270</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G96" t="n">
-        <v>20578848000</v>
+        <v>127000</v>
       </c>
       <c r="H96" t="n">
-        <v>5066.092575838703</v>
+        <v>1270</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4001,36 +4001,36 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G97" t="n">
-        <v>361000</v>
+        <v>20578848000</v>
       </c>
       <c r="H97" t="n">
-        <v>3610</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4967</v>
+        <v>8803</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -4038,175 +4038,175 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G98" t="n">
-        <v>8729143000</v>
+        <v>361000</v>
       </c>
       <c r="H98" t="n">
-        <v>2148.936934940886</v>
+        <v>3610</v>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G99" t="n">
-        <v>5292086000</v>
+        <v>8729143000</v>
       </c>
       <c r="H99" t="n">
-        <v>2112.609181636727</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I99" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G100" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H100" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I100" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G101" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H101" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I101" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G102" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H102" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I102" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4215,192 +4215,192 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G103" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H103" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I103" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G104" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H104" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I104" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G105" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H105" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I105" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G106" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H106" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I106" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G107" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H107" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I107" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>3591</v>
+        <v>4042</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4408,249 +4408,249 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2846091</v>
+        <v>16459200</v>
       </c>
       <c r="G108" t="n">
-        <v>6888596000</v>
+        <v>33451116000</v>
       </c>
       <c r="H108" t="n">
-        <v>2420.370957920882</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I108" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G109" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H109" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H110" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I110" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G111" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H111" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I111" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G112" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H112" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I112" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G113" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H113" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G114" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H114" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I114" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4659,21 +4659,21 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G115" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H115" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I115" t="n">
         <v>5.02</v>
@@ -4682,197 +4682,197 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G116" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H116" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G117" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H117" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I117" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G118" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H118" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I118" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G119" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H119" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G120" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H120" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I120" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4885,142 +4885,142 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G121" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H121" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I121" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G122" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H122" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I122" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G123" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H123" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G124" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H124" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I124" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5029,35 +5029,35 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G125" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H125" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I125" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5066,30 +5066,30 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>4293</v>
+        <v>4837</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>20896886</v>
+        <v>5428600</v>
       </c>
       <c r="G126" t="n">
-        <v>9376038000</v>
+        <v>4378021000</v>
       </c>
       <c r="H126" t="n">
-        <v>448.6811097117532</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I126" t="n">
-        <v>9.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4631</v>
+        <v>4293</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5111,355 +5111,355 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>6563759</v>
+        <v>20896886</v>
       </c>
       <c r="G127" t="n">
-        <v>16844475000</v>
+        <v>9376038000</v>
       </c>
       <c r="H127" t="n">
-        <v>2566.284807227078</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I127" t="n">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5449</v>
+        <v>4631</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2114100</v>
+        <v>6563759</v>
       </c>
       <c r="G128" t="n">
-        <v>3695597000</v>
+        <v>16844475000</v>
       </c>
       <c r="H128" t="n">
-        <v>1748.071046781136</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I128" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G129" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H129" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I129" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G130" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H130" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I130" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G131" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H131" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I131" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G132" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H132" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I132" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G133" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H133" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I133" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G134" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H134" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G135" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H135" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I135" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5947</v>
+        <v>5844</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>7446200</v>
+        <v>4998800</v>
       </c>
       <c r="G136" t="n">
-        <v>21182239000</v>
+        <v>24949147000</v>
       </c>
       <c r="H136" t="n">
-        <v>2844.704547285864</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I136" t="n">
-        <v>4.96</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5481,467 +5481,467 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G137" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H137" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I137" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>8303</v>
+        <v>5186</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>20000000</v>
+        <v>1536900</v>
       </c>
       <c r="G138" t="n">
-        <v>56014500000</v>
+        <v>4758738000</v>
       </c>
       <c r="H138" t="n">
-        <v>2800.725</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I138" t="n">
-        <v>9.75</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G139" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H139" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I139" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RVIC.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>5451</v>
+        <v>2812</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1752800</v>
-      </c>
-      <c r="G140" t="n">
-        <v>5669831000</v>
-      </c>
-      <c r="H140" t="n">
-        <v>3234.727863989046</v>
-      </c>
+        <v>1120000</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
-        <v>5.029999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100RT6D.zip</t>
+          <t>S100RU33.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>9072</v>
+        <v>5451</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>8377400</v>
+        <v>1752800</v>
       </c>
       <c r="G141" t="n">
-        <v>13394541000</v>
+        <v>5669831000</v>
       </c>
       <c r="H141" t="n">
-        <v>1598.889989734285</v>
+        <v>3234.727863989046</v>
       </c>
       <c r="I141" t="n">
-        <v>12.74</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100RSA5.zip</t>
+          <t>S100RT6D.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-09-04_02_2023-09-06.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5194</v>
+        <v>9072</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1068798</v>
+        <v>8377400</v>
       </c>
       <c r="G142" t="n">
-        <v>997342000</v>
+        <v>13394541000</v>
       </c>
       <c r="H142" t="n">
-        <v>933.1435874692879</v>
+        <v>1598.889989734285</v>
       </c>
       <c r="I142" t="n">
-        <v>9.77</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100RIEU.zip</t>
+          <t>S100RSA5.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-08-28_01_2023-09-01.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>8871</v>
+        <v>5194</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1807700</v>
+        <v>1068798</v>
       </c>
       <c r="G143" t="n">
-        <v>3235548000</v>
+        <v>997342000</v>
       </c>
       <c r="H143" t="n">
-        <v>1789.870000553189</v>
+        <v>933.1435874692879</v>
       </c>
       <c r="I143" t="n">
-        <v>5.050000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100RGLG.zip</t>
+          <t>S100RIEU.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-08-01_01_2023-08-08.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>5929</v>
+        <v>8871</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>11571500</v>
+        <v>1807700</v>
       </c>
       <c r="G144" t="n">
-        <v>15114770000</v>
+        <v>3235548000</v>
       </c>
       <c r="H144" t="n">
-        <v>1306.206628354146</v>
+        <v>1789.870000553189</v>
       </c>
       <c r="I144" t="n">
-        <v>5.01</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100R23B.zip</t>
+          <t>S100RGLG.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-07-24_01_2023-07-31.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>8140</v>
+        <v>5929</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1322800</v>
+        <v>11571500</v>
       </c>
       <c r="G145" t="n">
-        <v>4536170000</v>
+        <v>15114770000</v>
       </c>
       <c r="H145" t="n">
-        <v>3429.218324765649</v>
+        <v>1306.206628354146</v>
       </c>
       <c r="I145" t="n">
-        <v>5.29</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100QVSV.zip</t>
+          <t>S100R23B.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-06-20_01_2023-06-27.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1878</v>
+        <v>8140</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3452100</v>
+        <v>1322800</v>
       </c>
       <c r="G146" t="n">
-        <v>44793976000</v>
+        <v>4536170000</v>
       </c>
       <c r="H146" t="n">
-        <v>12975.86280814577</v>
+        <v>3429.218324765649</v>
       </c>
       <c r="I146" t="n">
-        <v>5.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100QVRX.zip</t>
+          <t>S100QVSV.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2023-06-02_01_2023-06-05.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>533500</v>
+        <v>3452100</v>
       </c>
       <c r="G147" t="n">
-        <v>2009924000</v>
+        <v>44793976000</v>
       </c>
       <c r="H147" t="n">
-        <v>3767.430178069353</v>
+        <v>12975.86280814577</v>
       </c>
       <c r="I147" t="n">
-        <v>5.11</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100QV9B.zip</t>
+          <t>S100QVRX.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2023-05-31_01_2023-06-07.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3593</v>
+        <v>1882</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1637060</v>
+        <v>533500</v>
       </c>
       <c r="G148" t="n">
-        <v>5502657000</v>
+        <v>2009924000</v>
       </c>
       <c r="H148" t="n">
-        <v>3361.304411567078</v>
+        <v>3767.430178069353</v>
       </c>
       <c r="I148" t="n">
-        <v>6.48</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100QU54.zip</t>
+          <t>S100QV9B.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-05-25_01_2023-06-02.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>7157</v>
+        <v>3593</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>4536300</v>
+        <v>1637060</v>
       </c>
       <c r="G149" t="n">
-        <v>4025006000</v>
+        <v>5502657000</v>
       </c>
       <c r="H149" t="n">
-        <v>887.288318673809</v>
+        <v>3361.304411567078</v>
       </c>
       <c r="I149" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100QUDZ.zip</t>
+          <t>S100QU54.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-31.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1861</v>
+        <v>7157</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5958,143 +5958,143 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3102784</v>
+        <v>4536300</v>
       </c>
       <c r="G150" t="n">
-        <v>8614573000</v>
+        <v>4025006000</v>
       </c>
       <c r="H150" t="n">
-        <v>2776.401128792723</v>
+        <v>887.288318673809</v>
       </c>
       <c r="I150" t="n">
-        <v>7.07</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100QSK8.zip</t>
+          <t>S100QUDZ.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-24_01_2023-05-29.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>7350</v>
+        <v>1861</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+        <v>3102784</v>
+      </c>
+      <c r="G151" t="n">
+        <v>8614573000</v>
+      </c>
+      <c r="H151" t="n">
+        <v>2776.401128792723</v>
+      </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100QRVC.zip</t>
+          <t>S100QSK8.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
+          <t>jplvh020000-lvh-001_E24872-000_2023-05-16_02_2023-05-19.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3549</v>
+        <v>7350</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1735200</v>
-      </c>
-      <c r="G152" t="n">
-        <v>11532479000</v>
-      </c>
-      <c r="H152" t="n">
-        <v>6646.195827570309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100QP55.zip</t>
+          <t>S100QRVC.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-15_01_2023-05-18.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>6770</v>
+        <v>3549</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>11259700</v>
+        <v>1735200</v>
       </c>
       <c r="G153" t="n">
-        <v>14161429000</v>
+        <v>11532479000</v>
       </c>
       <c r="H153" t="n">
-        <v>1257.709264012363</v>
+        <v>6646.195827570309</v>
       </c>
       <c r="I153" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100QRUW.zip</t>
+          <t>S100QP55.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-05-08_01_2023-05-15.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3391</v>
+        <v>6770</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -6102,89 +6102,126 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>6354522</v>
+        <v>11259700</v>
       </c>
       <c r="G154" t="n">
-        <v>28876223000</v>
+        <v>14161429000</v>
       </c>
       <c r="H154" t="n">
-        <v>4544.200649553184</v>
+        <v>1257.709264012363</v>
       </c>
       <c r="I154" t="n">
-        <v>12.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QRUW.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-05-08_01_2023-05-16.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1951</v>
+        <v>3391</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>5561200</v>
+        <v>6354522</v>
       </c>
       <c r="G155" t="n">
-        <v>12623472000</v>
+        <v>28876223000</v>
       </c>
       <c r="H155" t="n">
-        <v>2269.918722577861</v>
+        <v>4544.200649553184</v>
       </c>
       <c r="I155" t="n">
-        <v>5.06</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>S100QNRY.zip</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>5561200</v>
+      </c>
+      <c r="G156" t="n">
+        <v>12623472000</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2269.918722577861</v>
+      </c>
+      <c r="I156" t="n">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
           <t>S100QNNV.zip</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
-      <c r="D156" t="n">
+      <c r="D157" t="n">
         <v>3085</v>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>2023-04-25</t>
         </is>
       </c>
-      <c r="F156" t="n">
+      <c r="F157" t="n">
         <v>1756300</v>
       </c>
-      <c r="G156" t="n">
+      <c r="G157" t="n">
         <v>4694343000</v>
       </c>
-      <c r="H156" t="n">
+      <c r="H157" t="n">
         <v>2672.859420372374</v>
       </c>
-      <c r="I156" t="n">
+      <c r="I157" t="n">
         <v>5.31</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -614,21 +614,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4676</v>
+        <v>9468</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -636,36 +636,36 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2662900</v>
+        <v>13197300</v>
       </c>
       <c r="G6" t="n">
-        <v>8365298000</v>
+        <v>39531520000</v>
       </c>
       <c r="H6" t="n">
-        <v>3141.424011416125</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I6" t="n">
-        <v>1.57</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9468</v>
+        <v>4676</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>13197300</v>
+        <v>2662900</v>
       </c>
       <c r="G7" t="n">
-        <v>39531520000</v>
+        <v>8365298000</v>
       </c>
       <c r="H7" t="n">
-        <v>2995.424821743842</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I7" t="n">
-        <v>8.859999999999999</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="8">
@@ -799,21 +799,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6675</v>
+        <v>3549</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -821,36 +821,36 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>314400</v>
+        <v>13408159</v>
       </c>
       <c r="G11" t="n">
-        <v>1717778000</v>
+        <v>40855887000</v>
       </c>
       <c r="H11" t="n">
-        <v>5463.67048346056</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I11" t="n">
-        <v>5.029999999999999</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3549</v>
+        <v>6675</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13408159</v>
+        <v>314400</v>
       </c>
       <c r="G12" t="n">
-        <v>40855887000</v>
+        <v>1717778000</v>
       </c>
       <c r="H12" t="n">
-        <v>3047.091476167608</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I12" t="n">
-        <v>14.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1391,12 +1391,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1416,10 +1416,10 @@
         <v>16322100</v>
       </c>
       <c r="G27" t="n">
-        <v>268179335000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H27" t="n">
-        <v>16430.4430802409</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I27" t="n">
         <v>5.01</v>
@@ -1428,12 +1428,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1453,10 +1453,10 @@
         <v>16322100</v>
       </c>
       <c r="G28" t="n">
-        <v>268179335457000</v>
+        <v>268179335000</v>
       </c>
       <c r="H28" t="n">
-        <v>16430443.10823975</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I28" t="n">
         <v>5.01</v>
@@ -1465,21 +1465,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1487,36 +1487,36 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G29" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H29" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I29" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8011</v>
+        <v>6856</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1524,16 +1524,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>551300</v>
+        <v>4180400</v>
       </c>
       <c r="G30" t="n">
-        <v>1831405000</v>
+        <v>49662804000</v>
       </c>
       <c r="H30" t="n">
-        <v>3321.975331035734</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I30" t="n">
-        <v>5.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="31">
@@ -1835,12 +1835,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1872,12 +1872,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2351,21 +2351,21 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3106</v>
+        <v>9302</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2373,36 +2373,36 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>900156</v>
+        <v>3799000</v>
       </c>
       <c r="G53" t="n">
-        <v>4095263000</v>
+        <v>5671170000</v>
       </c>
       <c r="H53" t="n">
-        <v>4549.503641591014</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>9302</v>
+        <v>3106</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2410,16 +2410,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3799000</v>
+        <v>900156</v>
       </c>
       <c r="G54" t="n">
-        <v>5671170000</v>
+        <v>4095263000</v>
       </c>
       <c r="H54" t="n">
-        <v>1492.806001579363</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I54" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -2536,21 +2536,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6927</v>
+        <v>4849</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2558,36 +2558,36 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1142700</v>
+        <v>2946942</v>
       </c>
       <c r="G58" t="n">
-        <v>1023871000</v>
+        <v>5148132000</v>
       </c>
       <c r="H58" t="n">
-        <v>896.0103264198827</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I58" t="n">
-        <v>5.01</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4849</v>
+        <v>6927</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2595,16 +2595,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2946942</v>
+        <v>1142700</v>
       </c>
       <c r="G59" t="n">
-        <v>5148132000</v>
+        <v>1023871000</v>
       </c>
       <c r="H59" t="n">
-        <v>1746.940387696806</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I59" t="n">
-        <v>5.93</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="60">
@@ -2906,21 +2906,21 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>9987</v>
+        <v>4626</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2928,36 +2928,36 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3888200</v>
+        <v>4670190</v>
       </c>
       <c r="G68" t="n">
-        <v>16086019000</v>
+        <v>16652257000</v>
       </c>
       <c r="H68" t="n">
-        <v>4137.137750115735</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4626</v>
+        <v>9987</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2965,16 +2965,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4670190</v>
+        <v>3888200</v>
       </c>
       <c r="G69" t="n">
-        <v>16652257000</v>
+        <v>16086019000</v>
       </c>
       <c r="H69" t="n">
-        <v>3565.648720929983</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -3905,21 +3905,21 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3927,36 +3927,36 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G95" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H95" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I95" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5541</v>
+        <v>2168</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3964,16 +3964,16 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G96" t="n">
-        <v>127000</v>
+        <v>4445105000</v>
       </c>
       <c r="H96" t="n">
-        <v>1270</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="97">

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6154,74 +6154,37 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100QNRY.zip</t>
+          <t>S100QNNV.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-04-26_01_2023-04-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1951</v>
+        <v>3085</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>5561200</v>
+        <v>1756300</v>
       </c>
       <c r="G156" t="n">
-        <v>12623472000</v>
+        <v>4694343000</v>
       </c>
       <c r="H156" t="n">
-        <v>2269.918722577861</v>
+        <v>2672.859420372374</v>
       </c>
       <c r="I156" t="n">
-        <v>5.06</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>S100QNNV.zip</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-04-25_01_2023-05-02.csv</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>3085</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>2023-04-25</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>1756300</v>
-      </c>
-      <c r="G157" t="n">
-        <v>4694343000</v>
-      </c>
-      <c r="H157" t="n">
-        <v>2672.859420372374</v>
-      </c>
-      <c r="I157" t="n">
         <v>5.31</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,132 +466,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S100XXO7.zip</t>
+          <t>S100Y15W.zip</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2026-04-21_01_2026-04-28.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4626</v>
+        <v>9147</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17384460</v>
+        <v>12252200</v>
       </c>
       <c r="G2" t="n">
-        <v>38239610000</v>
+        <v>40939867000</v>
       </c>
       <c r="H2" t="n">
-        <v>2199.643244598912</v>
+        <v>3341.42986565678</v>
       </c>
       <c r="I2" t="n">
-        <v>14.88</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100XW5T.zip</t>
+          <t>S100XXO7.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4613</v>
+        <v>4626</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8982300</v>
+        <v>17384460</v>
       </c>
       <c r="G3" t="n">
-        <v>21391558000</v>
+        <v>38239610000</v>
       </c>
       <c r="H3" t="n">
-        <v>2381.523440544182</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="I3" t="n">
-        <v>5.050000000000001</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100XWKV.zip</t>
+          <t>S100XW5T.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6952</v>
+        <v>4613</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11964800</v>
+        <v>8982300</v>
       </c>
       <c r="G4" t="n">
-        <v>14335634000</v>
+        <v>21391558000</v>
       </c>
       <c r="H4" t="n">
-        <v>1198.150742177053</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="I4" t="n">
-        <v>5.029999999999999</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100XVQY.zip</t>
+          <t>S100XWKV.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5423</v>
+        <v>6952</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -599,27 +599,27 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6884398</v>
+        <v>11964800</v>
       </c>
       <c r="G5" t="n">
-        <v>11052572000</v>
+        <v>14335634000</v>
       </c>
       <c r="H5" t="n">
-        <v>1605.452212379354</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="I5" t="n">
-        <v>6.25</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XVQY.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -628,24 +628,24 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9468</v>
+        <v>5423</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13197300</v>
+        <v>6884398</v>
       </c>
       <c r="G6" t="n">
-        <v>39531520000</v>
+        <v>11052572000</v>
       </c>
       <c r="H6" t="n">
-        <v>2995.424821743842</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="I6" t="n">
-        <v>8.859999999999999</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
@@ -688,86 +688,86 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100XRXF.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3132</v>
+        <v>9468</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>14653542</v>
+        <v>13197300</v>
       </c>
       <c r="G8" t="n">
-        <v>23038030000</v>
+        <v>39531520000</v>
       </c>
       <c r="H8" t="n">
-        <v>1572.181660925393</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I8" t="n">
-        <v>8.18</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6594</v>
+        <v>3132</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>80322406</v>
+        <v>14653542</v>
       </c>
       <c r="G9" t="n">
-        <v>178330543000</v>
+        <v>23038030000</v>
       </c>
       <c r="H9" t="n">
-        <v>2220.184278344451</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I9" t="n">
-        <v>6.74</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -776,35 +776,35 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1721</v>
+        <v>6594</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7462000</v>
+        <v>80322406</v>
       </c>
       <c r="G10" t="n">
-        <v>27875864000</v>
+        <v>178330543000</v>
       </c>
       <c r="H10" t="n">
-        <v>3735.709461270437</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I10" t="n">
-        <v>5.609999999999999</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -813,44 +813,44 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3549</v>
+        <v>1721</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>13408159</v>
+        <v>7462000</v>
       </c>
       <c r="G11" t="n">
-        <v>40855887000</v>
+        <v>27875864000</v>
       </c>
       <c r="H11" t="n">
-        <v>3047.091476167608</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I11" t="n">
-        <v>14.02</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6675</v>
+        <v>3549</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -858,406 +858,406 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>314400</v>
+        <v>13408159</v>
       </c>
       <c r="G12" t="n">
-        <v>1717778000</v>
+        <v>40855887000</v>
       </c>
       <c r="H12" t="n">
-        <v>5463.67048346056</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I12" t="n">
-        <v>5.029999999999999</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7745</v>
+        <v>6675</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1458700</v>
+        <v>314400</v>
       </c>
       <c r="G13" t="n">
-        <v>3040190000</v>
+        <v>1717778000</v>
       </c>
       <c r="H13" t="n">
-        <v>2084.177692465894</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I13" t="n">
-        <v>5.24</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G14" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H14" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I14" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G15" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H15" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I15" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G16" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H16" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I16" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G17" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H17" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H18" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I18" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G19" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H19" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I19" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G20" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H20" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G21" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H21" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I21" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2432</v>
+        <v>2371</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>10372003</v>
       </c>
       <c r="G22" t="n">
-        <v>226000</v>
+        <v>24045569000</v>
       </c>
       <c r="H22" t="n">
-        <v>2260</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7378</v>
+        <v>2432</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1265,64 +1265,64 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>500400</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>698873000</v>
+        <v>226000</v>
       </c>
       <c r="H23" t="n">
-        <v>1396.628697042366</v>
+        <v>2260</v>
       </c>
       <c r="I23" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G24" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H24" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1331,98 +1331,98 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G25" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H25" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I25" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G26" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H26" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I26" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G27" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H27" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I27" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="28">
@@ -1465,58 +1465,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G29" t="n">
-        <v>1831405000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H29" t="n">
-        <v>3321.975331035734</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I29" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1524,101 +1524,101 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G30" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H30" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I30" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4549</v>
+        <v>6856</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2546351</v>
+        <v>4180400</v>
       </c>
       <c r="G31" t="n">
-        <v>4958319000</v>
+        <v>49662804000</v>
       </c>
       <c r="H31" t="n">
-        <v>1947.225264702313</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I31" t="n">
-        <v>7.37</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G32" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H32" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H33" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -1650,12 +1650,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H34" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -1687,12 +1687,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H35" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -1724,12 +1724,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H36" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -1761,12 +1761,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1775,109 +1775,109 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H37" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G38" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H38" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I38" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO9C.zip</t>
  